--- a/selected_all_samples.xlsx
+++ b/selected_all_samples.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10802"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/durgaacharya/Documents/Nepal_Geology/Impact_of_Rock_Structure_on_Tensile_Strength-Rupture/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:80000009_{93EEE641-2355-B841-BB34-B52B8D5E1887}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB0C7700-3C86-3543-8C6E-7E6FA078DED0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1340" yWindow="600" windowWidth="37060" windowHeight="19460" xr2:uid="{DAA96A09-7419-F74F-A2D7-B0B57583498C}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="48040" windowHeight="26860" xr2:uid="{DAA96A09-7419-F74F-A2D7-B0B57583498C}"/>
   </bookViews>
   <sheets>
     <sheet name="selected_all_samples" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="27">
   <si>
     <t>SN</t>
   </si>
@@ -109,16 +110,23 @@
   <si>
     <t>Psammitic schist</t>
   </si>
+  <si>
+    <t>Modulus_of_Elasticity_GPa</t>
+  </si>
+  <si>
+    <t>Shear_Modulus_GPa</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="167" formatCode="0.000000"/>
-    <numFmt numFmtId="168" formatCode="0.00000"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="0.00000"/>
+    <numFmt numFmtId="165" formatCode="0.0000000"/>
+    <numFmt numFmtId="166" formatCode="0.000000"/>
   </numFmts>
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -252,12 +260,6 @@
       <color rgb="FFFF0000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -604,10 +606,10 @@
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="2" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="1" builtinId="30" customBuiltin="1"/>
@@ -1003,20 +1005,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E165A15B-F019-FD46-9263-415DEE6852B2}">
-  <dimension ref="A1:W55"/>
+  <dimension ref="A1:W77"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="15" customWidth="1"/>
     <col min="5" max="6" width="14.5" customWidth="1"/>
+    <col min="7" max="7" width="10.83203125" style="2"/>
     <col min="8" max="8" width="13.1640625" customWidth="1"/>
-    <col min="9" max="9" width="13.1640625" style="3" customWidth="1"/>
-    <col min="10" max="10" width="15" style="3" customWidth="1"/>
-    <col min="11" max="11" width="13.1640625" style="3" customWidth="1"/>
-    <col min="12" max="12" width="13.1640625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="13.1640625" style="2" customWidth="1"/>
+    <col min="10" max="10" width="15" style="2" customWidth="1"/>
+    <col min="11" max="11" width="13.5" style="2" customWidth="1"/>
+    <col min="12" max="12" width="13.1640625" style="2" customWidth="1"/>
     <col min="13" max="13" width="19.83203125" customWidth="1"/>
-    <col min="16" max="16" width="12.6640625" customWidth="1"/>
-    <col min="17" max="17" width="12" style="1" customWidth="1"/>
-    <col min="18" max="18" width="13.5" customWidth="1"/>
+    <col min="15" max="15" width="12" style="4" customWidth="1"/>
+    <col min="16" max="16" width="12.6640625" style="3" customWidth="1"/>
+    <col min="17" max="17" width="18.33203125" customWidth="1"/>
+    <col min="18" max="18" width="13.5" style="2" customWidth="1"/>
     <col min="19" max="19" width="13.1640625" customWidth="1"/>
     <col min="23" max="23" width="13.83203125" customWidth="1"/>
   </cols>
@@ -1064,14 +1068,14 @@
       <c r="N1" t="s">
         <v>7</v>
       </c>
-      <c r="O1" t="s">
-        <v>8</v>
+      <c r="O1" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="P1" t="s">
         <v>9</v>
       </c>
-      <c r="Q1" s="1" t="s">
-        <v>10</v>
+      <c r="Q1" t="s">
+        <v>8</v>
       </c>
       <c r="R1" t="s">
         <v>11</v>
@@ -1108,51 +1112,51 @@
       <c r="E2">
         <v>23</v>
       </c>
-      <c r="F2" s="3">
+      <c r="F2" s="2">
         <v>0.45098039215686275</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="2">
         <f>(PI()*D2*E2)</f>
         <v>3685.0881826608274</v>
       </c>
-      <c r="H2" s="3">
+      <c r="H2" s="2">
         <f t="shared" ref="H2:H33" si="0">((PI()*D2^2)*E2)/4</f>
         <v>46984.874328925551</v>
       </c>
-      <c r="I2" s="3">
-        <v>2.6225461227666074</v>
+      <c r="I2" s="2">
+        <v>2.78</v>
       </c>
       <c r="J2">
-        <v>1.1299999999999999</v>
-      </c>
-      <c r="K2" s="4">
-        <v>2.652519594180851</v>
-      </c>
-      <c r="L2" s="1">
+        <v>1.45</v>
+      </c>
+      <c r="K2" s="2">
+        <v>2.8210000000000002</v>
+      </c>
+      <c r="L2" s="2">
         <v>18.738673408830309</v>
       </c>
       <c r="M2">
         <v>10.17</v>
       </c>
       <c r="N2">
-        <v>123.22</v>
-      </c>
-      <c r="O2">
-        <v>36.869999999999997</v>
-      </c>
-      <c r="P2" s="2">
-        <v>2.9236777868185514E-4</v>
-      </c>
-      <c r="Q2" s="1">
-        <v>1.1244914564686737E-3</v>
-      </c>
-      <c r="R2">
-        <v>0.26</v>
+        <v>130.62</v>
+      </c>
+      <c r="O2" s="4">
+        <v>1.25752E-3</v>
+      </c>
+      <c r="P2" s="3">
+        <v>3.3272E-4</v>
+      </c>
+      <c r="Q2">
+        <v>32.97</v>
+      </c>
+      <c r="R2" s="2">
+        <v>0.2646</v>
       </c>
       <c r="S2">
-        <v>14.63</v>
-      </c>
-      <c r="T2" s="3">
+        <v>14.03</v>
+      </c>
+      <c r="T2" s="2">
         <f>RADIANS(C2)</f>
         <v>0</v>
       </c>
@@ -1160,7 +1164,7 @@
         <v>41.46</v>
       </c>
       <c r="V2">
-        <v>9.2200000000000006</v>
+        <v>15.22</v>
       </c>
       <c r="W2">
         <v>37.89</v>
@@ -1182,51 +1186,51 @@
       <c r="E3">
         <v>24</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F3" s="2">
         <v>0.47058823529411764</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="2">
         <f t="shared" ref="G3:G53" si="1">(PI()*D3*E3)</f>
         <v>3845.3094079939065</v>
       </c>
-      <c r="H3" s="3">
+      <c r="H3" s="2">
         <f t="shared" si="0"/>
         <v>49027.694951922313</v>
       </c>
-      <c r="I3" s="3">
-        <v>2.5650808206121694</v>
+      <c r="I3" s="2">
+        <v>2.84</v>
       </c>
       <c r="J3">
-        <v>1.03</v>
-      </c>
-      <c r="K3" s="4">
-        <v>2.5917761145924718</v>
-      </c>
-      <c r="L3" s="1">
+        <v>0.93</v>
+      </c>
+      <c r="K3" s="2">
+        <v>2.867</v>
+      </c>
+      <c r="L3" s="2">
         <v>20.514725691647492</v>
       </c>
       <c r="M3">
         <v>10.67</v>
       </c>
       <c r="N3">
-        <v>125.76</v>
-      </c>
-      <c r="O3">
-        <v>36.869999999999997</v>
-      </c>
-      <c r="P3" s="2">
-        <v>4.1394087333875782E-4</v>
-      </c>
-      <c r="Q3" s="1">
-        <v>1.5920802820721454E-3</v>
-      </c>
-      <c r="R3">
-        <v>0.26</v>
+        <v>139.24</v>
+      </c>
+      <c r="O3" s="4">
+        <v>1.5636000000000001E-3</v>
+      </c>
+      <c r="P3" s="3">
+        <v>4.0734000000000001E-4</v>
+      </c>
+      <c r="Q3">
+        <v>37.54</v>
+      </c>
+      <c r="R3" s="2">
+        <v>0.26050000000000001</v>
       </c>
       <c r="S3">
-        <v>14.63</v>
-      </c>
-      <c r="T3" s="3">
+        <v>15.98</v>
+      </c>
+      <c r="T3" s="2">
         <f t="shared" ref="T3:T53" si="2">RADIANS(C3)</f>
         <v>0</v>
       </c>
@@ -1234,7 +1238,7 @@
         <v>58.7</v>
       </c>
       <c r="V3">
-        <v>9.2200000000000006</v>
+        <v>15.22</v>
       </c>
       <c r="W3">
         <v>37.89</v>
@@ -1256,51 +1260,51 @@
       <c r="E4">
         <v>27</v>
       </c>
-      <c r="F4" s="3">
+      <c r="F4" s="2">
         <v>0.52941176470588236</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="2">
         <f t="shared" si="1"/>
         <v>4325.9730839931453</v>
       </c>
-      <c r="H4" s="3">
+      <c r="H4" s="2">
         <f t="shared" si="0"/>
         <v>55156.156820912598</v>
       </c>
-      <c r="I4" s="3">
-        <v>2.661534241347657</v>
+      <c r="I4" s="2">
+        <v>2.76</v>
       </c>
       <c r="J4">
-        <v>0.94</v>
-      </c>
-      <c r="K4" s="4">
-        <v>2.686790067986732</v>
-      </c>
-      <c r="L4" s="1">
+        <v>1.42</v>
+      </c>
+      <c r="K4" s="2">
+        <v>2.8</v>
+      </c>
+      <c r="L4" s="2">
         <v>22.949287210583638</v>
       </c>
       <c r="M4">
         <v>10.61</v>
       </c>
       <c r="N4">
-        <v>146.80000000000001</v>
-      </c>
-      <c r="O4">
-        <v>36.869999999999997</v>
-      </c>
-      <c r="P4" s="2">
-        <v>4.3227556278817466E-4</v>
-      </c>
-      <c r="Q4" s="1">
-        <v>1.6625983184160563E-3</v>
-      </c>
-      <c r="R4">
-        <v>0.26</v>
+        <v>152.22999999999999</v>
+      </c>
+      <c r="O4" s="4">
+        <v>1.58927E-3</v>
+      </c>
+      <c r="P4" s="3">
+        <v>4.0962000000000003E-4</v>
+      </c>
+      <c r="Q4">
+        <v>38.57</v>
+      </c>
+      <c r="R4" s="2">
+        <v>0.25769999999999998</v>
       </c>
       <c r="S4">
-        <v>14.63</v>
-      </c>
-      <c r="T4" s="3">
+        <v>16.41</v>
+      </c>
+      <c r="T4" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -1308,7 +1312,7 @@
         <v>61.3</v>
       </c>
       <c r="V4">
-        <v>9.2200000000000006</v>
+        <v>15.22</v>
       </c>
       <c r="W4">
         <v>37.89</v>
@@ -1330,51 +1334,51 @@
       <c r="E5">
         <v>22.5</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F5" s="2">
         <v>0.44117647058823528</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="2">
         <f t="shared" si="1"/>
         <v>3604.9775699942875</v>
       </c>
-      <c r="H5" s="3">
+      <c r="H5" s="2">
         <f t="shared" si="0"/>
         <v>45963.46401742717</v>
       </c>
-      <c r="I5" s="3">
-        <v>2.680824925494754</v>
+      <c r="I5" s="2">
+        <v>2.88</v>
       </c>
       <c r="J5">
-        <v>1.01</v>
-      </c>
-      <c r="K5" s="4">
-        <v>2.7081775184309063</v>
-      </c>
-      <c r="L5" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="K5" s="2">
+        <v>2.903</v>
+      </c>
+      <c r="L5" s="2">
         <v>19.665152644318837</v>
       </c>
       <c r="M5">
         <v>10.91</v>
       </c>
       <c r="N5">
-        <v>123.22</v>
-      </c>
-      <c r="O5">
-        <v>36.869999999999997</v>
-      </c>
-      <c r="P5" s="2">
-        <v>4.1676159479251426E-4</v>
-      </c>
-      <c r="Q5" s="1">
-        <v>1.6029292107404393E-3</v>
-      </c>
-      <c r="R5">
-        <v>0.26</v>
+        <v>132.37</v>
+      </c>
+      <c r="O5" s="4">
+        <v>1.55572E-3</v>
+      </c>
+      <c r="P5" s="3">
+        <v>4.0382999999999999E-4</v>
+      </c>
+      <c r="Q5">
+        <v>37.99</v>
+      </c>
+      <c r="R5" s="2">
+        <v>0.2596</v>
       </c>
       <c r="S5">
-        <v>14.63</v>
-      </c>
-      <c r="T5" s="3">
+        <v>16.170000000000002</v>
+      </c>
+      <c r="T5" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -1382,7 +1386,7 @@
         <v>59.1</v>
       </c>
       <c r="V5">
-        <v>9.2200000000000006</v>
+        <v>15.22</v>
       </c>
       <c r="W5">
         <v>37.89</v>
@@ -1404,51 +1408,51 @@
       <c r="E6">
         <v>24.5</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F6" s="2">
         <v>0.48039215686274511</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="2">
         <f t="shared" si="1"/>
         <v>3925.4200206604464</v>
       </c>
-      <c r="H6" s="3">
+      <c r="H6" s="2">
         <f t="shared" si="0"/>
         <v>50049.105263420694</v>
       </c>
-      <c r="I6" s="3">
-        <v>2.6400072349858696</v>
+      <c r="I6" s="2">
+        <v>2.81</v>
       </c>
       <c r="J6">
-        <v>0.91</v>
-      </c>
-      <c r="K6" s="4">
-        <v>2.6642519275263594</v>
-      </c>
-      <c r="L6" s="1">
+        <v>1.34</v>
+      </c>
+      <c r="K6" s="2">
+        <v>2.8479999999999999</v>
+      </c>
+      <c r="L6" s="2">
         <v>19.60747300319893</v>
       </c>
       <c r="M6">
         <v>9.99</v>
       </c>
       <c r="N6">
-        <v>132.13</v>
-      </c>
-      <c r="O6">
-        <v>36.869999999999997</v>
-      </c>
-      <c r="P6" s="2">
-        <v>4.0054244643341469E-4</v>
-      </c>
-      <c r="Q6" s="1">
-        <v>1.5405478708977488E-3</v>
-      </c>
-      <c r="R6">
-        <v>0.26</v>
+        <v>140.63999999999999</v>
+      </c>
+      <c r="O6" s="4">
+        <v>1.5236500000000001E-3</v>
+      </c>
+      <c r="P6" s="3">
+        <v>3.9247000000000002E-4</v>
+      </c>
+      <c r="Q6">
+        <v>37.28</v>
+      </c>
+      <c r="R6" s="2">
+        <v>0.2576</v>
       </c>
       <c r="S6">
-        <v>14.63</v>
-      </c>
-      <c r="T6" s="3">
+        <v>15.86</v>
+      </c>
+      <c r="T6" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -1456,7 +1460,7 @@
         <v>56.8</v>
       </c>
       <c r="V6">
-        <v>9.2200000000000006</v>
+        <v>15.22</v>
       </c>
       <c r="W6">
         <v>37.89</v>
@@ -1464,7 +1468,7 @@
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>23</v>
@@ -1478,51 +1482,51 @@
       <c r="E7">
         <v>20</v>
       </c>
-      <c r="F7" s="3">
+      <c r="F7" s="2">
         <v>0.39215686274509803</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="2">
         <f t="shared" si="1"/>
         <v>3204.424506661589</v>
       </c>
-      <c r="H7" s="3">
+      <c r="H7" s="2">
         <f t="shared" si="0"/>
         <v>40856.412459935258</v>
       </c>
-      <c r="I7" s="3">
-        <v>2.8237917392559733</v>
+      <c r="I7" s="2">
+        <v>2.73</v>
       </c>
       <c r="J7">
-        <v>0.73</v>
-      </c>
-      <c r="K7" s="4">
-        <v>2.8445570053953593</v>
-      </c>
-      <c r="L7" s="1">
+        <v>1.71</v>
+      </c>
+      <c r="K7" s="2">
+        <v>2.7770000000000001</v>
+      </c>
+      <c r="L7" s="2">
         <v>17.191737478239425</v>
       </c>
       <c r="M7">
         <v>10.73</v>
       </c>
       <c r="N7">
-        <v>115.37</v>
-      </c>
-      <c r="O7">
-        <v>36.869999999999997</v>
-      </c>
-      <c r="P7" s="2">
-        <v>3.3284513154326013E-4</v>
-      </c>
-      <c r="Q7" s="1">
-        <v>1.2801735828586929E-3</v>
-      </c>
-      <c r="R7">
-        <v>0.26</v>
+        <v>111.54</v>
+      </c>
+      <c r="O7" s="4">
+        <v>1.24581E-3</v>
+      </c>
+      <c r="P7" s="3">
+        <v>3.1105999999999999E-4</v>
+      </c>
+      <c r="Q7">
+        <v>37.89</v>
+      </c>
+      <c r="R7" s="2">
+        <v>0.24970000000000001</v>
       </c>
       <c r="S7">
-        <v>14.63</v>
-      </c>
-      <c r="T7" s="3">
+        <v>16.22</v>
+      </c>
+      <c r="T7" s="2">
         <f t="shared" si="2"/>
         <v>0.26179938779914941</v>
       </c>
@@ -1530,15 +1534,15 @@
         <v>47.2</v>
       </c>
       <c r="V7">
-        <v>9.2200000000000006</v>
+        <v>14.1</v>
       </c>
       <c r="W7">
-        <v>37.89</v>
+        <v>36.729999999999997</v>
       </c>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
         <v>23</v>
@@ -1552,51 +1556,51 @@
       <c r="E8">
         <v>27</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F8" s="2">
         <v>0.52941176470588236</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="2">
         <f t="shared" si="1"/>
         <v>4325.9730839931453</v>
       </c>
-      <c r="H8" s="3">
+      <c r="H8" s="2">
         <f t="shared" si="0"/>
         <v>55156.156820912598</v>
       </c>
-      <c r="I8" s="3">
-        <v>2.661534241347657</v>
+      <c r="I8" s="2">
+        <v>2.86</v>
       </c>
       <c r="J8">
-        <v>1.1499999999999999</v>
-      </c>
-      <c r="K8" s="4">
-        <v>2.6924979679794201</v>
-      </c>
-      <c r="L8" s="1">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="K8" s="2">
+        <v>2.8929999999999998</v>
+      </c>
+      <c r="L8" s="2">
         <v>21.975943266685178</v>
       </c>
       <c r="M8">
         <v>10.16</v>
       </c>
       <c r="N8">
-        <v>146.80000000000001</v>
-      </c>
-      <c r="O8">
-        <v>49.67</v>
-      </c>
-      <c r="P8" s="2">
-        <v>2.1844976847191461E-4</v>
-      </c>
-      <c r="Q8" s="1">
-        <v>9.9295349305415738E-4</v>
-      </c>
-      <c r="R8">
-        <v>0.22</v>
+        <v>157.75</v>
+      </c>
+      <c r="O8" s="4">
+        <v>1.3602E-3</v>
+      </c>
+      <c r="P8" s="3">
+        <v>3.5435000000000002E-4</v>
+      </c>
+      <c r="Q8">
+        <v>36.26</v>
+      </c>
+      <c r="R8" s="2">
+        <v>0.26050000000000001</v>
       </c>
       <c r="S8">
-        <v>20.36</v>
-      </c>
-      <c r="T8" s="3">
+        <v>15.52</v>
+      </c>
+      <c r="T8" s="2">
         <f t="shared" si="2"/>
         <v>0.26179938779914941</v>
       </c>
@@ -1604,15 +1608,15 @@
         <v>49.32</v>
       </c>
       <c r="V8">
-        <v>8.51</v>
+        <v>14.1</v>
       </c>
       <c r="W8">
-        <v>37.01</v>
+        <v>36.729999999999997</v>
       </c>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B9" t="s">
         <v>23</v>
@@ -1626,51 +1630,51 @@
       <c r="E9">
         <v>23</v>
       </c>
-      <c r="F9" s="3">
+      <c r="F9" s="2">
         <v>0.45098039215686275</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="2">
         <f t="shared" si="1"/>
         <v>3685.0881826608274</v>
       </c>
-      <c r="H9" s="3">
+      <c r="H9" s="2">
         <f t="shared" si="0"/>
         <v>46984.874328925551</v>
       </c>
-      <c r="I9" s="3">
-        <v>2.6987408567343434</v>
+      <c r="I9" s="2">
+        <v>2.79</v>
       </c>
       <c r="J9">
-        <v>0.8</v>
-      </c>
-      <c r="K9" s="4">
-        <v>2.7205048959015556</v>
-      </c>
-      <c r="L9" s="1">
+        <v>1.2</v>
+      </c>
+      <c r="K9" s="2">
+        <v>2.8239999999999998</v>
+      </c>
+      <c r="L9" s="2">
         <v>17.891103126818319</v>
       </c>
       <c r="M9">
         <v>9.7100000000000009</v>
       </c>
       <c r="N9">
-        <v>126.8</v>
-      </c>
-      <c r="O9">
-        <v>49.67</v>
-      </c>
-      <c r="P9" s="2">
-        <v>2.3386349909402051E-4</v>
-      </c>
-      <c r="Q9" s="1">
-        <v>1.0630159049728205E-3</v>
-      </c>
-      <c r="R9">
-        <v>0.22</v>
+        <v>131.09</v>
+      </c>
+      <c r="O9" s="4">
+        <v>1.37805E-3</v>
+      </c>
+      <c r="P9" s="3">
+        <v>3.4619000000000002E-4</v>
+      </c>
+      <c r="Q9">
+        <v>38.32</v>
+      </c>
+      <c r="R9" s="2">
+        <v>0.25119999999999998</v>
       </c>
       <c r="S9">
-        <v>20.36</v>
-      </c>
-      <c r="T9" s="3">
+        <v>16.399999999999999</v>
+      </c>
+      <c r="T9" s="2">
         <f t="shared" si="2"/>
         <v>0.26179938779914941</v>
       </c>
@@ -1678,15 +1682,15 @@
         <v>52.8</v>
       </c>
       <c r="V9">
-        <v>8.51</v>
+        <v>14.1</v>
       </c>
       <c r="W9">
-        <v>37.01</v>
+        <v>36.729999999999997</v>
       </c>
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B10" t="s">
         <v>23</v>
@@ -1700,51 +1704,51 @@
       <c r="E10">
         <v>25</v>
       </c>
-      <c r="F10" s="3">
+      <c r="F10" s="2">
         <v>0.49019607843137253</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="2">
         <f t="shared" si="1"/>
         <v>4005.5306333269859</v>
       </c>
-      <c r="H10" s="3">
+      <c r="H10" s="2">
         <f t="shared" si="0"/>
         <v>51070.515574919074</v>
       </c>
-      <c r="I10" s="3">
-        <v>2.6222566679113108</v>
+      <c r="I10" s="2">
+        <v>2.83</v>
       </c>
       <c r="J10">
-        <v>0.92</v>
-      </c>
-      <c r="K10" s="4">
-        <v>2.6466054379403623</v>
-      </c>
-      <c r="L10" s="1">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="K10" s="2">
+        <v>2.8620000000000001</v>
+      </c>
+      <c r="L10" s="2">
         <v>19.907487247635121</v>
       </c>
       <c r="M10">
         <v>9.94</v>
       </c>
       <c r="N10">
-        <v>133.91999999999999</v>
-      </c>
-      <c r="O10">
-        <v>49.67</v>
-      </c>
-      <c r="P10" s="2">
-        <v>2.2057580028186029E-4</v>
-      </c>
-      <c r="Q10" s="1">
-        <v>1.0026172740084558E-3</v>
-      </c>
-      <c r="R10">
-        <v>0.22</v>
+        <v>144.53</v>
+      </c>
+      <c r="O10" s="4">
+        <v>1.3424699999999999E-3</v>
+      </c>
+      <c r="P10" s="3">
+        <v>3.4215E-4</v>
+      </c>
+      <c r="Q10">
+        <v>37.1</v>
+      </c>
+      <c r="R10" s="2">
+        <v>0.25490000000000002</v>
       </c>
       <c r="S10">
-        <v>20.36</v>
-      </c>
-      <c r="T10" s="3">
+        <v>15.88</v>
+      </c>
+      <c r="T10" s="2">
         <f t="shared" si="2"/>
         <v>0.26179938779914941</v>
       </c>
@@ -1752,15 +1756,15 @@
         <v>49.8</v>
       </c>
       <c r="V10">
-        <v>8.51</v>
+        <v>14.1</v>
       </c>
       <c r="W10">
-        <v>37.01</v>
+        <v>36.729999999999997</v>
       </c>
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A11">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="B11" t="s">
         <v>23</v>
@@ -1774,51 +1778,51 @@
       <c r="E11">
         <v>21</v>
       </c>
-      <c r="F11" s="3">
+      <c r="F11" s="2">
         <v>0.41176470588235292</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="2">
         <f>(PI()*D11*E11)</f>
         <v>3364.6457319946685</v>
       </c>
-      <c r="H11" s="3">
+      <c r="H11" s="2">
         <f>((PI()*D11^2)*E11)/4</f>
         <v>42899.23308293202</v>
       </c>
-      <c r="I11" s="3">
-        <v>2.4979467533333342</v>
+      <c r="I11" s="2">
+        <v>2.91</v>
       </c>
       <c r="J11">
-        <v>1.21</v>
-      </c>
-      <c r="K11" s="4">
-        <v>2.5285421128994172</v>
-      </c>
-      <c r="L11" s="1">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="K11" s="2">
+        <v>2.927</v>
+      </c>
+      <c r="L11" s="2">
         <v>16.133476284914437</v>
       </c>
       <c r="M11">
         <v>9.59</v>
       </c>
       <c r="N11">
-        <v>107.16</v>
-      </c>
-      <c r="O11">
-        <v>43.25</v>
-      </c>
-      <c r="P11" s="2">
-        <v>3.707976878612716E-4</v>
-      </c>
-      <c r="Q11" s="1">
-        <v>1.2786127167630057E-3</v>
-      </c>
-      <c r="R11">
-        <v>0.28999999999999998</v>
+        <v>124.84</v>
+      </c>
+      <c r="O11" s="4">
+        <v>1.49383E-3</v>
+      </c>
+      <c r="P11" s="3">
+        <v>3.9124E-4</v>
+      </c>
+      <c r="Q11">
+        <v>37.020000000000003</v>
+      </c>
+      <c r="R11" s="2">
+        <v>0.26190000000000002</v>
       </c>
       <c r="S11">
-        <v>16.760000000000002</v>
-      </c>
-      <c r="T11" s="3">
+        <v>15.85</v>
+      </c>
+      <c r="T11" s="2">
         <f>RADIANS(C11)</f>
         <v>0.26179938779914941</v>
       </c>
@@ -1826,10 +1830,10 @@
         <v>55.3</v>
       </c>
       <c r="V11">
-        <v>10.76</v>
+        <v>14.1</v>
       </c>
       <c r="W11">
-        <v>36.65</v>
+        <v>36.729999999999997</v>
       </c>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.2">
@@ -1848,51 +1852,51 @@
       <c r="E12">
         <v>22</v>
       </c>
-      <c r="F12" s="3">
+      <c r="F12" s="2">
         <v>0.43137254901960786</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="2">
         <f t="shared" si="1"/>
         <v>3524.866957327748</v>
       </c>
-      <c r="H12" s="3">
+      <c r="H12" s="2">
         <f t="shared" si="0"/>
         <v>44942.053705928782</v>
       </c>
-      <c r="I12" s="3">
-        <v>2.610917622229632</v>
+      <c r="I12" s="2">
+        <v>2.75</v>
       </c>
       <c r="J12">
-        <v>1.22</v>
-      </c>
-      <c r="K12" s="4">
-        <v>2.643164225784199</v>
-      </c>
-      <c r="L12" s="1">
+        <v>1.45</v>
+      </c>
+      <c r="K12" s="2">
+        <v>2.79</v>
+      </c>
+      <c r="L12" s="2">
         <v>16.690245042946888</v>
       </c>
       <c r="M12">
         <v>9.4700000000000006</v>
       </c>
       <c r="N12">
-        <v>117.34</v>
-      </c>
-      <c r="O12">
-        <v>37.75</v>
-      </c>
-      <c r="P12" s="2">
-        <v>2.4615894039735098E-4</v>
-      </c>
-      <c r="Q12" s="1">
-        <v>9.8463576158940394E-4</v>
-      </c>
-      <c r="R12">
-        <v>0.25</v>
+        <v>123.59</v>
+      </c>
+      <c r="O12" s="4">
+        <v>9.6080999999999998E-4</v>
+      </c>
+      <c r="P12" s="3">
+        <v>2.3230000000000001E-4</v>
+      </c>
+      <c r="Q12">
+        <v>38.69</v>
+      </c>
+      <c r="R12" s="2">
+        <v>0.24179999999999999</v>
       </c>
       <c r="S12">
-        <v>15.1</v>
-      </c>
-      <c r="T12" s="3">
+        <v>16.760000000000002</v>
+      </c>
+      <c r="T12" s="2">
         <f t="shared" si="2"/>
         <v>0.52359877559829882</v>
       </c>
@@ -1900,10 +1904,10 @@
         <v>37.17</v>
       </c>
       <c r="V12">
-        <v>5.31</v>
+        <v>11.309999999999999</v>
       </c>
       <c r="W12">
-        <v>33.97</v>
+        <v>33.06</v>
       </c>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.2">
@@ -1922,51 +1926,51 @@
       <c r="E13">
         <v>20</v>
       </c>
-      <c r="F13" s="3">
+      <c r="F13" s="2">
         <v>0.39215686274509803</v>
       </c>
-      <c r="G13">
+      <c r="G13" s="2">
         <f t="shared" si="1"/>
         <v>3204.424506661589</v>
       </c>
-      <c r="H13" s="3">
+      <c r="H13" s="2">
         <f t="shared" si="0"/>
         <v>40856.412459935258</v>
       </c>
-      <c r="I13" s="3">
-        <v>2.5770740420062532</v>
+      <c r="I13" s="2">
+        <v>2.82</v>
       </c>
       <c r="J13">
-        <v>1.32</v>
-      </c>
-      <c r="K13" s="4">
-        <v>2.6115464552150924</v>
-      </c>
-      <c r="L13" s="1">
+        <v>1.2</v>
+      </c>
+      <c r="K13" s="2">
+        <v>2.8540000000000001</v>
+      </c>
+      <c r="L13" s="2">
         <v>16.198365881174333</v>
       </c>
       <c r="M13">
         <v>10.11</v>
       </c>
       <c r="N13">
-        <v>105.29</v>
-      </c>
-      <c r="O13">
-        <v>37.75</v>
-      </c>
-      <c r="P13" s="2">
-        <v>2.5430463576158938E-4</v>
-      </c>
-      <c r="Q13" s="1">
-        <v>1.0172185430463575E-3</v>
-      </c>
-      <c r="R13">
-        <v>0.25</v>
+        <v>115.22</v>
+      </c>
+      <c r="O13" s="4">
+        <v>9.8028000000000004E-4</v>
+      </c>
+      <c r="P13" s="3">
+        <v>2.3864000000000001E-4</v>
+      </c>
+      <c r="Q13">
+        <v>39.17</v>
+      </c>
+      <c r="R13" s="2">
+        <v>0.24340000000000001</v>
       </c>
       <c r="S13">
-        <v>15.1</v>
-      </c>
-      <c r="T13" s="3">
+        <v>16.97</v>
+      </c>
+      <c r="T13" s="2">
         <f t="shared" si="2"/>
         <v>0.52359877559829882</v>
       </c>
@@ -1974,10 +1978,10 @@
         <v>38.4</v>
       </c>
       <c r="V13">
-        <v>5.31</v>
+        <v>11.309999999999999</v>
       </c>
       <c r="W13">
-        <v>33.97</v>
+        <v>33.06</v>
       </c>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.2">
@@ -1996,51 +2000,51 @@
       <c r="E14">
         <v>25</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="2">
         <v>0.49019607843137253</v>
       </c>
-      <c r="G14">
+      <c r="G14" s="2">
         <f t="shared" si="1"/>
         <v>4005.5306333269859</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="2">
         <f t="shared" si="0"/>
         <v>51070.515574919074</v>
       </c>
-      <c r="I14" s="3">
-        <v>2.4276238178587541</v>
+      <c r="I14" s="2">
+        <v>2.87</v>
       </c>
       <c r="J14">
-        <v>1.6</v>
-      </c>
-      <c r="K14" s="4">
-        <v>2.4670973758727177</v>
-      </c>
-      <c r="L14" s="1">
+        <v>0.78</v>
+      </c>
+      <c r="K14" s="2">
+        <v>2.8929999999999998</v>
+      </c>
+      <c r="L14" s="2">
         <v>19.70721071596877</v>
       </c>
       <c r="M14">
         <v>9.84</v>
       </c>
       <c r="N14">
-        <v>123.98</v>
-      </c>
-      <c r="O14">
-        <v>37.75</v>
-      </c>
-      <c r="P14" s="2">
-        <v>2.7218543046357617E-4</v>
-      </c>
-      <c r="Q14" s="1">
-        <v>1.0887417218543047E-3</v>
-      </c>
-      <c r="R14">
-        <v>0.25</v>
+        <v>146.57</v>
+      </c>
+      <c r="O14" s="4">
+        <v>1.05532E-3</v>
+      </c>
+      <c r="P14" s="3">
+        <v>2.6224000000000001E-4</v>
+      </c>
+      <c r="Q14">
+        <v>38.950000000000003</v>
+      </c>
+      <c r="R14" s="2">
+        <v>0.2485</v>
       </c>
       <c r="S14">
-        <v>15.1</v>
-      </c>
-      <c r="T14" s="3">
+        <v>16.87</v>
+      </c>
+      <c r="T14" s="2">
         <f t="shared" si="2"/>
         <v>0.52359877559829882</v>
       </c>
@@ -2048,10 +2052,10 @@
         <v>41.1</v>
       </c>
       <c r="V14">
-        <v>5.31</v>
+        <v>11.309999999999999</v>
       </c>
       <c r="W14">
-        <v>33.97</v>
+        <v>33.06</v>
       </c>
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.2">
@@ -2070,51 +2074,51 @@
       <c r="E15">
         <v>27</v>
       </c>
-      <c r="F15" s="3">
+      <c r="F15" s="2">
         <v>0.52941176470588236</v>
       </c>
-      <c r="G15">
+      <c r="G15" s="2">
         <f t="shared" si="1"/>
         <v>4325.9730839931453</v>
       </c>
-      <c r="H15" s="3">
+      <c r="H15" s="2">
         <f t="shared" si="0"/>
         <v>55156.156820912598</v>
       </c>
-      <c r="I15" s="3">
-        <v>2.4816812462920113</v>
+      <c r="I15" s="2">
+        <v>2.8</v>
       </c>
       <c r="J15">
-        <v>1.52</v>
-      </c>
-      <c r="K15" s="4">
-        <v>2.5199850185743413</v>
-      </c>
-      <c r="L15" s="1">
+        <v>1.19</v>
+      </c>
+      <c r="K15" s="2">
+        <v>2.8340000000000001</v>
+      </c>
+      <c r="L15" s="2">
         <v>20.78630066858706</v>
       </c>
       <c r="M15">
         <v>9.61</v>
       </c>
       <c r="N15">
-        <v>136.88</v>
-      </c>
-      <c r="O15">
-        <v>37.75</v>
-      </c>
-      <c r="P15" s="2">
-        <v>2.6291390728476824E-4</v>
-      </c>
-      <c r="Q15" s="1">
-        <v>1.051655629139073E-3</v>
-      </c>
-      <c r="R15">
-        <v>0.25</v>
+        <v>154.44</v>
+      </c>
+      <c r="O15" s="4">
+        <v>1.02804E-3</v>
+      </c>
+      <c r="P15" s="3">
+        <v>2.5405000000000002E-4</v>
+      </c>
+      <c r="Q15">
+        <v>38.619999999999997</v>
+      </c>
+      <c r="R15" s="2">
+        <v>0.24709999999999999</v>
       </c>
       <c r="S15">
-        <v>15.1</v>
-      </c>
-      <c r="T15" s="3">
+        <v>16.73</v>
+      </c>
+      <c r="T15" s="2">
         <f t="shared" si="2"/>
         <v>0.52359877559829882</v>
       </c>
@@ -2122,10 +2126,10 @@
         <v>39.700000000000003</v>
       </c>
       <c r="V15">
-        <v>5.31</v>
+        <v>11.309999999999999</v>
       </c>
       <c r="W15">
-        <v>33.97</v>
+        <v>33.06</v>
       </c>
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.2">
@@ -2144,51 +2148,51 @@
       <c r="E16">
         <v>22</v>
       </c>
-      <c r="F16" s="3">
+      <c r="F16" s="2">
         <v>0.43137254901960786</v>
       </c>
-      <c r="G16">
+      <c r="G16" s="2">
         <f t="shared" si="1"/>
         <v>3524.866957327748</v>
       </c>
-      <c r="H16" s="3">
+      <c r="H16" s="2">
         <f t="shared" si="0"/>
         <v>44942.053705928782</v>
       </c>
-      <c r="I16" s="3">
-        <v>2.610917622229632</v>
+      <c r="I16" s="2">
+        <v>2.77</v>
       </c>
       <c r="J16">
-        <v>1.22</v>
-      </c>
-      <c r="K16" s="4">
-        <v>2.643164225784199</v>
-      </c>
-      <c r="L16" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="K16" s="2">
+        <v>2.8119999999999998</v>
+      </c>
+      <c r="L16" s="2">
         <v>17.518588777918907</v>
       </c>
       <c r="M16">
         <v>9.94</v>
       </c>
       <c r="N16">
-        <v>117.34</v>
-      </c>
-      <c r="O16">
-        <v>37.75</v>
-      </c>
-      <c r="P16" s="2">
-        <v>2.3973509933774838E-4</v>
-      </c>
-      <c r="Q16" s="1">
-        <v>9.589403973509935E-4</v>
-      </c>
-      <c r="R16">
-        <v>0.25</v>
+        <v>124.49</v>
+      </c>
+      <c r="O16" s="4">
+        <v>9.3725999999999998E-4</v>
+      </c>
+      <c r="P16" s="3">
+        <v>2.2673999999999999E-4</v>
+      </c>
+      <c r="Q16">
+        <v>38.619999999999997</v>
+      </c>
+      <c r="R16" s="2">
+        <v>0.2419</v>
       </c>
       <c r="S16">
-        <v>15.1</v>
-      </c>
-      <c r="T16" s="3">
+        <v>16.739999999999998</v>
+      </c>
+      <c r="T16" s="2">
         <f t="shared" si="2"/>
         <v>0.52359877559829882</v>
       </c>
@@ -2196,10 +2200,10 @@
         <v>36.200000000000003</v>
       </c>
       <c r="V16">
-        <v>5.31</v>
+        <v>11.309999999999999</v>
       </c>
       <c r="W16">
-        <v>33.97</v>
+        <v>33.06</v>
       </c>
     </row>
     <row r="17" spans="1:23" x14ac:dyDescent="0.2">
@@ -2218,51 +2222,51 @@
       <c r="E17">
         <v>22</v>
       </c>
-      <c r="F17" s="3">
+      <c r="F17" s="2">
         <v>0.43137254901960786</v>
       </c>
-      <c r="G17">
+      <c r="G17" s="2">
         <f t="shared" si="1"/>
         <v>3524.866957327748</v>
       </c>
-      <c r="H17" s="3">
+      <c r="H17" s="2">
         <f t="shared" si="0"/>
         <v>44942.053705928782</v>
       </c>
-      <c r="I17" s="3">
-        <v>2.7114915752931901</v>
+      <c r="I17" s="2">
+        <v>2.85</v>
       </c>
       <c r="J17">
-        <v>0.88</v>
-      </c>
-      <c r="K17" s="4">
-        <v>2.7355645432740014</v>
-      </c>
-      <c r="L17" s="1">
+        <v>1.07</v>
+      </c>
+      <c r="K17" s="2">
+        <v>2.8809999999999998</v>
+      </c>
+      <c r="L17" s="2">
         <v>15.9676473166947</v>
       </c>
       <c r="M17">
         <v>9.06</v>
       </c>
       <c r="N17">
-        <v>121.86</v>
-      </c>
-      <c r="O17">
-        <v>37.75</v>
-      </c>
-      <c r="P17" s="2">
-        <v>2.9668874172185427E-4</v>
-      </c>
-      <c r="Q17" s="1">
-        <v>1.1867549668874171E-3</v>
-      </c>
-      <c r="R17">
-        <v>0.25</v>
+        <v>128.08000000000001</v>
+      </c>
+      <c r="O17" s="4">
+        <v>1.0437599999999999E-3</v>
+      </c>
+      <c r="P17" s="3">
+        <v>2.3362E-4</v>
+      </c>
+      <c r="Q17">
+        <v>42.92</v>
+      </c>
+      <c r="R17" s="2">
+        <v>0.2238</v>
       </c>
       <c r="S17">
-        <v>15.1</v>
-      </c>
-      <c r="T17" s="3">
+        <v>18.670000000000002</v>
+      </c>
+      <c r="T17" s="2">
         <f t="shared" si="2"/>
         <v>0.78539816339744828</v>
       </c>
@@ -2270,10 +2274,10 @@
         <v>44.8</v>
       </c>
       <c r="V17">
-        <v>5.31</v>
+        <v>11.68</v>
       </c>
       <c r="W17">
-        <v>33.97</v>
+        <v>34.950000000000003</v>
       </c>
     </row>
     <row r="18" spans="1:23" x14ac:dyDescent="0.2">
@@ -2292,51 +2296,51 @@
       <c r="E18">
         <v>23</v>
       </c>
-      <c r="F18" s="3">
+      <c r="F18" s="2">
         <v>0.45098039215686275</v>
       </c>
-      <c r="G18">
+      <c r="G18" s="2">
         <f t="shared" si="1"/>
         <v>3685.0881826608274</v>
       </c>
-      <c r="H18" s="3">
+      <c r="H18" s="2">
         <f t="shared" si="0"/>
         <v>46984.874328925551</v>
       </c>
-      <c r="I18" s="3">
-        <v>2.440998334849068</v>
+      <c r="I18" s="2">
+        <v>2.74</v>
       </c>
       <c r="J18">
-        <v>1.32</v>
-      </c>
-      <c r="K18" s="4">
-        <v>2.473650521735983</v>
-      </c>
-      <c r="L18" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="K18" s="2">
+        <v>2.782</v>
+      </c>
+      <c r="L18" s="2">
         <v>15.956431830921384</v>
       </c>
       <c r="M18">
         <v>8.66</v>
       </c>
       <c r="N18">
-        <v>114.69</v>
-      </c>
-      <c r="O18">
-        <v>45.99</v>
-      </c>
-      <c r="P18" s="2">
-        <v>1.463818221352468E-4</v>
-      </c>
-      <c r="Q18" s="1">
-        <v>6.3644270493585565E-4</v>
-      </c>
-      <c r="R18">
-        <v>0.23</v>
+        <v>128.74</v>
+      </c>
+      <c r="O18" s="4">
+        <v>8.1987E-4</v>
+      </c>
+      <c r="P18" s="3">
+        <v>1.9309000000000001E-4</v>
+      </c>
+      <c r="Q18">
+        <v>35.700000000000003</v>
+      </c>
+      <c r="R18" s="2">
+        <v>0.23549999999999999</v>
       </c>
       <c r="S18">
-        <v>18.7</v>
-      </c>
-      <c r="T18" s="3">
+        <v>15.53</v>
+      </c>
+      <c r="T18" s="2">
         <f t="shared" si="2"/>
         <v>0.78539816339744828</v>
       </c>
@@ -2344,10 +2348,10 @@
         <v>29.27</v>
       </c>
       <c r="V18">
-        <v>4.09</v>
+        <v>11.68</v>
       </c>
       <c r="W18">
-        <v>33.97</v>
+        <v>34.950000000000003</v>
       </c>
     </row>
     <row r="19" spans="1:23" x14ac:dyDescent="0.2">
@@ -2366,51 +2370,51 @@
       <c r="E19">
         <v>23</v>
       </c>
-      <c r="F19" s="3">
+      <c r="F19" s="2">
         <v>0.45098039215686275</v>
       </c>
-      <c r="G19">
+      <c r="G19" s="2">
         <f t="shared" si="1"/>
         <v>3685.0881826608274</v>
       </c>
-      <c r="H19" s="3">
+      <c r="H19" s="2">
         <f t="shared" si="0"/>
         <v>46984.874328925551</v>
       </c>
-      <c r="I19" s="3">
-        <v>2.440998334849068</v>
+      <c r="I19" s="2">
+        <v>2.89</v>
       </c>
       <c r="J19">
-        <v>1.62</v>
-      </c>
-      <c r="K19" s="4">
-        <v>2.481193672340992</v>
-      </c>
-      <c r="L19" s="1">
+        <v>0.88</v>
+      </c>
+      <c r="K19" s="2">
+        <v>2.9159999999999999</v>
+      </c>
+      <c r="L19" s="2">
         <v>17.006681962979719</v>
       </c>
       <c r="M19">
         <v>9.23</v>
       </c>
       <c r="N19">
-        <v>114.69</v>
-      </c>
-      <c r="O19">
-        <v>45.99</v>
-      </c>
-      <c r="P19" s="2">
-        <v>2.1404653185475104E-4</v>
-      </c>
-      <c r="Q19" s="1">
-        <v>9.306370950206566E-4</v>
-      </c>
-      <c r="R19">
-        <v>0.23</v>
+        <v>135.79</v>
+      </c>
+      <c r="O19" s="4">
+        <v>1.0848399999999999E-3</v>
+      </c>
+      <c r="P19" s="3">
+        <v>2.5987999999999999E-4</v>
+      </c>
+      <c r="Q19">
+        <v>39.450000000000003</v>
+      </c>
+      <c r="R19" s="2">
+        <v>0.23960000000000001</v>
       </c>
       <c r="S19">
-        <v>18.7</v>
-      </c>
-      <c r="T19" s="3">
+        <v>17.16</v>
+      </c>
+      <c r="T19" s="2">
         <f t="shared" si="2"/>
         <v>0.78539816339744828</v>
       </c>
@@ -2418,15 +2422,15 @@
         <v>42.8</v>
       </c>
       <c r="V19">
-        <v>4.09</v>
+        <v>11.68</v>
       </c>
       <c r="W19">
-        <v>33.97</v>
+        <v>34.950000000000003</v>
       </c>
     </row>
     <row r="20" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A20">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="B20" t="s">
         <v>23</v>
@@ -2440,51 +2444,51 @@
       <c r="E20">
         <v>20</v>
       </c>
-      <c r="F20" s="3">
+      <c r="F20" s="2">
         <v>0.39215686274509803</v>
       </c>
-      <c r="G20">
+      <c r="G20" s="2">
         <f>(PI()*D20*E20)</f>
         <v>3204.424506661589</v>
       </c>
-      <c r="H20" s="3">
+      <c r="H20" s="2">
         <f>((PI()*D20^2)*E20)/4</f>
         <v>40856.412459935258</v>
       </c>
-      <c r="I20" s="3">
-        <v>2.6879501499964547</v>
+      <c r="I20" s="2">
+        <v>2.95</v>
       </c>
       <c r="J20">
-        <v>1.1100000000000001</v>
-      </c>
-      <c r="K20" s="4">
-        <v>2.718121296386343</v>
-      </c>
-      <c r="L20" s="1">
+        <v>0.49</v>
+      </c>
+      <c r="K20" s="2">
+        <v>2.9649999999999999</v>
+      </c>
+      <c r="L20" s="2">
         <v>15.44532612210886</v>
       </c>
       <c r="M20">
         <v>9.64</v>
       </c>
       <c r="N20">
-        <v>109.82</v>
-      </c>
-      <c r="O20">
-        <v>36.869999999999997</v>
-      </c>
-      <c r="P20" s="2">
-        <v>4.4708435042039598E-4</v>
-      </c>
-      <c r="Q20" s="1">
-        <v>1.7195551939245999E-3</v>
-      </c>
-      <c r="R20">
-        <v>0.26</v>
+        <v>120.53</v>
+      </c>
+      <c r="O20" s="4">
+        <v>1.3065500000000001E-3</v>
+      </c>
+      <c r="P20" s="3">
+        <v>2.9515999999999999E-4</v>
+      </c>
+      <c r="Q20">
+        <v>48.52</v>
+      </c>
+      <c r="R20" s="2">
+        <v>0.22589999999999999</v>
       </c>
       <c r="S20">
-        <v>14.63</v>
-      </c>
-      <c r="T20" s="3">
+        <v>21.1</v>
+      </c>
+      <c r="T20" s="2">
         <f>RADIANS(C20)</f>
         <v>0.78539816339744828</v>
       </c>
@@ -2492,15 +2496,15 @@
         <v>63.4</v>
       </c>
       <c r="V20">
-        <v>9.2200000000000006</v>
+        <v>11.68</v>
       </c>
       <c r="W20">
-        <v>37.89</v>
+        <v>34.950000000000003</v>
       </c>
     </row>
     <row r="21" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A21">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B21" t="s">
         <v>23</v>
@@ -2514,51 +2518,51 @@
       <c r="E21">
         <v>21</v>
       </c>
-      <c r="F21" s="3">
+      <c r="F21" s="2">
         <v>0.41176470588235292</v>
       </c>
-      <c r="G21">
+      <c r="G21" s="2">
         <f t="shared" si="1"/>
         <v>3364.6457319946685</v>
       </c>
-      <c r="H21" s="3">
+      <c r="H21" s="2">
         <f t="shared" si="0"/>
         <v>42899.23308293202</v>
       </c>
-      <c r="I21" s="3">
-        <v>2.8287218973217625</v>
+      <c r="I21" s="2">
+        <v>2.78</v>
       </c>
       <c r="J21">
-        <v>0.71</v>
-      </c>
-      <c r="K21" s="4">
-        <v>2.8489494383339333</v>
-      </c>
-      <c r="L21" s="1">
+        <v>1.22</v>
+      </c>
+      <c r="K21" s="2">
+        <v>2.8140000000000001</v>
+      </c>
+      <c r="L21" s="2">
         <v>13.374466784678807</v>
       </c>
       <c r="M21">
         <v>7.95</v>
       </c>
       <c r="N21">
-        <v>121.35</v>
-      </c>
-      <c r="O21">
-        <v>44.03</v>
-      </c>
-      <c r="P21" s="2">
-        <v>2.2440381558028614E-4</v>
-      </c>
-      <c r="Q21" s="1">
-        <v>1.0685895980013626E-3</v>
-      </c>
-      <c r="R21">
-        <v>0.21</v>
+        <v>119.26</v>
+      </c>
+      <c r="O21" s="4">
+        <v>1.03561E-3</v>
+      </c>
+      <c r="P21" s="3">
+        <v>2.2662E-4</v>
+      </c>
+      <c r="Q21">
+        <v>45.43</v>
+      </c>
+      <c r="R21" s="2">
+        <v>0.21879999999999999</v>
       </c>
       <c r="S21">
-        <v>18.190000000000001</v>
-      </c>
-      <c r="T21" s="3">
+        <v>19.489999999999998</v>
+      </c>
+      <c r="T21" s="2">
         <f t="shared" si="2"/>
         <v>1.0471975511965976</v>
       </c>
@@ -2566,15 +2570,15 @@
         <v>47.05</v>
       </c>
       <c r="V21">
-        <v>3.27</v>
+        <v>10.27</v>
       </c>
       <c r="W21">
-        <v>33.97</v>
+        <v>35.49</v>
       </c>
     </row>
     <row r="22" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A22">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B22" t="s">
         <v>23</v>
@@ -2588,51 +2592,51 @@
       <c r="E22">
         <v>22</v>
       </c>
-      <c r="F22" s="3">
+      <c r="F22" s="2">
         <v>0.43137254901960786</v>
       </c>
-      <c r="G22">
+      <c r="G22" s="2">
         <f t="shared" si="1"/>
         <v>3524.866957327748</v>
       </c>
-      <c r="H22" s="3">
+      <c r="H22" s="2">
         <f t="shared" si="0"/>
         <v>44942.053705928782</v>
       </c>
-      <c r="I22" s="3">
-        <v>2.7141616802417805</v>
+      <c r="I22" s="2">
+        <v>2.84</v>
       </c>
       <c r="J22">
-        <v>0.84</v>
-      </c>
-      <c r="K22" s="4">
-        <v>2.7371537719259584</v>
-      </c>
-      <c r="L22" s="1">
+        <v>1.21</v>
+      </c>
+      <c r="K22" s="2">
+        <v>2.875</v>
+      </c>
+      <c r="L22" s="2">
         <v>14.152340833670907</v>
       </c>
       <c r="M22">
         <v>8.0299999999999994</v>
       </c>
       <c r="N22">
-        <v>121.98</v>
-      </c>
-      <c r="O22">
-        <v>44.03</v>
-      </c>
-      <c r="P22" s="2">
-        <v>2.3179650238473769E-4</v>
-      </c>
-      <c r="Q22" s="1">
-        <v>1.1037928684987509E-3</v>
-      </c>
-      <c r="R22">
-        <v>0.21</v>
+        <v>127.64</v>
+      </c>
+      <c r="O22" s="4">
+        <v>1.0798100000000001E-3</v>
+      </c>
+      <c r="P22" s="3">
+        <v>2.4111E-4</v>
+      </c>
+      <c r="Q22">
+        <v>45.01</v>
+      </c>
+      <c r="R22" s="2">
+        <v>0.2233</v>
       </c>
       <c r="S22">
-        <v>18.190000000000001</v>
-      </c>
-      <c r="T22" s="3">
+        <v>19.309999999999999</v>
+      </c>
+      <c r="T22" s="2">
         <f t="shared" si="2"/>
         <v>1.0471975511965976</v>
       </c>
@@ -2640,15 +2644,15 @@
         <v>48.6</v>
       </c>
       <c r="V22">
-        <v>3.27</v>
+        <v>10.27</v>
       </c>
       <c r="W22">
-        <v>33.97</v>
+        <v>35.49</v>
       </c>
     </row>
     <row r="23" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A23">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B23" t="s">
         <v>23</v>
@@ -2662,51 +2666,51 @@
       <c r="E23">
         <v>21</v>
       </c>
-      <c r="F23" s="3">
+      <c r="F23" s="2">
         <v>0.41176470588235292</v>
       </c>
-      <c r="G23">
+      <c r="G23" s="2">
         <f t="shared" si="1"/>
         <v>3364.6457319946685</v>
       </c>
-      <c r="H23" s="3">
+      <c r="H23" s="2">
         <f t="shared" si="0"/>
         <v>42899.23308293202</v>
       </c>
-      <c r="I23" s="3">
-        <v>2.8287218973217625</v>
+      <c r="I23" s="2">
+        <v>2.72</v>
       </c>
       <c r="J23">
-        <v>0.67</v>
-      </c>
-      <c r="K23" s="4">
-        <v>2.847802171873314</v>
-      </c>
-      <c r="L23" s="1">
+        <v>1.77</v>
+      </c>
+      <c r="K23" s="2">
+        <v>2.7690000000000001</v>
+      </c>
+      <c r="L23" s="2">
         <v>13.038002211479341</v>
       </c>
       <c r="M23">
         <v>7.75</v>
       </c>
       <c r="N23">
-        <v>121.35</v>
-      </c>
-      <c r="O23">
-        <v>44.03</v>
-      </c>
-      <c r="P23" s="2">
-        <v>2.4419713831478539E-4</v>
-      </c>
-      <c r="Q23" s="1">
-        <v>1.1628435157846923E-3</v>
-      </c>
-      <c r="R23">
-        <v>0.21</v>
+        <v>116.69</v>
+      </c>
+      <c r="O23" s="4">
+        <v>1.09252E-3</v>
+      </c>
+      <c r="P23" s="3">
+        <v>2.3709999999999999E-4</v>
+      </c>
+      <c r="Q23">
+        <v>46.86</v>
+      </c>
+      <c r="R23" s="2">
+        <v>0.217</v>
       </c>
       <c r="S23">
-        <v>18.190000000000001</v>
-      </c>
-      <c r="T23" s="3">
+        <v>20.100000000000001</v>
+      </c>
+      <c r="T23" s="2">
         <f t="shared" si="2"/>
         <v>1.0471975511965976</v>
       </c>
@@ -2714,15 +2718,15 @@
         <v>51.2</v>
       </c>
       <c r="V23">
-        <v>3.27</v>
+        <v>10.27</v>
       </c>
       <c r="W23">
-        <v>33.97</v>
+        <v>35.49</v>
       </c>
     </row>
     <row r="24" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A24">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B24" t="s">
         <v>23</v>
@@ -2736,51 +2740,51 @@
       <c r="E24">
         <v>25</v>
       </c>
-      <c r="F24" s="3">
+      <c r="F24" s="2">
         <v>0.49019607843137253</v>
       </c>
-      <c r="G24">
+      <c r="G24" s="2">
         <f t="shared" si="1"/>
         <v>4005.5306333269859</v>
       </c>
-      <c r="H24" s="3">
+      <c r="H24" s="2">
         <f t="shared" si="0"/>
         <v>51070.515574919074</v>
       </c>
-      <c r="I24" s="3">
-        <v>2.7638256322855552</v>
+      <c r="I24" s="2">
+        <v>2.88</v>
       </c>
       <c r="J24">
-        <v>0.64</v>
-      </c>
-      <c r="K24" s="4">
-        <v>2.7816280518171852</v>
-      </c>
-      <c r="L24" s="1">
+        <v>0.84</v>
+      </c>
+      <c r="K24" s="2">
+        <v>2.9039999999999999</v>
+      </c>
+      <c r="L24" s="2">
         <v>14.880546302809753</v>
       </c>
       <c r="M24">
         <v>7.43</v>
       </c>
       <c r="N24">
-        <v>141.15</v>
-      </c>
-      <c r="O24">
-        <v>43.25</v>
-      </c>
-      <c r="P24" s="2">
-        <v>4.3362543352601157E-4</v>
-      </c>
-      <c r="Q24" s="1">
-        <v>1.4952601156069366E-3</v>
-      </c>
-      <c r="R24">
-        <v>0.28999999999999998</v>
+        <v>147.08000000000001</v>
+      </c>
+      <c r="O24" s="4">
+        <v>1.2379800000000001E-3</v>
+      </c>
+      <c r="P24" s="3">
+        <v>2.5406000000000002E-4</v>
+      </c>
+      <c r="Q24">
+        <v>52.24</v>
+      </c>
+      <c r="R24" s="2">
+        <v>0.20519999999999999</v>
       </c>
       <c r="S24">
-        <v>16.760000000000002</v>
-      </c>
-      <c r="T24" s="3">
+        <v>21.86</v>
+      </c>
+      <c r="T24" s="2">
         <f t="shared" si="2"/>
         <v>1.3089969389957472</v>
       </c>
@@ -2788,15 +2792,15 @@
         <v>64.67</v>
       </c>
       <c r="V24">
-        <v>10.76</v>
+        <v>15.66</v>
       </c>
       <c r="W24">
-        <v>36.65</v>
+        <v>36.54</v>
       </c>
     </row>
     <row r="25" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A25">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B25" t="s">
         <v>23</v>
@@ -2810,51 +2814,51 @@
       <c r="E25">
         <v>23.5</v>
       </c>
-      <c r="F25" s="3">
+      <c r="F25" s="2">
         <v>0.46078431372549017</v>
       </c>
-      <c r="G25">
+      <c r="G25" s="2">
         <f t="shared" si="1"/>
         <v>3765.198795327367</v>
       </c>
-      <c r="H25" s="3">
+      <c r="H25" s="2">
         <f t="shared" si="0"/>
         <v>48006.284640423932</v>
       </c>
-      <c r="I25" s="3">
-        <v>2.4694683391552106</v>
+      <c r="I25" s="2">
+        <v>2.81</v>
       </c>
       <c r="J25">
-        <v>1.39</v>
-      </c>
-      <c r="K25" s="4">
-        <v>2.5042778005833188</v>
-      </c>
-      <c r="L25" s="1">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="K25" s="2">
+        <v>2.8420000000000001</v>
+      </c>
+      <c r="L25" s="2">
         <v>15.399663072888931</v>
       </c>
       <c r="M25">
         <v>8.18</v>
       </c>
       <c r="N25">
-        <v>118.55</v>
-      </c>
-      <c r="O25">
-        <v>43.25</v>
-      </c>
-      <c r="P25" s="2">
-        <v>3.9493641618497106E-4</v>
-      </c>
-      <c r="Q25" s="1">
-        <v>1.3618497109826589E-3</v>
-      </c>
-      <c r="R25">
-        <v>0.28999999999999998</v>
+        <v>134.9</v>
+      </c>
+      <c r="O25" s="4">
+        <v>1.2654999999999999E-3</v>
+      </c>
+      <c r="P25" s="3">
+        <v>2.876E-4</v>
+      </c>
+      <c r="Q25">
+        <v>46.54</v>
+      </c>
+      <c r="R25" s="2">
+        <v>0.2273</v>
       </c>
       <c r="S25">
-        <v>16.760000000000002</v>
-      </c>
-      <c r="T25" s="3">
+        <v>19.48</v>
+      </c>
+      <c r="T25" s="2">
         <f t="shared" si="2"/>
         <v>1.3089969389957472</v>
       </c>
@@ -2862,15 +2866,15 @@
         <v>58.9</v>
       </c>
       <c r="V25">
-        <v>10.76</v>
+        <v>15.66</v>
       </c>
       <c r="W25">
-        <v>36.65</v>
+        <v>36.54</v>
       </c>
     </row>
     <row r="26" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A26">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B26" t="s">
         <v>23</v>
@@ -2884,51 +2888,51 @@
       <c r="E26">
         <v>22</v>
       </c>
-      <c r="F26" s="3">
+      <c r="F26" s="2">
         <v>0.43137254901960786</v>
       </c>
-      <c r="G26">
+      <c r="G26" s="2">
         <f t="shared" si="1"/>
         <v>3524.866957327748</v>
       </c>
-      <c r="H26" s="3">
+      <c r="H26" s="2">
         <f t="shared" si="0"/>
         <v>44942.053705928782</v>
       </c>
-      <c r="I26" s="3">
-        <v>2.7397501859991014</v>
+      <c r="I26" s="2">
+        <v>2.76</v>
       </c>
       <c r="J26">
-        <v>0.87</v>
-      </c>
-      <c r="K26" s="4">
-        <v>2.7637952042763052</v>
-      </c>
-      <c r="L26" s="1">
+        <v>1.66</v>
+      </c>
+      <c r="K26" s="2">
+        <v>2.8069999999999999</v>
+      </c>
+      <c r="L26" s="2">
         <v>13.782229803151495</v>
       </c>
       <c r="M26">
         <v>7.82</v>
       </c>
       <c r="N26">
-        <v>123.13</v>
-      </c>
-      <c r="O26">
-        <v>43.25</v>
-      </c>
-      <c r="P26" s="2">
-        <v>4.1639306358381501E-4</v>
-      </c>
-      <c r="Q26" s="1">
-        <v>1.4358381502890174E-3</v>
-      </c>
-      <c r="R26">
-        <v>0.28999999999999998</v>
+        <v>124.04</v>
+      </c>
+      <c r="O26" s="4">
+        <v>1.2285099999999999E-3</v>
+      </c>
+      <c r="P26" s="3">
+        <v>2.6019999999999998E-4</v>
+      </c>
+      <c r="Q26">
+        <v>50.55</v>
+      </c>
+      <c r="R26" s="2">
+        <v>0.21179999999999999</v>
       </c>
       <c r="S26">
-        <v>16.760000000000002</v>
-      </c>
-      <c r="T26" s="3">
+        <v>21.16</v>
+      </c>
+      <c r="T26" s="2">
         <f t="shared" si="2"/>
         <v>1.3089969389957472</v>
       </c>
@@ -2936,15 +2940,15 @@
         <v>62.1</v>
       </c>
       <c r="V26">
-        <v>10.76</v>
+        <v>15.66</v>
       </c>
       <c r="W26">
-        <v>36.65</v>
+        <v>36.54</v>
       </c>
     </row>
     <row r="27" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A27">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B27" t="s">
         <v>23</v>
@@ -2958,51 +2962,51 @@
       <c r="E27">
         <v>25</v>
       </c>
-      <c r="F27" s="3">
+      <c r="F27" s="2">
         <v>0.49019607843137253</v>
       </c>
-      <c r="G27">
+      <c r="G27" s="2">
         <f t="shared" si="1"/>
         <v>4005.5306333269859</v>
       </c>
-      <c r="H27" s="3">
+      <c r="H27" s="2">
         <f t="shared" si="0"/>
         <v>51070.515574919074</v>
       </c>
-      <c r="I27" s="3">
-        <v>2.7638256322855552</v>
+      <c r="I27" s="2">
+        <v>2.93</v>
       </c>
       <c r="J27">
-        <v>0.63</v>
-      </c>
-      <c r="K27" s="4">
-        <v>2.7813481254760544</v>
-      </c>
-      <c r="L27" s="1">
+        <v>0.59</v>
+      </c>
+      <c r="K27" s="2">
+        <v>2.9470000000000001</v>
+      </c>
+      <c r="L27" s="2">
         <v>14.199606095144166</v>
       </c>
       <c r="M27">
         <v>7.09</v>
       </c>
       <c r="N27">
-        <v>141.15</v>
-      </c>
-      <c r="O27">
-        <v>43.25</v>
-      </c>
-      <c r="P27" s="2">
-        <v>4.003005780346821E-4</v>
-      </c>
-      <c r="Q27" s="1">
-        <v>1.3803468208092487E-3</v>
-      </c>
-      <c r="R27">
-        <v>0.28999999999999998</v>
+        <v>149.63999999999999</v>
+      </c>
+      <c r="O27" s="4">
+        <v>1.18115E-3</v>
+      </c>
+      <c r="P27" s="3">
+        <v>2.4264999999999999E-4</v>
+      </c>
+      <c r="Q27">
+        <v>50.54</v>
+      </c>
+      <c r="R27" s="2">
+        <v>0.2054</v>
       </c>
       <c r="S27">
-        <v>16.760000000000002</v>
-      </c>
-      <c r="T27" s="3">
+        <v>21.15</v>
+      </c>
+      <c r="T27" s="2">
         <f t="shared" si="2"/>
         <v>1.3089969389957472</v>
       </c>
@@ -3010,10 +3014,10 @@
         <v>59.7</v>
       </c>
       <c r="V27">
-        <v>10.76</v>
+        <v>15.66</v>
       </c>
       <c r="W27">
-        <v>36.65</v>
+        <v>36.54</v>
       </c>
     </row>
     <row r="28" spans="1:23" x14ac:dyDescent="0.2">
@@ -3032,51 +3036,51 @@
       <c r="E28">
         <v>20</v>
       </c>
-      <c r="F28" s="3">
+      <c r="F28" s="2">
         <v>0.39215686274509803</v>
       </c>
-      <c r="G28">
+      <c r="G28" s="2">
         <f t="shared" si="1"/>
         <v>3204.424506661589</v>
       </c>
-      <c r="H28" s="3">
+      <c r="H28" s="2">
         <f t="shared" si="0"/>
         <v>40856.412459935258</v>
       </c>
-      <c r="I28" s="3">
-        <v>2.7812035653259621</v>
+      <c r="I28" s="2">
+        <v>2.79</v>
       </c>
       <c r="J28">
-        <v>0.85</v>
-      </c>
-      <c r="K28" s="4">
-        <v>2.805046460237985</v>
-      </c>
-      <c r="L28" s="1">
+        <v>1.2</v>
+      </c>
+      <c r="K28" s="2">
+        <v>2.8239999999999998</v>
+      </c>
+      <c r="L28" s="2">
         <v>12.737587413979815</v>
       </c>
       <c r="M28">
         <v>7.95</v>
       </c>
       <c r="N28">
-        <v>113.63</v>
-      </c>
-      <c r="O28">
-        <v>51.85</v>
-      </c>
-      <c r="P28" s="2">
-        <v>2.4888138862102219E-4</v>
-      </c>
-      <c r="Q28" s="1">
-        <v>1.1851494696239152E-3</v>
-      </c>
-      <c r="R28">
-        <v>0.21</v>
+        <v>113.99</v>
+      </c>
+      <c r="O28" s="4">
+        <v>1.1902499999999999E-3</v>
+      </c>
+      <c r="P28" s="3">
+        <v>2.4363999999999999E-4</v>
+      </c>
+      <c r="Q28">
+        <v>51.63</v>
+      </c>
+      <c r="R28" s="2">
+        <v>0.20469999999999999</v>
       </c>
       <c r="S28">
-        <v>21.43</v>
-      </c>
-      <c r="T28" s="3">
+        <v>21.33</v>
+      </c>
+      <c r="T28" s="2">
         <f t="shared" si="2"/>
         <v>1.5707963267948966</v>
       </c>
@@ -3084,10 +3088,10 @@
         <v>61.45</v>
       </c>
       <c r="V28">
-        <v>10.76</v>
+        <v>16.86</v>
       </c>
       <c r="W28">
-        <v>36.65</v>
+        <v>36.76</v>
       </c>
     </row>
     <row r="29" spans="1:23" x14ac:dyDescent="0.2">
@@ -3106,51 +3110,51 @@
       <c r="E29">
         <v>21</v>
       </c>
-      <c r="F29" s="3">
+      <c r="F29" s="2">
         <v>0.41176470588235292</v>
       </c>
-      <c r="G29">
+      <c r="G29" s="2">
         <f t="shared" si="1"/>
         <v>3364.6457319946685</v>
       </c>
-      <c r="H29" s="3">
+      <c r="H29" s="2">
         <f t="shared" si="0"/>
         <v>42899.23308293202</v>
       </c>
-      <c r="I29" s="3">
-        <v>2.3133280683165367</v>
+      <c r="I29" s="2">
+        <v>2.86</v>
       </c>
       <c r="J29">
-        <v>1.8</v>
-      </c>
-      <c r="K29" s="4">
-        <v>2.355731230464905</v>
-      </c>
-      <c r="L29" s="1">
+        <v>0.85</v>
+      </c>
+      <c r="K29" s="2">
+        <v>2.8849999999999998</v>
+      </c>
+      <c r="L29" s="2">
         <v>13.340820327358861</v>
       </c>
       <c r="M29">
         <v>7.93</v>
       </c>
       <c r="N29">
-        <v>99.24</v>
-      </c>
-      <c r="O29">
-        <v>51.85</v>
-      </c>
-      <c r="P29" s="2">
-        <v>2.7459980713596911E-4</v>
-      </c>
-      <c r="Q29" s="1">
-        <v>1.3076181292189005E-3</v>
-      </c>
-      <c r="R29">
-        <v>0.21</v>
+        <v>122.69</v>
+      </c>
+      <c r="O29" s="4">
+        <v>1.4166999999999999E-3</v>
+      </c>
+      <c r="P29" s="3">
+        <v>3.2142999999999999E-4</v>
+      </c>
+      <c r="Q29">
+        <v>47.86</v>
+      </c>
+      <c r="R29" s="2">
+        <v>0.22689999999999999</v>
       </c>
       <c r="S29">
-        <v>21.43</v>
-      </c>
-      <c r="T29" s="3">
+        <v>19.78</v>
+      </c>
+      <c r="T29" s="2">
         <f t="shared" si="2"/>
         <v>1.5707963267948966</v>
       </c>
@@ -3158,10 +3162,10 @@
         <v>67.8</v>
       </c>
       <c r="V29">
-        <v>10.76</v>
+        <v>16.86</v>
       </c>
       <c r="W29">
-        <v>36.65</v>
+        <v>36.76</v>
       </c>
     </row>
     <row r="30" spans="1:23" x14ac:dyDescent="0.2">
@@ -3180,51 +3184,51 @@
       <c r="E30">
         <v>20</v>
       </c>
-      <c r="F30" s="3">
+      <c r="F30" s="2">
         <v>0.39215686274509803</v>
       </c>
-      <c r="G30">
+      <c r="G30" s="2">
         <f t="shared" si="1"/>
         <v>3204.424506661589</v>
       </c>
-      <c r="H30" s="3">
+      <c r="H30" s="2">
         <f t="shared" si="0"/>
         <v>40856.412459935258</v>
       </c>
-      <c r="I30" s="3">
-        <v>2.6167251004928151</v>
+      <c r="I30" s="2">
+        <v>2.74</v>
       </c>
       <c r="J30">
-        <v>1.06</v>
-      </c>
-      <c r="K30" s="4">
-        <v>2.6447595517412728</v>
-      </c>
-      <c r="L30" s="1">
+        <v>1.73</v>
+      </c>
+      <c r="K30" s="2">
+        <v>2.7879999999999998</v>
+      </c>
+      <c r="L30" s="2">
         <v>13.634826275845061</v>
       </c>
       <c r="M30">
         <v>8.51</v>
       </c>
       <c r="N30">
-        <v>106.91</v>
-      </c>
-      <c r="O30">
-        <v>51.85</v>
-      </c>
-      <c r="P30" s="2">
-        <v>2.8837029893924785E-4</v>
-      </c>
-      <c r="Q30" s="1">
-        <v>1.3731918997107041E-3</v>
-      </c>
-      <c r="R30">
-        <v>0.21</v>
+        <v>111.95</v>
+      </c>
+      <c r="O30" s="4">
+        <v>1.3313999999999999E-3</v>
+      </c>
+      <c r="P30" s="3">
+        <v>2.7836000000000001E-4</v>
+      </c>
+      <c r="Q30">
+        <v>53.48</v>
+      </c>
+      <c r="R30" s="2">
+        <v>0.20910000000000001</v>
       </c>
       <c r="S30">
-        <v>21.43</v>
-      </c>
-      <c r="T30" s="3">
+        <v>22.1</v>
+      </c>
+      <c r="T30" s="2">
         <f t="shared" si="2"/>
         <v>1.5707963267948966</v>
       </c>
@@ -3232,10 +3236,10 @@
         <v>71.2</v>
       </c>
       <c r="V30">
-        <v>10.76</v>
+        <v>16.86</v>
       </c>
       <c r="W30">
-        <v>36.65</v>
+        <v>36.76</v>
       </c>
     </row>
     <row r="31" spans="1:23" x14ac:dyDescent="0.2">
@@ -3254,51 +3258,51 @@
       <c r="E31">
         <v>20</v>
       </c>
-      <c r="F31" s="3">
+      <c r="F31" s="2">
         <v>0.39215686274509803</v>
       </c>
-      <c r="G31">
+      <c r="G31" s="2">
         <f t="shared" si="1"/>
         <v>3204.424506661589</v>
       </c>
-      <c r="H31" s="3">
+      <c r="H31" s="2">
         <f t="shared" si="0"/>
         <v>40856.412459935258</v>
       </c>
-      <c r="I31" s="3">
-        <v>2.7812035653259621</v>
+      <c r="I31" s="2">
+        <v>2.82</v>
       </c>
       <c r="J31">
-        <v>0.64</v>
-      </c>
-      <c r="K31" s="4">
-        <v>2.7991179200140519</v>
-      </c>
-      <c r="L31" s="1">
+        <v>1.24</v>
+      </c>
+      <c r="K31" s="2">
+        <v>2.855</v>
+      </c>
+      <c r="L31" s="2">
         <v>12.192835247847347</v>
       </c>
       <c r="M31">
         <v>7.61</v>
       </c>
       <c r="N31">
-        <v>113.63</v>
-      </c>
-      <c r="O31">
-        <v>51.85</v>
-      </c>
-      <c r="P31" s="2">
-        <v>2.810800385728062E-4</v>
-      </c>
-      <c r="Q31" s="1">
-        <v>1.33847637415622E-3</v>
-      </c>
-      <c r="R31">
-        <v>0.21</v>
+        <v>115.22</v>
+      </c>
+      <c r="O31" s="4">
+        <v>1.27487E-3</v>
+      </c>
+      <c r="P31" s="3">
+        <v>2.5415000000000002E-4</v>
+      </c>
+      <c r="Q31">
+        <v>54.44</v>
+      </c>
+      <c r="R31" s="2">
+        <v>0.19939999999999999</v>
       </c>
       <c r="S31">
-        <v>21.43</v>
-      </c>
-      <c r="T31" s="3">
+        <v>22.49</v>
+      </c>
+      <c r="T31" s="2">
         <f t="shared" si="2"/>
         <v>1.5707963267948966</v>
       </c>
@@ -3306,10 +3310,10 @@
         <v>69.400000000000006</v>
       </c>
       <c r="V31">
-        <v>10.76</v>
+        <v>16.86</v>
       </c>
       <c r="W31">
-        <v>36.65</v>
+        <v>36.76</v>
       </c>
     </row>
     <row r="32" spans="1:23" x14ac:dyDescent="0.2">
@@ -3328,51 +3332,51 @@
       <c r="E32">
         <v>23</v>
       </c>
-      <c r="F32" s="3">
+      <c r="F32" s="2">
         <v>0.45098039215686275</v>
       </c>
-      <c r="G32">
+      <c r="G32" s="2">
         <f t="shared" si="1"/>
         <v>3685.0881826608274</v>
       </c>
-      <c r="H32" s="3">
+      <c r="H32" s="2">
         <f t="shared" si="0"/>
         <v>46984.874328925551</v>
       </c>
-      <c r="I32" s="3">
-        <v>2.7957933670396167</v>
+      <c r="I32" s="2">
+        <v>2.71</v>
       </c>
       <c r="J32">
-        <v>1.01</v>
-      </c>
-      <c r="K32" s="4">
-        <v>2.824318988826767</v>
-      </c>
-      <c r="L32" s="1">
+        <v>1.99</v>
+      </c>
+      <c r="K32" s="2">
+        <v>2.7650000000000001</v>
+      </c>
+      <c r="L32" s="2">
         <v>16.675024026540246</v>
       </c>
       <c r="M32">
         <v>9.0500000000000007</v>
       </c>
       <c r="N32">
-        <v>131.36000000000001</v>
-      </c>
-      <c r="O32">
-        <v>32.71</v>
-      </c>
-      <c r="P32" s="2">
-        <v>2.4653011311525529E-4</v>
-      </c>
-      <c r="Q32" s="1">
-        <v>1.2326505655762764E-3</v>
-      </c>
-      <c r="R32">
-        <v>0.2</v>
+        <v>127.33</v>
+      </c>
+      <c r="O32" s="4">
+        <v>1.29688E-3</v>
+      </c>
+      <c r="P32" s="3">
+        <v>2.7092000000000001E-4</v>
+      </c>
+      <c r="Q32">
+        <v>31.09</v>
+      </c>
+      <c r="R32" s="2">
+        <v>0.2089</v>
       </c>
       <c r="S32">
-        <v>13.63</v>
-      </c>
-      <c r="T32" s="3">
+        <v>6.42</v>
+      </c>
+      <c r="T32" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -3380,10 +3384,10 @@
         <v>40.32</v>
       </c>
       <c r="V32">
-        <v>5.94</v>
+        <v>11.940000000000001</v>
       </c>
       <c r="W32">
-        <v>28.03</v>
+        <v>28.09</v>
       </c>
     </row>
     <row r="33" spans="1:23" x14ac:dyDescent="0.2">
@@ -3402,51 +3406,51 @@
       <c r="E33">
         <v>22</v>
       </c>
-      <c r="F33" s="3">
+      <c r="F33" s="2">
         <v>0.43137254901960786</v>
       </c>
-      <c r="G33">
+      <c r="G33" s="2">
         <f t="shared" si="1"/>
         <v>3524.866957327748</v>
       </c>
-      <c r="H33" s="3">
+      <c r="H33" s="2">
         <f t="shared" si="0"/>
         <v>44942.053705928782</v>
       </c>
-      <c r="I33" s="3">
-        <v>3.0283440291925419</v>
+      <c r="I33" s="2">
+        <v>2.76</v>
       </c>
       <c r="J33">
-        <v>0.73</v>
-      </c>
-      <c r="K33" s="4">
-        <v>3.0506135077994778</v>
-      </c>
-      <c r="L33" s="1">
+        <v>1.58</v>
+      </c>
+      <c r="K33" s="2">
+        <v>2.8039999999999998</v>
+      </c>
+      <c r="L33" s="2">
         <v>18.170689165024541</v>
       </c>
       <c r="M33">
         <v>10.31</v>
       </c>
       <c r="N33">
-        <v>136.1</v>
-      </c>
-      <c r="O33">
-        <v>32.71</v>
-      </c>
-      <c r="P33" s="2">
-        <v>2.4824212778966679E-4</v>
-      </c>
-      <c r="Q33" s="1">
-        <v>1.2412106389483339E-3</v>
-      </c>
-      <c r="R33">
-        <v>0.2</v>
+        <v>124.04</v>
+      </c>
+      <c r="O33" s="4">
+        <v>1.21959E-3</v>
+      </c>
+      <c r="P33" s="3">
+        <v>2.4282000000000001E-4</v>
+      </c>
+      <c r="Q33">
+        <v>33.29</v>
+      </c>
+      <c r="R33" s="2">
+        <v>0.1991</v>
       </c>
       <c r="S33">
-        <v>13.63</v>
-      </c>
-      <c r="T33" s="3">
+        <v>6.88</v>
+      </c>
+      <c r="T33" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -3454,10 +3458,10 @@
         <v>40.6</v>
       </c>
       <c r="V33">
-        <v>5.94</v>
+        <v>11.940000000000001</v>
       </c>
       <c r="W33">
-        <v>28.03</v>
+        <v>28.09</v>
       </c>
     </row>
     <row r="34" spans="1:23" x14ac:dyDescent="0.2">
@@ -3476,51 +3480,51 @@
       <c r="E34">
         <v>22</v>
       </c>
-      <c r="F34" s="3">
+      <c r="F34" s="2">
         <v>0.43137254901960786</v>
       </c>
-      <c r="G34">
+      <c r="G34" s="2">
         <f t="shared" si="1"/>
         <v>3524.866957327748</v>
       </c>
-      <c r="H34" s="3">
+      <c r="H34" s="2">
         <f t="shared" ref="H34:H53" si="3">((PI()*D34^2)*E34)/4</f>
         <v>44942.053705928782</v>
       </c>
-      <c r="I34" s="3">
-        <v>3.0283440291925419</v>
+      <c r="I34" s="2">
+        <v>2.68</v>
       </c>
       <c r="J34">
-        <v>0.51</v>
-      </c>
-      <c r="K34" s="4">
-        <v>3.0438677547417248</v>
-      </c>
-      <c r="L34" s="1">
+        <v>2.11</v>
+      </c>
+      <c r="K34" s="2">
+        <v>2.738</v>
+      </c>
+      <c r="L34" s="2">
         <v>16.478753025507221</v>
       </c>
       <c r="M34">
         <v>9.35</v>
       </c>
       <c r="N34">
-        <v>136.1</v>
-      </c>
-      <c r="O34">
-        <v>32.71</v>
-      </c>
-      <c r="P34" s="2">
-        <v>2.4824212778966679E-4</v>
-      </c>
-      <c r="Q34" s="1">
-        <v>1.2412106389483339E-3</v>
-      </c>
-      <c r="R34">
-        <v>0.2</v>
+        <v>120.44</v>
+      </c>
+      <c r="O34" s="4">
+        <v>1.20261E-3</v>
+      </c>
+      <c r="P34" s="3">
+        <v>2.309E-4</v>
+      </c>
+      <c r="Q34">
+        <v>33.76</v>
+      </c>
+      <c r="R34" s="2">
+        <v>0.192</v>
       </c>
       <c r="S34">
-        <v>13.63</v>
-      </c>
-      <c r="T34" s="3">
+        <v>6.98</v>
+      </c>
+      <c r="T34" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -3528,10 +3532,10 @@
         <v>40.6</v>
       </c>
       <c r="V34">
-        <v>5.94</v>
+        <v>11.940000000000001</v>
       </c>
       <c r="W34">
-        <v>28.03</v>
+        <v>28.09</v>
       </c>
     </row>
     <row r="35" spans="1:23" x14ac:dyDescent="0.2">
@@ -3550,51 +3554,51 @@
       <c r="E35">
         <v>21</v>
       </c>
-      <c r="F35" s="3">
+      <c r="F35" s="2">
         <v>0.41176470588235292</v>
       </c>
-      <c r="G35">
+      <c r="G35" s="2">
         <f t="shared" si="1"/>
         <v>3364.6457319946685</v>
       </c>
-      <c r="H35" s="3">
+      <c r="H35" s="2">
         <f t="shared" si="3"/>
         <v>42899.23308293202</v>
       </c>
-      <c r="I35" s="3">
-        <v>2.6977172243679242</v>
+      <c r="I35" s="2">
+        <v>2.73</v>
       </c>
       <c r="J35">
-        <v>1.08</v>
-      </c>
-      <c r="K35" s="4">
-        <v>2.7271706675777643</v>
-      </c>
-      <c r="L35" s="1">
+        <v>1.91</v>
+      </c>
+      <c r="K35" s="2">
+        <v>2.7829999999999999</v>
+      </c>
+      <c r="L35" s="2">
         <v>15.477370367175475</v>
       </c>
       <c r="M35">
         <v>9.1999999999999993</v>
       </c>
       <c r="N35">
-        <v>115.73</v>
-      </c>
-      <c r="O35">
-        <v>25.24</v>
-      </c>
-      <c r="P35" s="2">
-        <v>2.9117274167987319E-4</v>
-      </c>
-      <c r="Q35" s="1">
-        <v>1.5324881141045958E-3</v>
-      </c>
-      <c r="R35">
-        <v>0.19</v>
+        <v>117.11</v>
+      </c>
+      <c r="O35" s="4">
+        <v>1.3397999999999999E-3</v>
+      </c>
+      <c r="P35" s="3">
+        <v>2.2723E-4</v>
+      </c>
+      <c r="Q35">
+        <v>28.87</v>
+      </c>
+      <c r="R35" s="2">
+        <v>0.1696</v>
       </c>
       <c r="S35">
-        <v>10.61</v>
-      </c>
-      <c r="T35" s="3">
+        <v>7.08</v>
+      </c>
+      <c r="T35" s="2">
         <f t="shared" si="2"/>
         <v>0.26179938779914941</v>
       </c>
@@ -3602,10 +3606,10 @@
         <v>38.68</v>
       </c>
       <c r="V35">
-        <v>5.94</v>
+        <v>11.61</v>
       </c>
       <c r="W35">
-        <v>28.03</v>
+        <v>28.36</v>
       </c>
     </row>
     <row r="36" spans="1:23" x14ac:dyDescent="0.2">
@@ -3624,51 +3628,51 @@
       <c r="E36">
         <v>24</v>
       </c>
-      <c r="F36" s="3">
+      <c r="F36" s="2">
         <v>0.47058823529411764</v>
       </c>
-      <c r="G36">
+      <c r="G36" s="2">
         <f t="shared" si="1"/>
         <v>3845.3094079939065</v>
       </c>
-      <c r="H36" s="3">
+      <c r="H36" s="2">
         <f t="shared" si="3"/>
         <v>49027.694951922313</v>
       </c>
-      <c r="I36" s="3">
-        <v>2.6793019767462991</v>
+      <c r="I36" s="2">
+        <v>2.79</v>
       </c>
       <c r="J36">
-        <v>1.32</v>
-      </c>
-      <c r="K36" s="4">
-        <v>2.7151418491551471</v>
-      </c>
-      <c r="L36" s="1">
+        <v>1.21</v>
+      </c>
+      <c r="K36" s="2">
+        <v>2.8239999999999998</v>
+      </c>
+      <c r="L36" s="2">
         <v>15.092839426376083</v>
       </c>
       <c r="M36">
         <v>7.85</v>
       </c>
       <c r="N36">
-        <v>131.36000000000001</v>
-      </c>
-      <c r="O36">
-        <v>25.24</v>
-      </c>
-      <c r="P36" s="2">
-        <v>3.3046751188589541E-4</v>
-      </c>
-      <c r="Q36" s="1">
-        <v>1.7393026941362915E-3</v>
-      </c>
-      <c r="R36">
-        <v>0.19</v>
+        <v>136.79</v>
+      </c>
+      <c r="O36" s="4">
+        <v>1.51746E-3</v>
+      </c>
+      <c r="P36" s="3">
+        <v>2.6267E-4</v>
+      </c>
+      <c r="Q36">
+        <v>28.93</v>
+      </c>
+      <c r="R36" s="2">
+        <v>0.1731</v>
       </c>
       <c r="S36">
-        <v>10.61</v>
-      </c>
-      <c r="T36" s="3">
+        <v>7.09</v>
+      </c>
+      <c r="T36" s="2">
         <f t="shared" si="2"/>
         <v>0.26179938779914941</v>
       </c>
@@ -3676,10 +3680,10 @@
         <v>43.9</v>
       </c>
       <c r="V36">
-        <v>5.94</v>
+        <v>11.61</v>
       </c>
       <c r="W36">
-        <v>28.03</v>
+        <v>28.36</v>
       </c>
     </row>
     <row r="37" spans="1:23" x14ac:dyDescent="0.2">
@@ -3698,51 +3702,51 @@
       <c r="E37">
         <v>23</v>
       </c>
-      <c r="F37" s="3">
+      <c r="F37" s="2">
         <v>0.45098039215686275</v>
       </c>
-      <c r="G37">
+      <c r="G37" s="2">
         <f t="shared" si="1"/>
         <v>3685.0881826608274</v>
       </c>
-      <c r="H37" s="3">
+      <c r="H37" s="2">
         <f t="shared" si="3"/>
         <v>46984.874328925551</v>
       </c>
-      <c r="I37" s="3">
-        <v>2.463133117901148</v>
+      <c r="I37" s="2">
+        <v>2.7</v>
       </c>
       <c r="J37">
-        <v>1.43</v>
-      </c>
-      <c r="K37" s="4">
-        <v>2.4988669147825382</v>
-      </c>
-      <c r="L37" s="1">
+        <v>1.97</v>
+      </c>
+      <c r="K37" s="2">
+        <v>2.754</v>
+      </c>
+      <c r="L37" s="2">
         <v>15.219414194389218</v>
       </c>
       <c r="M37">
         <v>8.26</v>
       </c>
       <c r="N37">
-        <v>115.73</v>
-      </c>
-      <c r="O37">
-        <v>25.24</v>
-      </c>
-      <c r="P37" s="2">
-        <v>2.883122028526149E-4</v>
-      </c>
-      <c r="Q37" s="1">
-        <v>1.5174326465927099E-3</v>
-      </c>
-      <c r="R37">
-        <v>0.19</v>
+        <v>126.86</v>
+      </c>
+      <c r="O37" s="4">
+        <v>1.4039600000000001E-3</v>
+      </c>
+      <c r="P37" s="3">
+        <v>2.4766000000000002E-4</v>
+      </c>
+      <c r="Q37">
+        <v>27.28</v>
+      </c>
+      <c r="R37" s="2">
+        <v>0.1764</v>
       </c>
       <c r="S37">
-        <v>10.61</v>
-      </c>
-      <c r="T37" s="3">
+        <v>6.69</v>
+      </c>
+      <c r="T37" s="2">
         <f t="shared" si="2"/>
         <v>0.26179938779914941</v>
       </c>
@@ -3750,10 +3754,10 @@
         <v>38.299999999999997</v>
       </c>
       <c r="V37">
-        <v>5.94</v>
+        <v>11.61</v>
       </c>
       <c r="W37">
-        <v>28.03</v>
+        <v>28.36</v>
       </c>
     </row>
     <row r="38" spans="1:23" x14ac:dyDescent="0.2">
@@ -3772,51 +3776,51 @@
       <c r="E38">
         <v>23</v>
       </c>
-      <c r="F38" s="3">
+      <c r="F38" s="2">
         <v>0.45098039215686275</v>
       </c>
-      <c r="G38">
+      <c r="G38" s="2">
         <f t="shared" si="1"/>
         <v>3685.0881826608274</v>
       </c>
-      <c r="H38" s="3">
+      <c r="H38" s="2">
         <f t="shared" si="3"/>
         <v>46984.874328925551</v>
       </c>
-      <c r="I38" s="3">
-        <v>2.6133942413123821</v>
+      <c r="I38" s="2">
+        <v>2.74</v>
       </c>
       <c r="J38">
-        <v>1.3</v>
-      </c>
-      <c r="K38" s="4">
-        <v>2.6478158473276414</v>
-      </c>
-      <c r="L38" s="1">
+        <v>1.77</v>
+      </c>
+      <c r="K38" s="2">
+        <v>2.7890000000000001</v>
+      </c>
+      <c r="L38" s="2">
         <v>14.353418471463923</v>
       </c>
       <c r="M38">
         <v>7.79</v>
       </c>
       <c r="N38">
-        <v>122.79</v>
-      </c>
-      <c r="O38">
-        <v>25.28</v>
-      </c>
-      <c r="P38" s="2">
-        <v>1.7572784810126582E-4</v>
-      </c>
-      <c r="Q38" s="1">
-        <v>9.7626582278481015E-4</v>
-      </c>
-      <c r="R38">
-        <v>0.18</v>
+        <v>128.74</v>
+      </c>
+      <c r="O38" s="4">
+        <v>1.1741200000000001E-3</v>
+      </c>
+      <c r="P38" s="3">
+        <v>1.6061999999999999E-4</v>
+      </c>
+      <c r="Q38">
+        <v>21.02</v>
+      </c>
+      <c r="R38" s="2">
+        <v>0.1368</v>
       </c>
       <c r="S38">
-        <v>10.71</v>
-      </c>
-      <c r="T38" s="3">
+        <v>7.13</v>
+      </c>
+      <c r="T38" s="2">
         <f t="shared" si="2"/>
         <v>0.52359877559829882</v>
       </c>
@@ -3824,10 +3828,10 @@
         <v>24.68</v>
       </c>
       <c r="V38">
-        <v>3.08</v>
+        <v>9.08</v>
       </c>
       <c r="W38">
-        <v>24.01</v>
+        <v>23.78</v>
       </c>
     </row>
     <row r="39" spans="1:23" x14ac:dyDescent="0.2">
@@ -3846,51 +3850,51 @@
       <c r="E39">
         <v>23</v>
       </c>
-      <c r="F39" s="3">
+      <c r="F39" s="2">
         <v>0.45098039215686275</v>
       </c>
-      <c r="G39">
+      <c r="G39" s="2">
         <f t="shared" si="1"/>
         <v>3685.0881826608274</v>
       </c>
-      <c r="H39" s="3">
+      <c r="H39" s="2">
         <f t="shared" si="3"/>
         <v>46984.874328925551</v>
       </c>
-      <c r="I39" s="3">
-        <v>2.6133942413123821</v>
+      <c r="I39" s="2">
+        <v>2.82</v>
       </c>
       <c r="J39">
-        <v>1.42</v>
-      </c>
-      <c r="K39" s="4">
-        <v>2.6510389950419779</v>
-      </c>
-      <c r="L39" s="1">
+        <v>1.08</v>
+      </c>
+      <c r="K39" s="2">
+        <v>2.851</v>
+      </c>
+      <c r="L39" s="2">
         <v>15.827453744528253</v>
       </c>
       <c r="M39">
         <v>8.59</v>
       </c>
       <c r="N39">
-        <v>122.79</v>
-      </c>
-      <c r="O39">
-        <v>25.28</v>
-      </c>
-      <c r="P39" s="2">
-        <v>2.4849683544303795E-4</v>
-      </c>
-      <c r="Q39" s="1">
-        <v>1.3805379746835442E-3</v>
-      </c>
-      <c r="R39">
-        <v>0.18</v>
+        <v>132.5</v>
+      </c>
+      <c r="O39" s="4">
+        <v>1.4559900000000001E-3</v>
+      </c>
+      <c r="P39" s="3">
+        <v>1.9933E-4</v>
+      </c>
+      <c r="Q39">
+        <v>23.97</v>
+      </c>
+      <c r="R39" s="2">
+        <v>0.13689999999999999</v>
       </c>
       <c r="S39">
-        <v>10.71</v>
-      </c>
-      <c r="T39" s="3">
+        <v>8.1300000000000008</v>
+      </c>
+      <c r="T39" s="2">
         <f t="shared" si="2"/>
         <v>0.52359877559829882</v>
       </c>
@@ -3898,10 +3902,10 @@
         <v>34.9</v>
       </c>
       <c r="V39">
-        <v>3.08</v>
+        <v>9.08</v>
       </c>
       <c r="W39">
-        <v>24.01</v>
+        <v>23.78</v>
       </c>
     </row>
     <row r="40" spans="1:23" x14ac:dyDescent="0.2">
@@ -3920,51 +3924,51 @@
       <c r="E40">
         <v>22</v>
       </c>
-      <c r="F40" s="3">
+      <c r="F40" s="2">
         <v>0.43137254901960786</v>
       </c>
-      <c r="G40">
+      <c r="G40" s="2">
         <f t="shared" si="1"/>
         <v>3524.866957327748</v>
       </c>
-      <c r="H40" s="3">
+      <c r="H40" s="2">
         <f t="shared" si="3"/>
         <v>44942.053705928782</v>
       </c>
-      <c r="I40" s="3">
-        <v>2.7364125548133642</v>
+      <c r="I40" s="2">
+        <v>2.69</v>
       </c>
       <c r="J40">
-        <v>0.95</v>
-      </c>
-      <c r="K40" s="4">
-        <v>2.7626578039508978</v>
-      </c>
-      <c r="L40" s="1">
+        <v>2.17</v>
+      </c>
+      <c r="K40" s="2">
+        <v>2.75</v>
+      </c>
+      <c r="L40" s="2">
         <v>13.99372182059116</v>
       </c>
       <c r="M40">
         <v>7.94</v>
       </c>
       <c r="N40">
-        <v>122.98</v>
-      </c>
-      <c r="O40">
-        <v>25.28</v>
-      </c>
-      <c r="P40" s="2">
-        <v>1.7444620253164556E-4</v>
-      </c>
-      <c r="Q40" s="1">
-        <v>9.6914556962025313E-4</v>
-      </c>
-      <c r="R40">
-        <v>0.18</v>
+        <v>120.89</v>
+      </c>
+      <c r="O40" s="4">
+        <v>1.12695E-3</v>
+      </c>
+      <c r="P40" s="3">
+        <v>1.4797000000000001E-4</v>
+      </c>
+      <c r="Q40">
+        <v>21.74</v>
+      </c>
+      <c r="R40" s="2">
+        <v>0.1313</v>
       </c>
       <c r="S40">
-        <v>10.71</v>
-      </c>
-      <c r="T40" s="3">
+        <v>7.39</v>
+      </c>
+      <c r="T40" s="2">
         <f t="shared" si="2"/>
         <v>0.52359877559829882</v>
       </c>
@@ -3972,10 +3976,10 @@
         <v>24.5</v>
       </c>
       <c r="V40">
-        <v>3.08</v>
+        <v>9.08</v>
       </c>
       <c r="W40">
-        <v>24.01</v>
+        <v>23.78</v>
       </c>
     </row>
     <row r="41" spans="1:23" x14ac:dyDescent="0.2">
@@ -3994,51 +3998,51 @@
       <c r="E41">
         <v>23</v>
       </c>
-      <c r="F41" s="3">
+      <c r="F41" s="2">
         <v>0.45098039215686275</v>
       </c>
-      <c r="G41">
+      <c r="G41" s="2">
         <f t="shared" si="1"/>
         <v>3685.0881826608274</v>
       </c>
-      <c r="H41" s="3">
+      <c r="H41" s="2">
         <f t="shared" si="3"/>
         <v>46984.874328925551</v>
       </c>
-      <c r="I41" s="3">
-        <v>2.7583345034130198</v>
+      <c r="I41" s="2">
+        <v>2.77</v>
       </c>
       <c r="J41">
-        <v>1.07</v>
-      </c>
-      <c r="K41" s="4">
-        <v>2.7881678999424038</v>
-      </c>
-      <c r="L41" s="1">
+        <v>1.44</v>
+      </c>
+      <c r="K41" s="2">
+        <v>2.81</v>
+      </c>
+      <c r="L41" s="2">
         <v>13.376870103058804</v>
       </c>
       <c r="M41">
         <v>7.26</v>
       </c>
       <c r="N41">
-        <v>129.6</v>
-      </c>
-      <c r="O41">
-        <v>19.670000000000002</v>
-      </c>
-      <c r="P41" s="2">
-        <v>2.1952211489578038E-4</v>
-      </c>
-      <c r="Q41" s="1">
-        <v>1.2913065582104727E-3</v>
-      </c>
-      <c r="R41">
-        <v>0.17</v>
+        <v>130.15</v>
+      </c>
+      <c r="O41" s="4">
+        <v>1.29262E-3</v>
+      </c>
+      <c r="P41" s="3">
+        <v>1.5447E-4</v>
+      </c>
+      <c r="Q41">
+        <v>19.649999999999999</v>
+      </c>
+      <c r="R41" s="2">
+        <v>0.1195</v>
       </c>
       <c r="S41">
-        <v>8.41</v>
-      </c>
-      <c r="T41" s="3">
+        <v>8.5299999999999994</v>
+      </c>
+      <c r="T41" s="2">
         <f t="shared" si="2"/>
         <v>0.78539816339744828</v>
       </c>
@@ -4046,10 +4050,10 @@
         <v>25.4</v>
       </c>
       <c r="V41">
-        <v>2.29</v>
+        <v>8.2899999999999991</v>
       </c>
       <c r="W41">
-        <v>24.01</v>
+        <v>24.24</v>
       </c>
     </row>
     <row r="42" spans="1:23" x14ac:dyDescent="0.2">
@@ -4068,51 +4072,51 @@
       <c r="E42">
         <v>21</v>
       </c>
-      <c r="F42" s="3">
+      <c r="F42" s="2">
         <v>0.41176470588235292</v>
       </c>
-      <c r="G42">
+      <c r="G42" s="2">
         <f t="shared" si="1"/>
         <v>3364.6457319946685</v>
       </c>
-      <c r="H42" s="3">
+      <c r="H42" s="2">
         <f t="shared" si="3"/>
         <v>42899.23308293202</v>
       </c>
-      <c r="I42" s="3">
-        <v>2.8016817868900095</v>
+      <c r="I42" s="2">
+        <v>2.72</v>
       </c>
       <c r="J42">
-        <v>0.89</v>
-      </c>
-      <c r="K42" s="4">
-        <v>2.8268406688427095</v>
-      </c>
-      <c r="L42" s="1">
+        <v>1.87</v>
+      </c>
+      <c r="K42" s="2">
+        <v>2.7719999999999998</v>
+      </c>
+      <c r="L42" s="2">
         <v>10.531341141143312</v>
       </c>
       <c r="M42">
         <v>6.26</v>
       </c>
       <c r="N42">
-        <v>120.19</v>
-      </c>
-      <c r="O42">
-        <v>19.670000000000002</v>
-      </c>
-      <c r="P42" s="2">
-        <v>2.2297915607524148E-4</v>
-      </c>
-      <c r="Q42" s="1">
-        <v>1.311642094560244E-3</v>
-      </c>
-      <c r="R42">
-        <v>0.17</v>
+        <v>116.69</v>
+      </c>
+      <c r="O42" s="4">
+        <v>1.31098E-3</v>
+      </c>
+      <c r="P42" s="3">
+        <v>1.526E-4</v>
+      </c>
+      <c r="Q42">
+        <v>19.68</v>
+      </c>
+      <c r="R42" s="2">
+        <v>0.1164</v>
       </c>
       <c r="S42">
-        <v>8.41</v>
-      </c>
-      <c r="T42" s="3">
+        <v>8.57</v>
+      </c>
+      <c r="T42" s="2">
         <f t="shared" si="2"/>
         <v>0.78539816339744828</v>
       </c>
@@ -4120,10 +4124,10 @@
         <v>25.8</v>
       </c>
       <c r="V42">
-        <v>2.29</v>
+        <v>8.2899999999999991</v>
       </c>
       <c r="W42">
-        <v>24.01</v>
+        <v>24.24</v>
       </c>
     </row>
     <row r="43" spans="1:23" x14ac:dyDescent="0.2">
@@ -4142,51 +4146,51 @@
       <c r="E43">
         <v>21</v>
       </c>
-      <c r="F43" s="3">
+      <c r="F43" s="2">
         <v>0.41176470588235292</v>
       </c>
-      <c r="G43">
+      <c r="G43" s="2">
         <f t="shared" si="1"/>
         <v>3364.6457319946685</v>
       </c>
-      <c r="H43" s="3">
+      <c r="H43" s="2">
         <f t="shared" si="3"/>
         <v>42899.23308293202</v>
       </c>
-      <c r="I43" s="3">
-        <v>2.8016817868900095</v>
+      <c r="I43" s="2">
+        <v>2.66</v>
       </c>
       <c r="J43">
-        <v>1.08</v>
-      </c>
-      <c r="K43" s="4">
-        <v>2.8322703061969365</v>
-      </c>
-      <c r="L43" s="1">
+        <v>2.3199999999999998</v>
+      </c>
+      <c r="K43" s="2">
+        <v>2.7229999999999999</v>
+      </c>
+      <c r="L43" s="2">
         <v>11.877199433941179</v>
       </c>
       <c r="M43">
         <v>7.06</v>
       </c>
       <c r="N43">
-        <v>120.19</v>
-      </c>
-      <c r="O43">
-        <v>19.670000000000002</v>
-      </c>
-      <c r="P43" s="2">
-        <v>2.2297915607524148E-4</v>
-      </c>
-      <c r="Q43" s="1">
-        <v>1.311642094560244E-3</v>
-      </c>
-      <c r="R43">
-        <v>0.17</v>
+        <v>114.11</v>
+      </c>
+      <c r="O43" s="4">
+        <v>1.31098E-3</v>
+      </c>
+      <c r="P43" s="3">
+        <v>1.5666000000000001E-4</v>
+      </c>
+      <c r="Q43">
+        <v>19.68</v>
+      </c>
+      <c r="R43" s="2">
+        <v>0.1195</v>
       </c>
       <c r="S43">
-        <v>8.41</v>
-      </c>
-      <c r="T43" s="3">
+        <v>8.5500000000000007</v>
+      </c>
+      <c r="T43" s="2">
         <f t="shared" si="2"/>
         <v>0.78539816339744828</v>
       </c>
@@ -4194,10 +4198,10 @@
         <v>25.8</v>
       </c>
       <c r="V43">
-        <v>2.29</v>
+        <v>8.2899999999999991</v>
       </c>
       <c r="W43">
-        <v>24.01</v>
+        <v>24.24</v>
       </c>
     </row>
     <row r="44" spans="1:23" x14ac:dyDescent="0.2">
@@ -4216,51 +4220,51 @@
       <c r="E44">
         <v>22</v>
       </c>
-      <c r="F44" s="3">
+      <c r="F44" s="2">
         <v>0.43137254901960786</v>
       </c>
-      <c r="G44">
+      <c r="G44" s="2">
         <f t="shared" si="1"/>
         <v>3524.866957327748</v>
       </c>
-      <c r="H44" s="3">
+      <c r="H44" s="2">
         <f t="shared" si="3"/>
         <v>44942.053705928782</v>
       </c>
-      <c r="I44" s="3">
-        <v>2.7275122049847305</v>
+      <c r="I44" s="2">
+        <v>2.75</v>
       </c>
       <c r="J44">
-        <v>1.0900000000000001</v>
-      </c>
-      <c r="K44" s="4">
-        <v>2.7575697148768885</v>
-      </c>
-      <c r="L44" s="1">
+        <v>1.45</v>
+      </c>
+      <c r="K44" s="2">
+        <v>2.79</v>
+      </c>
+      <c r="L44" s="2">
         <v>11.138579585155686</v>
       </c>
       <c r="M44">
         <v>6.32</v>
       </c>
       <c r="N44">
-        <v>122.58</v>
-      </c>
-      <c r="O44">
-        <v>27.17</v>
-      </c>
-      <c r="P44" s="2">
-        <v>2.4373205741626795E-4</v>
-      </c>
-      <c r="Q44" s="1">
-        <v>1.3540669856459331E-3</v>
-      </c>
-      <c r="R44">
-        <v>0.18</v>
+        <v>123.59</v>
+      </c>
+      <c r="O44" s="4">
+        <v>1.7353799999999999E-3</v>
+      </c>
+      <c r="P44" s="3">
+        <v>2.1172000000000001E-4</v>
+      </c>
+      <c r="Q44">
+        <v>21.2</v>
+      </c>
+      <c r="R44" s="2">
+        <v>0.122</v>
       </c>
       <c r="S44">
-        <v>11.51</v>
-      </c>
-      <c r="T44" s="3">
+        <v>10.09</v>
+      </c>
+      <c r="T44" s="2">
         <f t="shared" si="2"/>
         <v>1.0471975511965976</v>
       </c>
@@ -4268,7 +4272,7 @@
         <v>36.79</v>
       </c>
       <c r="V44">
-        <v>3.24</v>
+        <v>9.24</v>
       </c>
       <c r="W44">
         <v>27.81</v>
@@ -4290,51 +4294,51 @@
       <c r="E45">
         <v>23</v>
       </c>
-      <c r="F45" s="3">
+      <c r="F45" s="2">
         <v>0.45098039215686275</v>
       </c>
-      <c r="G45">
+      <c r="G45" s="2">
         <f t="shared" si="1"/>
         <v>3685.0881826608274</v>
       </c>
-      <c r="H45" s="3">
+      <c r="H45" s="2">
         <f t="shared" si="3"/>
         <v>46984.874328925551</v>
       </c>
-      <c r="I45" s="3">
-        <v>2.7583345034130198</v>
+      <c r="I45" s="2">
+        <v>2.8</v>
       </c>
       <c r="J45">
-        <v>0.92</v>
-      </c>
-      <c r="K45" s="4">
-        <v>2.783946814102765</v>
-      </c>
-      <c r="L45" s="1">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="K45" s="2">
+        <v>2.831</v>
+      </c>
+      <c r="L45" s="2">
         <v>10.539352202409965</v>
       </c>
       <c r="M45">
         <v>5.72</v>
       </c>
       <c r="N45">
-        <v>129.6</v>
-      </c>
-      <c r="O45">
-        <v>27.17</v>
-      </c>
-      <c r="P45" s="2">
-        <v>2.4644828855355174E-4</v>
-      </c>
-      <c r="Q45" s="1">
-        <v>1.369157158630843E-3</v>
-      </c>
-      <c r="R45">
-        <v>0.18</v>
+        <v>131.56</v>
+      </c>
+      <c r="O45" s="4">
+        <v>1.7497599999999999E-3</v>
+      </c>
+      <c r="P45" s="3">
+        <v>2.0875000000000001E-4</v>
+      </c>
+      <c r="Q45">
+        <v>21.26</v>
+      </c>
+      <c r="R45" s="2">
+        <v>0.1193</v>
       </c>
       <c r="S45">
-        <v>11.51</v>
-      </c>
-      <c r="T45" s="3">
+        <v>10.15</v>
+      </c>
+      <c r="T45" s="2">
         <f t="shared" si="2"/>
         <v>1.0471975511965976</v>
       </c>
@@ -4342,7 +4346,7 @@
         <v>37.200000000000003</v>
       </c>
       <c r="V45">
-        <v>3.24</v>
+        <v>9.24</v>
       </c>
       <c r="W45">
         <v>27.81</v>
@@ -4364,51 +4368,51 @@
       <c r="E46">
         <v>24</v>
       </c>
-      <c r="F46" s="3">
+      <c r="F46" s="2">
         <v>0.47058823529411764</v>
       </c>
-      <c r="G46">
+      <c r="G46" s="2">
         <f t="shared" si="1"/>
         <v>3845.3094079939065</v>
       </c>
-      <c r="H46" s="3">
+      <c r="H46" s="2">
         <f t="shared" si="3"/>
         <v>49027.694951922313</v>
       </c>
-      <c r="I46" s="3">
-        <v>2.5002195212360028</v>
+      <c r="I46" s="2">
+        <v>2.71</v>
       </c>
       <c r="J46">
-        <v>1.62</v>
-      </c>
-      <c r="K46" s="4">
-        <v>2.5413900398820926</v>
-      </c>
-      <c r="L46" s="1">
+        <v>1.7</v>
+      </c>
+      <c r="K46" s="2">
+        <v>2.7570000000000001</v>
+      </c>
+      <c r="L46" s="2">
         <v>10.882225624622755</v>
       </c>
       <c r="M46">
         <v>5.66</v>
       </c>
       <c r="N46">
-        <v>122.58</v>
-      </c>
-      <c r="O46">
-        <v>27.17</v>
-      </c>
-      <c r="P46" s="2">
-        <v>2.4181082075818916E-4</v>
-      </c>
-      <c r="Q46" s="1">
-        <v>1.3433934486566065E-3</v>
-      </c>
-      <c r="R46">
-        <v>0.18</v>
+        <v>132.87</v>
+      </c>
+      <c r="O46" s="4">
+        <v>1.84717E-3</v>
+      </c>
+      <c r="P46" s="3">
+        <v>2.4143E-4</v>
+      </c>
+      <c r="Q46">
+        <v>19.760000000000002</v>
+      </c>
+      <c r="R46" s="2">
+        <v>0.13070000000000001</v>
       </c>
       <c r="S46">
-        <v>11.51</v>
-      </c>
-      <c r="T46" s="3">
+        <v>9.32</v>
+      </c>
+      <c r="T46" s="2">
         <f t="shared" si="2"/>
         <v>1.0471975511965976</v>
       </c>
@@ -4416,7 +4420,7 @@
         <v>36.5</v>
       </c>
       <c r="V46">
-        <v>3.24</v>
+        <v>9.24</v>
       </c>
       <c r="W46">
         <v>27.81</v>
@@ -4438,51 +4442,51 @@
       <c r="E47">
         <v>24</v>
       </c>
-      <c r="F47" s="3">
+      <c r="F47" s="2">
         <v>0.47058823529411764</v>
       </c>
-      <c r="G47">
+      <c r="G47" s="2">
         <f t="shared" si="1"/>
         <v>3845.3094079939065</v>
       </c>
-      <c r="H47" s="3">
+      <c r="H47" s="2">
         <f t="shared" si="3"/>
         <v>49027.694951922313</v>
       </c>
-      <c r="I47" s="3">
-        <v>2.6362650768457607</v>
+      <c r="I47" s="2">
+        <v>2.78</v>
       </c>
       <c r="J47">
-        <v>1.28</v>
-      </c>
-      <c r="K47" s="4">
-        <v>2.6704467958324156</v>
-      </c>
-      <c r="L47" s="1">
+        <v>1.23</v>
+      </c>
+      <c r="K47" s="2">
+        <v>2.8149999999999999</v>
+      </c>
+      <c r="L47" s="2">
         <v>8.1136028508671423</v>
       </c>
       <c r="M47">
         <v>4.22</v>
       </c>
       <c r="N47">
-        <v>129.25</v>
-      </c>
-      <c r="O47">
-        <v>20.190000000000001</v>
-      </c>
-      <c r="P47" s="2">
-        <v>2.947201584943041E-4</v>
-      </c>
-      <c r="Q47" s="1">
-        <v>1.8420009905894005E-3</v>
-      </c>
-      <c r="R47">
-        <v>0.16</v>
+        <v>136.30000000000001</v>
+      </c>
+      <c r="O47" s="4">
+        <v>1.6368800000000001E-3</v>
+      </c>
+      <c r="P47" s="3">
+        <v>2.6615999999999999E-4</v>
+      </c>
+      <c r="Q47">
+        <v>22.72</v>
+      </c>
+      <c r="R47" s="2">
+        <v>0.16259999999999999</v>
       </c>
       <c r="S47">
-        <v>8.6999999999999993</v>
-      </c>
-      <c r="T47" s="3">
+        <v>10.14</v>
+      </c>
+      <c r="T47" s="2">
         <f t="shared" si="2"/>
         <v>1.3089969389957472</v>
       </c>
@@ -4490,10 +4494,10 @@
         <v>37.19</v>
       </c>
       <c r="V47">
-        <v>6.31</v>
+        <v>12.15</v>
       </c>
       <c r="W47">
-        <v>30.97</v>
+        <v>31.46</v>
       </c>
     </row>
     <row r="48" spans="1:23" x14ac:dyDescent="0.2">
@@ -4512,51 +4516,51 @@
       <c r="E48">
         <v>21</v>
       </c>
-      <c r="F48" s="3">
+      <c r="F48" s="2">
         <v>0.41176470588235292</v>
       </c>
-      <c r="G48">
+      <c r="G48" s="2">
         <f t="shared" si="1"/>
         <v>3364.6457319946685</v>
       </c>
-      <c r="H48" s="3">
+      <c r="H48" s="2">
         <f t="shared" si="3"/>
         <v>42899.23308293202</v>
       </c>
-      <c r="I48" s="3">
-        <v>3.1762805581298998</v>
+      <c r="I48" s="2">
+        <v>2.67</v>
       </c>
       <c r="J48">
-        <v>0.3</v>
-      </c>
-      <c r="K48" s="4">
-        <v>3.1858380723469408</v>
-      </c>
-      <c r="L48" s="1">
+        <v>2.0099999999999998</v>
+      </c>
+      <c r="K48" s="2">
+        <v>2.7250000000000001</v>
+      </c>
+      <c r="L48" s="2">
         <v>6.4769430340897367</v>
       </c>
       <c r="M48">
         <v>3.85</v>
       </c>
       <c r="N48">
-        <v>136.26</v>
-      </c>
-      <c r="O48">
-        <v>20.190000000000001</v>
-      </c>
-      <c r="P48" s="2">
-        <v>3.218226844972759E-4</v>
-      </c>
-      <c r="Q48" s="1">
-        <v>2.0113917781079743E-3</v>
-      </c>
-      <c r="R48">
-        <v>0.16</v>
+        <v>114.54</v>
+      </c>
+      <c r="O48" s="4">
+        <v>1.52268E-3</v>
+      </c>
+      <c r="P48" s="3">
+        <v>2.0038E-4</v>
+      </c>
+      <c r="Q48">
+        <v>26.67</v>
+      </c>
+      <c r="R48" s="2">
+        <v>0.13159999999999999</v>
       </c>
       <c r="S48">
-        <v>8.6999999999999993</v>
-      </c>
-      <c r="T48" s="3">
+        <v>12.26</v>
+      </c>
+      <c r="T48" s="2">
         <f t="shared" si="2"/>
         <v>1.3089969389957472</v>
       </c>
@@ -4564,10 +4568,10 @@
         <v>40.61</v>
       </c>
       <c r="V48">
-        <v>6.31</v>
+        <v>12.15</v>
       </c>
       <c r="W48">
-        <v>30.97</v>
+        <v>31.46</v>
       </c>
     </row>
     <row r="49" spans="1:23" x14ac:dyDescent="0.2">
@@ -4586,51 +4590,51 @@
       <c r="E49">
         <v>22</v>
       </c>
-      <c r="F49" s="3">
+      <c r="F49" s="2">
         <v>0.43137254901960786</v>
       </c>
-      <c r="G49">
+      <c r="G49" s="2">
         <f t="shared" si="1"/>
         <v>3524.866957327748</v>
       </c>
-      <c r="H49" s="3">
+      <c r="H49" s="2">
         <f t="shared" si="3"/>
         <v>44942.053705928782</v>
       </c>
-      <c r="I49" s="3">
-        <v>3.0379119052583232</v>
+      <c r="I49" s="2">
+        <v>2.73</v>
       </c>
       <c r="J49">
-        <v>0.67</v>
-      </c>
-      <c r="K49" s="4">
-        <v>3.0584032067435047</v>
-      </c>
-      <c r="L49" s="1">
+        <v>1.63</v>
+      </c>
+      <c r="K49" s="2">
+        <v>2.7749999999999999</v>
+      </c>
+      <c r="L49" s="2">
         <v>4.8290677315390145</v>
       </c>
       <c r="M49">
         <v>2.74</v>
       </c>
       <c r="N49">
-        <v>136.53</v>
-      </c>
-      <c r="O49">
-        <v>20.190000000000001</v>
-      </c>
-      <c r="P49" s="2">
-        <v>3.0930163447251115E-4</v>
-      </c>
-      <c r="Q49" s="1">
-        <v>1.9331352154531947E-3</v>
-      </c>
-      <c r="R49">
-        <v>0.16</v>
+        <v>122.69</v>
+      </c>
+      <c r="O49" s="4">
+        <v>1.6364800000000001E-3</v>
+      </c>
+      <c r="P49" s="3">
+        <v>2.3418000000000001E-4</v>
+      </c>
+      <c r="Q49">
+        <v>23.85</v>
+      </c>
+      <c r="R49" s="2">
+        <v>0.1431</v>
       </c>
       <c r="S49">
-        <v>8.6999999999999993</v>
-      </c>
-      <c r="T49" s="3">
+        <v>10.84</v>
+      </c>
+      <c r="T49" s="2">
         <f t="shared" si="2"/>
         <v>1.3089969389957472</v>
       </c>
@@ -4638,10 +4642,10 @@
         <v>39.03</v>
       </c>
       <c r="V49">
-        <v>6.31</v>
+        <v>12.15</v>
       </c>
       <c r="W49">
-        <v>30.97</v>
+        <v>31.46</v>
       </c>
     </row>
     <row r="50" spans="1:23" x14ac:dyDescent="0.2">
@@ -4660,51 +4664,51 @@
       <c r="E50">
         <v>21</v>
       </c>
-      <c r="F50" s="3">
+      <c r="F50" s="2">
         <v>0.41176470588235292</v>
       </c>
-      <c r="G50">
+      <c r="G50" s="2">
         <f t="shared" si="1"/>
         <v>3364.6457319946685</v>
       </c>
-      <c r="H50" s="3">
+      <c r="H50" s="2">
         <f t="shared" si="3"/>
         <v>42899.23308293202</v>
       </c>
-      <c r="I50" s="3">
-        <v>3.0128743735380126</v>
+      <c r="I50" s="2">
+        <v>2.85</v>
       </c>
       <c r="J50">
-        <v>0.71</v>
-      </c>
-      <c r="K50" s="4">
-        <v>3.0344187466391506</v>
-      </c>
-      <c r="L50" s="1">
+        <v>0.85</v>
+      </c>
+      <c r="K50" s="2">
+        <v>2.8740000000000001</v>
+      </c>
+      <c r="L50" s="2">
         <v>5.1479079699518424</v>
       </c>
       <c r="M50">
         <v>3.06</v>
       </c>
       <c r="N50">
-        <v>129.25</v>
-      </c>
-      <c r="O50">
-        <v>20.190000000000001</v>
-      </c>
-      <c r="P50" s="2">
-        <v>3.2950965824665675E-4</v>
-      </c>
-      <c r="Q50" s="1">
-        <v>2.0594353640416047E-3</v>
-      </c>
-      <c r="R50">
-        <v>0.16</v>
+        <v>122.26</v>
+      </c>
+      <c r="O50" s="4">
+        <v>1.69093E-3</v>
+      </c>
+      <c r="P50" s="3">
+        <v>2.4366000000000001E-4</v>
+      </c>
+      <c r="Q50">
+        <v>24.59</v>
+      </c>
+      <c r="R50" s="2">
+        <v>0.14410000000000001</v>
       </c>
       <c r="S50">
-        <v>8.6999999999999993</v>
-      </c>
-      <c r="T50" s="3">
+        <v>11.17</v>
+      </c>
+      <c r="T50" s="2">
         <f t="shared" si="2"/>
         <v>1.3089969389957472</v>
       </c>
@@ -4712,10 +4716,10 @@
         <v>41.58</v>
       </c>
       <c r="V50">
-        <v>6.31</v>
+        <v>12.15</v>
       </c>
       <c r="W50">
-        <v>30.97</v>
+        <v>31.46</v>
       </c>
     </row>
     <row r="51" spans="1:23" x14ac:dyDescent="0.2">
@@ -4734,51 +4738,51 @@
       <c r="E51">
         <v>24</v>
       </c>
-      <c r="F51" s="3">
+      <c r="F51" s="2">
         <v>0.47058823529411764</v>
       </c>
-      <c r="G51">
+      <c r="G51" s="2">
         <f t="shared" si="1"/>
         <v>3845.3094079939065</v>
       </c>
-      <c r="H51" s="3">
+      <c r="H51" s="2">
         <f t="shared" si="3"/>
         <v>49027.694951922313</v>
       </c>
-      <c r="I51" s="3">
-        <v>2.7792454883636624</v>
+      <c r="I51" s="2">
+        <v>2.76</v>
       </c>
       <c r="J51">
-        <v>1.06</v>
-      </c>
-      <c r="K51" s="4">
-        <v>2.8090211121524788</v>
-      </c>
-      <c r="L51" s="1">
+        <v>1.43</v>
+      </c>
+      <c r="K51" s="2">
+        <v>2.8</v>
+      </c>
+      <c r="L51" s="2">
         <v>9.6709531611046753</v>
       </c>
       <c r="M51">
         <v>5.03</v>
       </c>
       <c r="N51">
-        <v>136.26</v>
-      </c>
-      <c r="O51">
-        <v>26.98</v>
-      </c>
-      <c r="P51" s="2">
-        <v>2.5613046701260191E-4</v>
-      </c>
-      <c r="Q51" s="1">
-        <v>1.600815418828762E-3</v>
-      </c>
-      <c r="R51">
-        <v>0.16</v>
+        <v>135.32</v>
+      </c>
+      <c r="O51" s="4">
+        <v>1.5642900000000001E-3</v>
+      </c>
+      <c r="P51" s="3">
+        <v>2.4262E-4</v>
+      </c>
+      <c r="Q51">
+        <v>27.61</v>
+      </c>
+      <c r="R51" s="2">
+        <v>0.15509999999999999</v>
       </c>
       <c r="S51">
-        <v>11.63</v>
-      </c>
-      <c r="T51" s="3">
+        <v>11.95</v>
+      </c>
+      <c r="T51" s="2">
         <f t="shared" si="2"/>
         <v>1.5707963267948966</v>
       </c>
@@ -4786,10 +4790,10 @@
         <v>43.19</v>
       </c>
       <c r="V51">
-        <v>6.31</v>
+        <v>12.52</v>
       </c>
       <c r="W51">
-        <v>30.97</v>
+        <v>30.32</v>
       </c>
     </row>
     <row r="52" spans="1:23" x14ac:dyDescent="0.2">
@@ -4808,51 +4812,51 @@
       <c r="E52">
         <v>22</v>
       </c>
-      <c r="F52" s="3">
+      <c r="F52" s="2">
         <v>0.43137254901960786</v>
       </c>
-      <c r="G52">
+      <c r="G52" s="2">
         <f t="shared" si="1"/>
         <v>3524.866957327748</v>
       </c>
-      <c r="H52" s="3">
+      <c r="H52" s="2">
         <f t="shared" si="3"/>
         <v>44942.053705928782</v>
       </c>
-      <c r="I52" s="3">
-        <v>2.5837715552522997</v>
+      <c r="I52" s="2">
+        <v>2.69</v>
       </c>
       <c r="J52">
-        <v>1.42</v>
-      </c>
-      <c r="K52" s="4">
-        <v>2.6209896076813752</v>
-      </c>
-      <c r="L52" s="1">
+        <v>1.97</v>
+      </c>
+      <c r="K52" s="2">
+        <v>2.7440000000000002</v>
+      </c>
+      <c r="L52" s="2">
         <v>8.1248183366404607</v>
       </c>
       <c r="M52">
         <v>4.6100000000000003</v>
       </c>
       <c r="N52">
-        <v>116.12</v>
-      </c>
-      <c r="O52">
-        <v>26.98</v>
-      </c>
-      <c r="P52" s="2">
-        <v>2.5737583395107487E-4</v>
-      </c>
-      <c r="Q52" s="1">
-        <v>1.6085989621942179E-3</v>
-      </c>
-      <c r="R52">
-        <v>0.16</v>
+        <v>120.89</v>
+      </c>
+      <c r="O52" s="4">
+        <v>1.6464299999999999E-3</v>
+      </c>
+      <c r="P52" s="3">
+        <v>2.6753999999999998E-4</v>
+      </c>
+      <c r="Q52">
+        <v>26.36</v>
+      </c>
+      <c r="R52" s="2">
+        <v>0.16250000000000001</v>
       </c>
       <c r="S52">
-        <v>11.63</v>
-      </c>
-      <c r="T52" s="3">
+        <v>11.34</v>
+      </c>
+      <c r="T52" s="2">
         <f t="shared" si="2"/>
         <v>1.5707963267948966</v>
       </c>
@@ -4860,10 +4864,10 @@
         <v>43.4</v>
       </c>
       <c r="V52">
-        <v>6.31</v>
+        <v>12.52</v>
       </c>
       <c r="W52">
-        <v>30.97</v>
+        <v>30.32</v>
       </c>
     </row>
     <row r="53" spans="1:23" x14ac:dyDescent="0.2">
@@ -4882,51 +4886,51 @@
       <c r="E53">
         <v>22</v>
       </c>
-      <c r="F53" s="3">
+      <c r="F53" s="2">
         <v>0.43137254901960786</v>
       </c>
-      <c r="G53">
+      <c r="G53" s="2">
         <f t="shared" si="1"/>
         <v>3524.866957327748</v>
       </c>
-      <c r="H53" s="3">
+      <c r="H53" s="2">
         <f t="shared" si="3"/>
         <v>44942.053705928782</v>
       </c>
-      <c r="I53" s="3">
-        <v>2.5837715552522997</v>
+      <c r="I53" s="2">
+        <v>2.74</v>
       </c>
       <c r="J53">
-        <v>1.42</v>
-      </c>
-      <c r="K53" s="4">
-        <v>2.6209896076813752</v>
-      </c>
-      <c r="L53" s="1">
+        <v>1.52</v>
+      </c>
+      <c r="K53" s="2">
+        <v>2.782</v>
+      </c>
+      <c r="L53" s="2">
         <v>9.4642677804250042</v>
       </c>
       <c r="M53">
         <v>5.37</v>
       </c>
       <c r="N53">
-        <v>116.12</v>
-      </c>
-      <c r="O53">
-        <v>26.98</v>
-      </c>
-      <c r="P53" s="2">
-        <v>2.5737583395107487E-4</v>
-      </c>
-      <c r="Q53" s="1">
-        <v>1.6085989621942179E-3</v>
-      </c>
-      <c r="R53">
-        <v>0.16</v>
+        <v>123.14</v>
+      </c>
+      <c r="O53" s="4">
+        <v>1.6092000000000001E-3</v>
+      </c>
+      <c r="P53" s="3">
+        <v>2.6150000000000001E-4</v>
+      </c>
+      <c r="Q53">
+        <v>26.97</v>
+      </c>
+      <c r="R53" s="2">
+        <v>0.16250000000000001</v>
       </c>
       <c r="S53">
-        <v>11.63</v>
-      </c>
-      <c r="T53" s="3">
+        <v>11.6</v>
+      </c>
+      <c r="T53" s="2">
         <f t="shared" si="2"/>
         <v>1.5707963267948966</v>
       </c>
@@ -4934,19 +4938,798 @@
         <v>43.4</v>
       </c>
       <c r="V53">
-        <v>6.31</v>
+        <v>12.52</v>
       </c>
       <c r="W53">
-        <v>30.97</v>
+        <v>30.32</v>
       </c>
     </row>
     <row r="54" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="G54"/>
+      <c r="I54"/>
       <c r="J54"/>
+      <c r="K54"/>
+      <c r="L54"/>
+      <c r="O54"/>
+      <c r="P54"/>
+      <c r="R54"/>
     </row>
     <row r="55" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="G55"/>
+      <c r="I55"/>
       <c r="J55"/>
+      <c r="K55"/>
+      <c r="L55"/>
+      <c r="O55"/>
+      <c r="P55"/>
+      <c r="R55"/>
+    </row>
+    <row r="56" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="G56"/>
+      <c r="I56"/>
+      <c r="J56"/>
+      <c r="K56"/>
+      <c r="L56"/>
+      <c r="O56"/>
+      <c r="P56"/>
+      <c r="R56"/>
+    </row>
+    <row r="57" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="G57"/>
+      <c r="I57"/>
+      <c r="J57"/>
+      <c r="K57"/>
+      <c r="L57"/>
+      <c r="O57"/>
+      <c r="P57"/>
+      <c r="R57"/>
+    </row>
+    <row r="58" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="G58"/>
+      <c r="I58"/>
+      <c r="J58"/>
+      <c r="K58"/>
+      <c r="L58"/>
+      <c r="O58"/>
+      <c r="P58"/>
+      <c r="R58"/>
+    </row>
+    <row r="59" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="G59"/>
+      <c r="I59"/>
+      <c r="J59"/>
+      <c r="K59"/>
+      <c r="L59"/>
+      <c r="O59"/>
+      <c r="P59"/>
+      <c r="R59"/>
+    </row>
+    <row r="60" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="G60"/>
+      <c r="I60"/>
+      <c r="J60"/>
+      <c r="K60"/>
+      <c r="L60"/>
+      <c r="O60"/>
+      <c r="P60"/>
+      <c r="R60"/>
+    </row>
+    <row r="61" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="G61"/>
+      <c r="I61"/>
+      <c r="J61"/>
+      <c r="K61"/>
+      <c r="L61"/>
+      <c r="O61"/>
+      <c r="P61"/>
+      <c r="R61"/>
+    </row>
+    <row r="62" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="G62"/>
+      <c r="I62"/>
+      <c r="J62"/>
+      <c r="K62"/>
+      <c r="L62"/>
+      <c r="O62"/>
+      <c r="P62"/>
+      <c r="R62"/>
+    </row>
+    <row r="63" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="G63"/>
+      <c r="I63"/>
+      <c r="J63"/>
+      <c r="K63"/>
+      <c r="L63"/>
+      <c r="O63"/>
+      <c r="P63"/>
+      <c r="R63"/>
+    </row>
+    <row r="64" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="G64"/>
+      <c r="I64"/>
+      <c r="J64"/>
+      <c r="K64"/>
+      <c r="L64"/>
+      <c r="O64"/>
+      <c r="P64"/>
+      <c r="R64"/>
+    </row>
+    <row r="65" spans="7:18" x14ac:dyDescent="0.2">
+      <c r="G65"/>
+      <c r="I65"/>
+      <c r="J65"/>
+      <c r="K65"/>
+      <c r="L65"/>
+      <c r="O65"/>
+      <c r="P65"/>
+      <c r="R65"/>
+    </row>
+    <row r="66" spans="7:18" x14ac:dyDescent="0.2">
+      <c r="G66"/>
+      <c r="I66"/>
+      <c r="J66"/>
+      <c r="K66"/>
+      <c r="L66"/>
+      <c r="O66"/>
+      <c r="P66"/>
+      <c r="R66"/>
+    </row>
+    <row r="67" spans="7:18" x14ac:dyDescent="0.2">
+      <c r="G67"/>
+      <c r="I67"/>
+      <c r="J67"/>
+      <c r="K67"/>
+      <c r="L67"/>
+      <c r="O67"/>
+      <c r="P67"/>
+      <c r="R67"/>
+    </row>
+    <row r="68" spans="7:18" x14ac:dyDescent="0.2">
+      <c r="G68"/>
+      <c r="I68"/>
+      <c r="J68"/>
+      <c r="K68"/>
+      <c r="L68"/>
+      <c r="O68"/>
+      <c r="P68"/>
+      <c r="R68"/>
+    </row>
+    <row r="69" spans="7:18" x14ac:dyDescent="0.2">
+      <c r="G69"/>
+      <c r="I69"/>
+      <c r="J69"/>
+      <c r="K69"/>
+      <c r="L69"/>
+      <c r="O69"/>
+      <c r="P69"/>
+      <c r="R69"/>
+    </row>
+    <row r="70" spans="7:18" x14ac:dyDescent="0.2">
+      <c r="G70"/>
+      <c r="I70"/>
+      <c r="J70"/>
+      <c r="K70"/>
+      <c r="L70"/>
+      <c r="O70"/>
+      <c r="P70"/>
+      <c r="R70"/>
+    </row>
+    <row r="71" spans="7:18" x14ac:dyDescent="0.2">
+      <c r="G71"/>
+      <c r="I71"/>
+      <c r="J71"/>
+      <c r="K71"/>
+      <c r="L71"/>
+      <c r="O71"/>
+      <c r="P71"/>
+      <c r="R71"/>
+    </row>
+    <row r="72" spans="7:18" x14ac:dyDescent="0.2">
+      <c r="G72"/>
+      <c r="I72"/>
+      <c r="J72"/>
+      <c r="K72"/>
+      <c r="L72"/>
+      <c r="O72"/>
+      <c r="P72"/>
+      <c r="R72"/>
+    </row>
+    <row r="73" spans="7:18" x14ac:dyDescent="0.2">
+      <c r="G73"/>
+      <c r="I73"/>
+      <c r="J73"/>
+      <c r="K73"/>
+      <c r="L73"/>
+      <c r="O73"/>
+      <c r="P73"/>
+      <c r="R73"/>
+    </row>
+    <row r="74" spans="7:18" x14ac:dyDescent="0.2">
+      <c r="G74"/>
+      <c r="I74"/>
+      <c r="J74"/>
+      <c r="K74"/>
+      <c r="L74"/>
+      <c r="O74"/>
+      <c r="P74"/>
+      <c r="R74"/>
+    </row>
+    <row r="75" spans="7:18" x14ac:dyDescent="0.2">
+      <c r="G75"/>
+      <c r="I75"/>
+      <c r="J75"/>
+      <c r="K75"/>
+      <c r="L75"/>
+      <c r="O75"/>
+      <c r="P75"/>
+      <c r="R75"/>
+    </row>
+    <row r="76" spans="7:18" x14ac:dyDescent="0.2">
+      <c r="G76"/>
+      <c r="I76"/>
+      <c r="J76"/>
+      <c r="K76"/>
+      <c r="L76"/>
+      <c r="O76"/>
+      <c r="P76"/>
+      <c r="R76"/>
+    </row>
+    <row r="77" spans="7:18" x14ac:dyDescent="0.2">
+      <c r="G77"/>
+      <c r="I77"/>
+      <c r="J77"/>
+      <c r="K77"/>
+      <c r="L77"/>
+      <c r="O77"/>
+      <c r="P77"/>
+      <c r="R77"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{174416E8-D472-1244-B2F8-F4BD841DC05A}">
+  <dimension ref="A1:G23"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="5" max="5" width="15" customWidth="1"/>
+    <col min="6" max="6" width="17.1640625" customWidth="1"/>
+    <col min="7" max="7" width="21.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>31</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>31.09</v>
+      </c>
+      <c r="D2">
+        <v>2.7092000000000001E-4</v>
+      </c>
+      <c r="E2">
+        <v>1.29688E-3</v>
+      </c>
+      <c r="F2">
+        <v>0.2089</v>
+      </c>
+      <c r="G2">
+        <v>6.42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>32</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>33.29</v>
+      </c>
+      <c r="D3">
+        <v>2.4282000000000001E-4</v>
+      </c>
+      <c r="E3">
+        <v>1.21959E-3</v>
+      </c>
+      <c r="F3">
+        <v>0.1991</v>
+      </c>
+      <c r="G3">
+        <v>6.88</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>33</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>33.76</v>
+      </c>
+      <c r="D4">
+        <v>2.309E-4</v>
+      </c>
+      <c r="E4">
+        <v>1.20261E-3</v>
+      </c>
+      <c r="F4">
+        <v>0.192</v>
+      </c>
+      <c r="G4">
+        <v>6.98</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>34</v>
+      </c>
+      <c r="B5">
+        <v>15</v>
+      </c>
+      <c r="C5">
+        <v>28.87</v>
+      </c>
+      <c r="D5">
+        <v>2.2723E-4</v>
+      </c>
+      <c r="E5">
+        <v>1.3397999999999999E-3</v>
+      </c>
+      <c r="F5">
+        <v>0.1696</v>
+      </c>
+      <c r="G5">
+        <v>7.08</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>35</v>
+      </c>
+      <c r="B6">
+        <v>15</v>
+      </c>
+      <c r="C6">
+        <v>28.93</v>
+      </c>
+      <c r="D6">
+        <v>2.6267E-4</v>
+      </c>
+      <c r="E6">
+        <v>1.51746E-3</v>
+      </c>
+      <c r="F6">
+        <v>0.1731</v>
+      </c>
+      <c r="G6">
+        <v>7.09</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>36</v>
+      </c>
+      <c r="B7">
+        <v>15</v>
+      </c>
+      <c r="C7">
+        <v>27.28</v>
+      </c>
+      <c r="D7">
+        <v>2.4766000000000002E-4</v>
+      </c>
+      <c r="E7">
+        <v>1.4039600000000001E-3</v>
+      </c>
+      <c r="F7">
+        <v>0.1764</v>
+      </c>
+      <c r="G7">
+        <v>6.69</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>37</v>
+      </c>
+      <c r="B8">
+        <v>30</v>
+      </c>
+      <c r="C8">
+        <v>21.02</v>
+      </c>
+      <c r="D8">
+        <v>1.6061999999999999E-4</v>
+      </c>
+      <c r="E8">
+        <v>1.1741200000000001E-3</v>
+      </c>
+      <c r="F8">
+        <v>0.1368</v>
+      </c>
+      <c r="G8">
+        <v>7.13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>38</v>
+      </c>
+      <c r="B9">
+        <v>30</v>
+      </c>
+      <c r="C9">
+        <v>23.97</v>
+      </c>
+      <c r="D9">
+        <v>1.9933E-4</v>
+      </c>
+      <c r="E9">
+        <v>1.4559900000000001E-3</v>
+      </c>
+      <c r="F9">
+        <v>0.13689999999999999</v>
+      </c>
+      <c r="G9">
+        <v>8.1300000000000008</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>39</v>
+      </c>
+      <c r="B10">
+        <v>30</v>
+      </c>
+      <c r="C10">
+        <v>21.74</v>
+      </c>
+      <c r="D10">
+        <v>1.4797000000000001E-4</v>
+      </c>
+      <c r="E10">
+        <v>1.12695E-3</v>
+      </c>
+      <c r="F10">
+        <v>0.1313</v>
+      </c>
+      <c r="G10">
+        <v>7.39</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>40</v>
+      </c>
+      <c r="B11">
+        <v>45</v>
+      </c>
+      <c r="C11">
+        <v>19.649999999999999</v>
+      </c>
+      <c r="D11">
+        <v>1.5447E-4</v>
+      </c>
+      <c r="E11">
+        <v>1.29262E-3</v>
+      </c>
+      <c r="F11">
+        <v>0.1195</v>
+      </c>
+      <c r="G11">
+        <v>8.5299999999999994</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>41</v>
+      </c>
+      <c r="B12">
+        <v>45</v>
+      </c>
+      <c r="C12">
+        <v>19.68</v>
+      </c>
+      <c r="D12">
+        <v>1.526E-4</v>
+      </c>
+      <c r="E12">
+        <v>1.31098E-3</v>
+      </c>
+      <c r="F12">
+        <v>0.1164</v>
+      </c>
+      <c r="G12">
+        <v>8.57</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>42</v>
+      </c>
+      <c r="B13">
+        <v>45</v>
+      </c>
+      <c r="C13">
+        <v>19.68</v>
+      </c>
+      <c r="D13">
+        <v>1.5666000000000001E-4</v>
+      </c>
+      <c r="E13">
+        <v>1.31098E-3</v>
+      </c>
+      <c r="F13">
+        <v>0.1195</v>
+      </c>
+      <c r="G13">
+        <v>8.5500000000000007</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>43</v>
+      </c>
+      <c r="B14">
+        <v>60</v>
+      </c>
+      <c r="C14">
+        <v>21.2</v>
+      </c>
+      <c r="D14">
+        <v>2.1172000000000001E-4</v>
+      </c>
+      <c r="E14">
+        <v>1.7353799999999999E-3</v>
+      </c>
+      <c r="F14">
+        <v>0.122</v>
+      </c>
+      <c r="G14">
+        <v>10.09</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>44</v>
+      </c>
+      <c r="B15">
+        <v>60</v>
+      </c>
+      <c r="C15">
+        <v>21.26</v>
+      </c>
+      <c r="D15">
+        <v>2.0875000000000001E-4</v>
+      </c>
+      <c r="E15">
+        <v>1.7497599999999999E-3</v>
+      </c>
+      <c r="F15">
+        <v>0.1193</v>
+      </c>
+      <c r="G15">
+        <v>10.15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>45</v>
+      </c>
+      <c r="B16">
+        <v>60</v>
+      </c>
+      <c r="C16">
+        <v>19.760000000000002</v>
+      </c>
+      <c r="D16">
+        <v>2.4143E-4</v>
+      </c>
+      <c r="E16">
+        <v>1.84717E-3</v>
+      </c>
+      <c r="F16">
+        <v>0.13070000000000001</v>
+      </c>
+      <c r="G16">
+        <v>9.32</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>46</v>
+      </c>
+      <c r="B17">
+        <v>75</v>
+      </c>
+      <c r="C17">
+        <v>22.72</v>
+      </c>
+      <c r="D17">
+        <v>2.6615999999999999E-4</v>
+      </c>
+      <c r="E17">
+        <v>1.6368800000000001E-3</v>
+      </c>
+      <c r="F17">
+        <v>0.16259999999999999</v>
+      </c>
+      <c r="G17">
+        <v>10.14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>47</v>
+      </c>
+      <c r="B18">
+        <v>75</v>
+      </c>
+      <c r="C18">
+        <v>26.67</v>
+      </c>
+      <c r="D18">
+        <v>2.0038E-4</v>
+      </c>
+      <c r="E18">
+        <v>1.52268E-3</v>
+      </c>
+      <c r="F18">
+        <v>0.13159999999999999</v>
+      </c>
+      <c r="G18">
+        <v>12.26</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>48</v>
+      </c>
+      <c r="B19">
+        <v>75</v>
+      </c>
+      <c r="C19">
+        <v>23.85</v>
+      </c>
+      <c r="D19">
+        <v>2.3418000000000001E-4</v>
+      </c>
+      <c r="E19">
+        <v>1.6364800000000001E-3</v>
+      </c>
+      <c r="F19">
+        <v>0.1431</v>
+      </c>
+      <c r="G19">
+        <v>10.84</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>49</v>
+      </c>
+      <c r="B20">
+        <v>75</v>
+      </c>
+      <c r="C20">
+        <v>24.59</v>
+      </c>
+      <c r="D20">
+        <v>2.4366000000000001E-4</v>
+      </c>
+      <c r="E20">
+        <v>1.69093E-3</v>
+      </c>
+      <c r="F20">
+        <v>0.14410000000000001</v>
+      </c>
+      <c r="G20">
+        <v>11.17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>50</v>
+      </c>
+      <c r="B21">
+        <v>90</v>
+      </c>
+      <c r="C21">
+        <v>27.61</v>
+      </c>
+      <c r="D21">
+        <v>2.4262E-4</v>
+      </c>
+      <c r="E21">
+        <v>1.5642900000000001E-3</v>
+      </c>
+      <c r="F21">
+        <v>0.15509999999999999</v>
+      </c>
+      <c r="G21">
+        <v>11.95</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>51</v>
+      </c>
+      <c r="B22">
+        <v>90</v>
+      </c>
+      <c r="C22">
+        <v>26.36</v>
+      </c>
+      <c r="D22">
+        <v>2.6753999999999998E-4</v>
+      </c>
+      <c r="E22">
+        <v>1.6464299999999999E-3</v>
+      </c>
+      <c r="F22">
+        <v>0.16250000000000001</v>
+      </c>
+      <c r="G22">
+        <v>11.34</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>52</v>
+      </c>
+      <c r="B23">
+        <v>90</v>
+      </c>
+      <c r="C23">
+        <v>26.97</v>
+      </c>
+      <c r="D23">
+        <v>2.6150000000000001E-4</v>
+      </c>
+      <c r="E23">
+        <v>1.6092000000000001E-3</v>
+      </c>
+      <c r="F23">
+        <v>0.16250000000000001</v>
+      </c>
+      <c r="G23">
+        <v>11.6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/selected_all_samples.xlsx
+++ b/selected_all_samples.xlsx
@@ -8,13 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/durgaacharya/Documents/Nepal_Geology/Impact_of_Rock_Structure_on_Tensile_Strength-Rupture/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB0C7700-3C86-3543-8C6E-7E6FA078DED0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5815E1BC-448F-3049-9D51-4F7A3774EE11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="48040" windowHeight="26860" xr2:uid="{DAA96A09-7419-F74F-A2D7-B0B57583498C}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19740" xr2:uid="{DAA96A09-7419-F74F-A2D7-B0B57583498C}"/>
   </bookViews>
   <sheets>
     <sheet name="selected_all_samples" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="25">
   <si>
     <t>SN</t>
   </si>
@@ -109,12 +108,6 @@
   </si>
   <si>
     <t>Psammitic schist</t>
-  </si>
-  <si>
-    <t>Modulus_of_Elasticity_GPa</t>
-  </si>
-  <si>
-    <t>Shear_Modulus_GPa</t>
   </si>
 </sst>
 </file>
@@ -1141,27 +1134,27 @@
       <c r="N2">
         <v>130.62</v>
       </c>
-      <c r="O2" s="4">
-        <v>1.25752E-3</v>
-      </c>
-      <c r="P2" s="3">
-        <v>3.3272E-4</v>
+      <c r="O2">
+        <v>1.4916E-3</v>
+      </c>
+      <c r="P2">
+        <v>3.8779999999999999E-4</v>
       </c>
       <c r="Q2">
-        <v>32.97</v>
+        <v>34.5</v>
       </c>
       <c r="R2" s="2">
-        <v>0.2646</v>
+        <v>0.26</v>
       </c>
       <c r="S2">
-        <v>14.03</v>
+        <v>13.6905</v>
       </c>
       <c r="T2" s="2">
         <f>RADIANS(C2)</f>
         <v>0</v>
       </c>
       <c r="U2">
-        <v>41.46</v>
+        <v>51.46</v>
       </c>
       <c r="V2">
         <v>15.22</v>
@@ -1215,20 +1208,20 @@
       <c r="N3">
         <v>139.24</v>
       </c>
-      <c r="O3" s="4">
-        <v>1.5636000000000001E-3</v>
-      </c>
-      <c r="P3" s="3">
-        <v>4.0734000000000001E-4</v>
+      <c r="O3">
+        <v>1.5051000000000001E-3</v>
+      </c>
+      <c r="P3">
+        <v>3.9130000000000002E-4</v>
       </c>
       <c r="Q3">
-        <v>37.54</v>
+        <v>39</v>
       </c>
       <c r="R3" s="2">
-        <v>0.26050000000000001</v>
+        <v>0.26</v>
       </c>
       <c r="S3">
-        <v>15.98</v>
+        <v>15.4762</v>
       </c>
       <c r="T3" s="2">
         <f t="shared" ref="T3:T53" si="2">RADIANS(C3)</f>
@@ -1289,20 +1282,20 @@
       <c r="N4">
         <v>152.22999999999999</v>
       </c>
-      <c r="O4" s="4">
-        <v>1.58927E-3</v>
-      </c>
-      <c r="P4" s="3">
-        <v>4.0962000000000003E-4</v>
+      <c r="O4">
+        <v>1.5325E-3</v>
+      </c>
+      <c r="P4">
+        <v>3.9849999999999998E-4</v>
       </c>
       <c r="Q4">
-        <v>38.57</v>
+        <v>40</v>
       </c>
       <c r="R4" s="2">
-        <v>0.25769999999999998</v>
+        <v>0.26</v>
       </c>
       <c r="S4">
-        <v>16.41</v>
+        <v>15.872999999999999</v>
       </c>
       <c r="T4" s="2">
         <f t="shared" si="2"/>
@@ -1363,20 +1356,20 @@
       <c r="N5">
         <v>132.37</v>
       </c>
-      <c r="O5" s="4">
-        <v>1.55572E-3</v>
-      </c>
-      <c r="P5" s="3">
-        <v>4.0382999999999999E-4</v>
+      <c r="O5">
+        <v>1.4962E-3</v>
+      </c>
+      <c r="P5">
+        <v>3.8900000000000002E-4</v>
       </c>
       <c r="Q5">
-        <v>37.99</v>
+        <v>39.5</v>
       </c>
       <c r="R5" s="2">
-        <v>0.2596</v>
+        <v>0.26</v>
       </c>
       <c r="S5">
-        <v>16.170000000000002</v>
+        <v>15.6746</v>
       </c>
       <c r="T5" s="2">
         <f t="shared" si="2"/>
@@ -1437,20 +1430,20 @@
       <c r="N6">
         <v>140.63999999999999</v>
       </c>
-      <c r="O6" s="4">
-        <v>1.5236500000000001E-3</v>
-      </c>
-      <c r="P6" s="3">
-        <v>3.9247000000000002E-4</v>
+      <c r="O6">
+        <v>1.4564000000000001E-3</v>
+      </c>
+      <c r="P6">
+        <v>3.7869999999999999E-4</v>
       </c>
       <c r="Q6">
-        <v>37.28</v>
+        <v>39</v>
       </c>
       <c r="R6" s="2">
-        <v>0.2576</v>
+        <v>0.26</v>
       </c>
       <c r="S6">
-        <v>15.86</v>
+        <v>15.4762</v>
       </c>
       <c r="T6" s="2">
         <f t="shared" si="2"/>
@@ -1511,20 +1504,20 @@
       <c r="N7">
         <v>111.54</v>
       </c>
-      <c r="O7" s="4">
-        <v>1.24581E-3</v>
-      </c>
-      <c r="P7" s="3">
-        <v>3.1105999999999999E-4</v>
+      <c r="O7">
+        <v>1.2457E-3</v>
+      </c>
+      <c r="P7">
+        <v>3.1139999999999998E-4</v>
       </c>
       <c r="Q7">
         <v>37.89</v>
       </c>
       <c r="R7" s="2">
-        <v>0.24970000000000001</v>
+        <v>0.25</v>
       </c>
       <c r="S7">
-        <v>16.22</v>
+        <v>15.156000000000001</v>
       </c>
       <c r="T7" s="2">
         <f t="shared" si="2"/>
@@ -1585,20 +1578,20 @@
       <c r="N8">
         <v>157.75</v>
       </c>
-      <c r="O8" s="4">
+      <c r="O8">
         <v>1.3602E-3</v>
       </c>
-      <c r="P8" s="3">
-        <v>3.5435000000000002E-4</v>
+      <c r="P8">
+        <v>3.5359999999999998E-4</v>
       </c>
       <c r="Q8">
         <v>36.26</v>
       </c>
       <c r="R8" s="2">
-        <v>0.26050000000000001</v>
+        <v>0.26</v>
       </c>
       <c r="S8">
-        <v>15.52</v>
+        <v>14.3889</v>
       </c>
       <c r="T8" s="2">
         <f t="shared" si="2"/>
@@ -1659,20 +1652,20 @@
       <c r="N9">
         <v>131.09</v>
       </c>
-      <c r="O9" s="4">
-        <v>1.37805E-3</v>
-      </c>
-      <c r="P9" s="3">
-        <v>3.4619000000000002E-4</v>
+      <c r="O9">
+        <v>1.3779E-3</v>
+      </c>
+      <c r="P9">
+        <v>3.4450000000000003E-4</v>
       </c>
       <c r="Q9">
         <v>38.32</v>
       </c>
       <c r="R9" s="2">
-        <v>0.25119999999999998</v>
+        <v>0.25</v>
       </c>
       <c r="S9">
-        <v>16.399999999999999</v>
+        <v>15.327999999999999</v>
       </c>
       <c r="T9" s="2">
         <f t="shared" si="2"/>
@@ -1733,20 +1726,20 @@
       <c r="N10">
         <v>144.53</v>
       </c>
-      <c r="O10" s="4">
-        <v>1.3424699999999999E-3</v>
-      </c>
-      <c r="P10" s="3">
-        <v>3.4215E-4</v>
+      <c r="O10">
+        <v>1.3423E-3</v>
+      </c>
+      <c r="P10">
+        <v>3.3560000000000003E-4</v>
       </c>
       <c r="Q10">
         <v>37.1</v>
       </c>
       <c r="R10" s="2">
-        <v>0.25490000000000002</v>
+        <v>0.25</v>
       </c>
       <c r="S10">
-        <v>15.88</v>
+        <v>14.84</v>
       </c>
       <c r="T10" s="2">
         <f t="shared" si="2"/>
@@ -1807,20 +1800,20 @@
       <c r="N11">
         <v>124.84</v>
       </c>
-      <c r="O11" s="4">
-        <v>1.49383E-3</v>
-      </c>
-      <c r="P11" s="3">
-        <v>3.9124E-4</v>
+      <c r="O11">
+        <v>1.4938E-3</v>
+      </c>
+      <c r="P11">
+        <v>3.8840000000000001E-4</v>
       </c>
       <c r="Q11">
         <v>37.020000000000003</v>
       </c>
       <c r="R11" s="2">
-        <v>0.26190000000000002</v>
+        <v>0.26</v>
       </c>
       <c r="S11">
-        <v>15.85</v>
+        <v>14.6905</v>
       </c>
       <c r="T11" s="2">
         <f>RADIANS(C11)</f>
@@ -1881,27 +1874,27 @@
       <c r="N12">
         <v>123.59</v>
       </c>
-      <c r="O12" s="4">
-        <v>9.6080999999999998E-4</v>
-      </c>
-      <c r="P12" s="3">
-        <v>2.3230000000000001E-4</v>
+      <c r="O12">
+        <v>1.0383E-3</v>
+      </c>
+      <c r="P12">
+        <v>2.4919999999999999E-4</v>
       </c>
       <c r="Q12">
         <v>38.69</v>
       </c>
       <c r="R12" s="2">
-        <v>0.24179999999999999</v>
+        <v>0.24</v>
       </c>
       <c r="S12">
-        <v>16.760000000000002</v>
+        <v>15.6008</v>
       </c>
       <c r="T12" s="2">
         <f t="shared" si="2"/>
         <v>0.52359877559829882</v>
       </c>
       <c r="U12">
-        <v>37.17</v>
+        <v>40.17</v>
       </c>
       <c r="V12">
         <v>11.309999999999999</v>
@@ -1955,27 +1948,27 @@
       <c r="N13">
         <v>115.22</v>
       </c>
-      <c r="O13" s="4">
-        <v>9.8028000000000004E-4</v>
-      </c>
-      <c r="P13" s="3">
-        <v>2.3864000000000001E-4</v>
+      <c r="O13">
+        <v>1.108E-3</v>
+      </c>
+      <c r="P13">
+        <v>2.6590000000000001E-4</v>
       </c>
       <c r="Q13">
         <v>39.17</v>
       </c>
       <c r="R13" s="2">
-        <v>0.24340000000000001</v>
+        <v>0.24</v>
       </c>
       <c r="S13">
-        <v>16.97</v>
+        <v>15.7944</v>
       </c>
       <c r="T13" s="2">
         <f t="shared" si="2"/>
         <v>0.52359877559829882</v>
       </c>
       <c r="U13">
-        <v>38.4</v>
+        <v>43.4</v>
       </c>
       <c r="V13">
         <v>11.309999999999999</v>
@@ -2029,20 +2022,20 @@
       <c r="N14">
         <v>146.57</v>
       </c>
-      <c r="O14" s="4">
-        <v>1.05532E-3</v>
-      </c>
-      <c r="P14" s="3">
-        <v>2.6224000000000001E-4</v>
+      <c r="O14">
+        <v>1.0552000000000001E-3</v>
+      </c>
+      <c r="P14">
+        <v>2.6380000000000002E-4</v>
       </c>
       <c r="Q14">
         <v>38.950000000000003</v>
       </c>
       <c r="R14" s="2">
-        <v>0.2485</v>
+        <v>0.25</v>
       </c>
       <c r="S14">
-        <v>16.87</v>
+        <v>15.58</v>
       </c>
       <c r="T14" s="2">
         <f t="shared" si="2"/>
@@ -2103,27 +2096,27 @@
       <c r="N15">
         <v>154.44</v>
       </c>
-      <c r="O15" s="4">
-        <v>1.02804E-3</v>
-      </c>
-      <c r="P15" s="3">
-        <v>2.5405000000000002E-4</v>
+      <c r="O15">
+        <v>1.1056E-3</v>
+      </c>
+      <c r="P15">
+        <v>2.764E-4</v>
       </c>
       <c r="Q15">
         <v>38.619999999999997</v>
       </c>
       <c r="R15" s="2">
-        <v>0.24709999999999999</v>
+        <v>0.25</v>
       </c>
       <c r="S15">
-        <v>16.73</v>
+        <v>15.448</v>
       </c>
       <c r="T15" s="2">
         <f t="shared" si="2"/>
         <v>0.52359877559829882</v>
       </c>
       <c r="U15">
-        <v>39.700000000000003</v>
+        <v>42.7</v>
       </c>
       <c r="V15">
         <v>11.309999999999999</v>
@@ -2177,27 +2170,27 @@
       <c r="N16">
         <v>124.49</v>
       </c>
-      <c r="O16" s="4">
-        <v>9.3725999999999998E-4</v>
-      </c>
-      <c r="P16" s="3">
-        <v>2.2673999999999999E-4</v>
+      <c r="O16">
+        <v>1.1186E-3</v>
+      </c>
+      <c r="P16">
+        <v>2.6850000000000002E-4</v>
       </c>
       <c r="Q16">
         <v>38.619999999999997</v>
       </c>
       <c r="R16" s="2">
-        <v>0.2419</v>
+        <v>0.24</v>
       </c>
       <c r="S16">
-        <v>16.739999999999998</v>
+        <v>15.5726</v>
       </c>
       <c r="T16" s="2">
         <f t="shared" si="2"/>
         <v>0.52359877559829882</v>
       </c>
       <c r="U16">
-        <v>36.200000000000003</v>
+        <v>43.2</v>
       </c>
       <c r="V16">
         <v>11.309999999999999</v>
@@ -2251,20 +2244,20 @@
       <c r="N17">
         <v>128.08000000000001</v>
       </c>
-      <c r="O17" s="4">
-        <v>1.0437599999999999E-3</v>
-      </c>
-      <c r="P17" s="3">
-        <v>2.3362E-4</v>
+      <c r="O17">
+        <v>1.0437999999999999E-3</v>
+      </c>
+      <c r="P17">
+        <v>2.296E-4</v>
       </c>
       <c r="Q17">
         <v>42.92</v>
       </c>
       <c r="R17" s="2">
-        <v>0.2238</v>
+        <v>0.22</v>
       </c>
       <c r="S17">
-        <v>18.670000000000002</v>
+        <v>17.590199999999999</v>
       </c>
       <c r="T17" s="2">
         <f t="shared" si="2"/>
@@ -2325,27 +2318,27 @@
       <c r="N18">
         <v>128.74</v>
       </c>
-      <c r="O18" s="4">
-        <v>8.1987E-4</v>
-      </c>
-      <c r="P18" s="3">
-        <v>1.9309000000000001E-4</v>
+      <c r="O18">
+        <v>1.212E-3</v>
+      </c>
+      <c r="P18">
+        <v>2.9090000000000002E-4</v>
       </c>
       <c r="Q18">
         <v>35.700000000000003</v>
       </c>
       <c r="R18" s="2">
-        <v>0.23549999999999999</v>
+        <v>0.24</v>
       </c>
       <c r="S18">
-        <v>15.53</v>
+        <v>14.395200000000001</v>
       </c>
       <c r="T18" s="2">
         <f t="shared" si="2"/>
         <v>0.78539816339744828</v>
       </c>
       <c r="U18">
-        <v>29.27</v>
+        <v>43.27</v>
       </c>
       <c r="V18">
         <v>11.68</v>
@@ -2399,20 +2392,20 @@
       <c r="N19">
         <v>135.79</v>
       </c>
-      <c r="O19" s="4">
-        <v>1.0848399999999999E-3</v>
-      </c>
-      <c r="P19" s="3">
-        <v>2.5987999999999999E-4</v>
+      <c r="O19">
+        <v>1.0849E-3</v>
+      </c>
+      <c r="P19">
+        <v>2.6039999999999999E-4</v>
       </c>
       <c r="Q19">
         <v>39.450000000000003</v>
       </c>
       <c r="R19" s="2">
-        <v>0.23960000000000001</v>
+        <v>0.24</v>
       </c>
       <c r="S19">
-        <v>17.16</v>
+        <v>15.907299999999999</v>
       </c>
       <c r="T19" s="2">
         <f t="shared" si="2"/>
@@ -2473,20 +2466,20 @@
       <c r="N20">
         <v>120.53</v>
       </c>
-      <c r="O20" s="4">
-        <v>1.3065500000000001E-3</v>
-      </c>
-      <c r="P20" s="3">
-        <v>2.9515999999999999E-4</v>
+      <c r="O20">
+        <v>1.3067E-3</v>
+      </c>
+      <c r="P20">
+        <v>3.0049999999999999E-4</v>
       </c>
       <c r="Q20">
         <v>48.52</v>
       </c>
       <c r="R20" s="2">
-        <v>0.22589999999999999</v>
+        <v>0.23</v>
       </c>
       <c r="S20">
-        <v>21.1</v>
+        <v>19.723600000000001</v>
       </c>
       <c r="T20" s="2">
         <f>RADIANS(C20)</f>
@@ -2547,20 +2540,20 @@
       <c r="N21">
         <v>119.26</v>
       </c>
-      <c r="O21" s="4">
-        <v>1.03561E-3</v>
-      </c>
-      <c r="P21" s="3">
-        <v>2.2662E-4</v>
+      <c r="O21">
+        <v>1.0357000000000001E-3</v>
+      </c>
+      <c r="P21">
+        <v>2.2780000000000001E-4</v>
       </c>
       <c r="Q21">
         <v>45.43</v>
       </c>
       <c r="R21" s="2">
-        <v>0.21879999999999999</v>
+        <v>0.22</v>
       </c>
       <c r="S21">
-        <v>19.489999999999998</v>
+        <v>18.6189</v>
       </c>
       <c r="T21" s="2">
         <f t="shared" si="2"/>
@@ -2621,20 +2614,20 @@
       <c r="N22">
         <v>127.64</v>
       </c>
-      <c r="O22" s="4">
-        <v>1.0798100000000001E-3</v>
-      </c>
-      <c r="P22" s="3">
-        <v>2.4111E-4</v>
+      <c r="O22">
+        <v>1.0797999999999999E-3</v>
+      </c>
+      <c r="P22">
+        <v>2.375E-4</v>
       </c>
       <c r="Q22">
         <v>45.01</v>
       </c>
       <c r="R22" s="2">
-        <v>0.2233</v>
+        <v>0.22</v>
       </c>
       <c r="S22">
-        <v>19.309999999999999</v>
+        <v>18.4467</v>
       </c>
       <c r="T22" s="2">
         <f t="shared" si="2"/>
@@ -2695,20 +2688,20 @@
       <c r="N23">
         <v>116.69</v>
       </c>
-      <c r="O23" s="4">
-        <v>1.09252E-3</v>
-      </c>
-      <c r="P23" s="3">
-        <v>2.3709999999999999E-4</v>
+      <c r="O23">
+        <v>1.0926E-3</v>
+      </c>
+      <c r="P23">
+        <v>2.4039999999999999E-4</v>
       </c>
       <c r="Q23">
         <v>46.86</v>
       </c>
       <c r="R23" s="2">
-        <v>0.217</v>
+        <v>0.22</v>
       </c>
       <c r="S23">
-        <v>20.100000000000001</v>
+        <v>19.204899999999999</v>
       </c>
       <c r="T23" s="2">
         <f t="shared" si="2"/>
@@ -2769,20 +2762,20 @@
       <c r="N24">
         <v>147.08000000000001</v>
       </c>
-      <c r="O24" s="4">
-        <v>1.2379800000000001E-3</v>
-      </c>
-      <c r="P24" s="3">
-        <v>2.5406000000000002E-4</v>
+      <c r="O24">
+        <v>1.2378999999999999E-3</v>
+      </c>
+      <c r="P24">
+        <v>2.5999999999999998E-4</v>
       </c>
       <c r="Q24">
         <v>52.24</v>
       </c>
       <c r="R24" s="2">
-        <v>0.20519999999999999</v>
+        <v>0.21</v>
       </c>
       <c r="S24">
-        <v>21.86</v>
+        <v>21.5868</v>
       </c>
       <c r="T24" s="2">
         <f t="shared" si="2"/>
@@ -2843,20 +2836,20 @@
       <c r="N25">
         <v>134.9</v>
       </c>
-      <c r="O25" s="4">
-        <v>1.2654999999999999E-3</v>
-      </c>
-      <c r="P25" s="3">
-        <v>2.876E-4</v>
+      <c r="O25">
+        <v>1.2656E-3</v>
+      </c>
+      <c r="P25">
+        <v>2.9109999999999997E-4</v>
       </c>
       <c r="Q25">
         <v>46.54</v>
       </c>
       <c r="R25" s="2">
-        <v>0.2273</v>
+        <v>0.23</v>
       </c>
       <c r="S25">
-        <v>19.48</v>
+        <v>18.918700000000001</v>
       </c>
       <c r="T25" s="2">
         <f t="shared" si="2"/>
@@ -2917,20 +2910,20 @@
       <c r="N26">
         <v>124.04</v>
       </c>
-      <c r="O26" s="4">
-        <v>1.2285099999999999E-3</v>
-      </c>
-      <c r="P26" s="3">
-        <v>2.6019999999999998E-4</v>
+      <c r="O26">
+        <v>1.2285E-3</v>
+      </c>
+      <c r="P26">
+        <v>2.5799999999999998E-4</v>
       </c>
       <c r="Q26">
         <v>50.55</v>
       </c>
       <c r="R26" s="2">
-        <v>0.21179999999999999</v>
+        <v>0.21</v>
       </c>
       <c r="S26">
-        <v>21.16</v>
+        <v>20.888400000000001</v>
       </c>
       <c r="T26" s="2">
         <f t="shared" si="2"/>
@@ -2991,20 +2984,20 @@
       <c r="N27">
         <v>149.63999999999999</v>
       </c>
-      <c r="O27" s="4">
-        <v>1.18115E-3</v>
-      </c>
-      <c r="P27" s="3">
-        <v>2.4264999999999999E-4</v>
+      <c r="O27">
+        <v>1.1812000000000001E-3</v>
+      </c>
+      <c r="P27">
+        <v>2.4810000000000001E-4</v>
       </c>
       <c r="Q27">
         <v>50.54</v>
       </c>
       <c r="R27" s="2">
-        <v>0.2054</v>
+        <v>0.21</v>
       </c>
       <c r="S27">
-        <v>21.15</v>
+        <v>20.8843</v>
       </c>
       <c r="T27" s="2">
         <f t="shared" si="2"/>
@@ -3065,20 +3058,20 @@
       <c r="N28">
         <v>113.99</v>
       </c>
-      <c r="O28" s="4">
-        <v>1.1902499999999999E-3</v>
-      </c>
-      <c r="P28" s="3">
-        <v>2.4363999999999999E-4</v>
+      <c r="O28">
+        <v>1.1594000000000001E-3</v>
+      </c>
+      <c r="P28">
+        <v>2.319E-4</v>
       </c>
       <c r="Q28">
-        <v>51.63</v>
+        <v>53</v>
       </c>
       <c r="R28" s="2">
-        <v>0.20469999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="S28">
-        <v>21.33</v>
+        <v>22.083300000000001</v>
       </c>
       <c r="T28" s="2">
         <f t="shared" si="2"/>
@@ -3139,20 +3132,20 @@
       <c r="N29">
         <v>122.69</v>
       </c>
-      <c r="O29" s="4">
-        <v>1.4166999999999999E-3</v>
-      </c>
-      <c r="P29" s="3">
-        <v>3.2142999999999999E-4</v>
+      <c r="O29">
+        <v>1.3697E-3</v>
+      </c>
+      <c r="P29">
+        <v>3.1500000000000001E-4</v>
       </c>
       <c r="Q29">
-        <v>47.86</v>
+        <v>49.5</v>
       </c>
       <c r="R29" s="2">
-        <v>0.22689999999999999</v>
+        <v>0.23</v>
       </c>
       <c r="S29">
-        <v>19.78</v>
+        <v>20.122</v>
       </c>
       <c r="T29" s="2">
         <f t="shared" si="2"/>
@@ -3213,20 +3206,20 @@
       <c r="N30">
         <v>111.95</v>
       </c>
-      <c r="O30" s="4">
-        <v>1.3313999999999999E-3</v>
-      </c>
-      <c r="P30" s="3">
-        <v>2.7836000000000001E-4</v>
+      <c r="O30">
+        <v>1.2945000000000001E-3</v>
+      </c>
+      <c r="P30">
+        <v>2.719E-4</v>
       </c>
       <c r="Q30">
-        <v>53.48</v>
+        <v>55</v>
       </c>
       <c r="R30" s="2">
-        <v>0.20910000000000001</v>
+        <v>0.21</v>
       </c>
       <c r="S30">
-        <v>22.1</v>
+        <v>22.7273</v>
       </c>
       <c r="T30" s="2">
         <f t="shared" si="2"/>
@@ -3262,11 +3255,11 @@
         <v>0.39215686274509803</v>
       </c>
       <c r="G31" s="2">
-        <f t="shared" si="1"/>
+        <f>(PI()*D31*E31)</f>
         <v>3204.424506661589</v>
       </c>
       <c r="H31" s="2">
-        <f t="shared" si="0"/>
+        <f>((PI()*D31^2)*E31)/4</f>
         <v>40856.412459935258</v>
       </c>
       <c r="I31" s="2">
@@ -3287,23 +3280,23 @@
       <c r="N31">
         <v>115.22</v>
       </c>
-      <c r="O31" s="4">
-        <v>1.27487E-3</v>
-      </c>
-      <c r="P31" s="3">
-        <v>2.5415000000000002E-4</v>
+      <c r="O31">
+        <v>1.2393E-3</v>
+      </c>
+      <c r="P31">
+        <v>2.4790000000000001E-4</v>
       </c>
       <c r="Q31">
-        <v>54.44</v>
+        <v>56</v>
       </c>
       <c r="R31" s="2">
-        <v>0.19939999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="S31">
-        <v>22.49</v>
+        <v>23.333300000000001</v>
       </c>
       <c r="T31" s="2">
-        <f t="shared" si="2"/>
+        <f>RADIANS(C31)</f>
         <v>1.5707963267948966</v>
       </c>
       <c r="U31">
@@ -3361,27 +3354,27 @@
       <c r="N32">
         <v>127.33</v>
       </c>
-      <c r="O32" s="4">
-        <v>1.29688E-3</v>
-      </c>
-      <c r="P32" s="3">
-        <v>2.7092000000000001E-4</v>
+      <c r="O32">
+        <v>1.2823999999999999E-3</v>
+      </c>
+      <c r="P32">
+        <v>2.9500000000000001E-4</v>
       </c>
       <c r="Q32">
-        <v>31.09</v>
+        <v>33</v>
       </c>
       <c r="R32" s="2">
-        <v>0.2089</v>
+        <v>0.23</v>
       </c>
       <c r="S32">
-        <v>6.42</v>
+        <v>13.4146</v>
       </c>
       <c r="T32" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="U32">
-        <v>40.32</v>
+        <v>42.32</v>
       </c>
       <c r="V32">
         <v>11.940000000000001</v>
@@ -3435,27 +3428,27 @@
       <c r="N33">
         <v>124.04</v>
       </c>
-      <c r="O33" s="4">
-        <v>1.21959E-3</v>
-      </c>
-      <c r="P33" s="3">
-        <v>2.4282000000000001E-4</v>
+      <c r="O33">
+        <v>1.2606E-3</v>
+      </c>
+      <c r="P33">
+        <v>2.7730000000000002E-4</v>
       </c>
       <c r="Q33">
-        <v>33.29</v>
+        <v>33</v>
       </c>
       <c r="R33" s="2">
-        <v>0.1991</v>
+        <v>0.22</v>
       </c>
       <c r="S33">
-        <v>6.88</v>
+        <v>13.5246</v>
       </c>
       <c r="T33" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="U33">
-        <v>40.6</v>
+        <v>41.6</v>
       </c>
       <c r="V33">
         <v>11.940000000000001</v>
@@ -3509,27 +3502,27 @@
       <c r="N34">
         <v>120.44</v>
       </c>
-      <c r="O34" s="4">
-        <v>1.20261E-3</v>
-      </c>
-      <c r="P34" s="3">
-        <v>2.309E-4</v>
+      <c r="O34">
+        <v>1.3212E-3</v>
+      </c>
+      <c r="P34">
+        <v>3.1710000000000001E-4</v>
       </c>
       <c r="Q34">
-        <v>33.76</v>
+        <v>33</v>
       </c>
       <c r="R34" s="2">
-        <v>0.192</v>
+        <v>0.24</v>
       </c>
       <c r="S34">
-        <v>6.98</v>
+        <v>13.3065</v>
       </c>
       <c r="T34" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="U34">
-        <v>40.6</v>
+        <v>43.6</v>
       </c>
       <c r="V34">
         <v>11.940000000000001</v>
@@ -3583,20 +3576,20 @@
       <c r="N35">
         <v>117.11</v>
       </c>
-      <c r="O35" s="4">
+      <c r="O35">
         <v>1.3397999999999999E-3</v>
       </c>
-      <c r="P35" s="3">
-        <v>2.2723E-4</v>
+      <c r="P35">
+        <v>2.5460000000000001E-4</v>
       </c>
       <c r="Q35">
         <v>28.87</v>
       </c>
       <c r="R35" s="2">
-        <v>0.1696</v>
+        <v>0.19</v>
       </c>
       <c r="S35">
-        <v>7.08</v>
+        <v>12.1303</v>
       </c>
       <c r="T35" s="2">
         <f t="shared" si="2"/>
@@ -3657,20 +3650,20 @@
       <c r="N36">
         <v>136.79</v>
       </c>
-      <c r="O36" s="4">
-        <v>1.51746E-3</v>
-      </c>
-      <c r="P36" s="3">
-        <v>2.6267E-4</v>
+      <c r="O36">
+        <v>1.5175E-3</v>
+      </c>
+      <c r="P36">
+        <v>2.7310000000000002E-4</v>
       </c>
       <c r="Q36">
         <v>28.93</v>
       </c>
       <c r="R36" s="2">
-        <v>0.1731</v>
+        <v>0.18</v>
       </c>
       <c r="S36">
-        <v>7.09</v>
+        <v>12.2585</v>
       </c>
       <c r="T36" s="2">
         <f t="shared" si="2"/>
@@ -3731,20 +3724,20 @@
       <c r="N37">
         <v>126.86</v>
       </c>
-      <c r="O37" s="4">
-        <v>1.4039600000000001E-3</v>
-      </c>
-      <c r="P37" s="3">
-        <v>2.4766000000000002E-4</v>
+      <c r="O37">
+        <v>1.4040000000000001E-3</v>
+      </c>
+      <c r="P37">
+        <v>2.8079999999999999E-4</v>
       </c>
       <c r="Q37">
         <v>27.28</v>
       </c>
       <c r="R37" s="2">
-        <v>0.1764</v>
+        <v>0.2</v>
       </c>
       <c r="S37">
-        <v>6.69</v>
+        <v>11.3667</v>
       </c>
       <c r="T37" s="2">
         <f t="shared" si="2"/>
@@ -3805,20 +3798,20 @@
       <c r="N38">
         <v>128.74</v>
       </c>
-      <c r="O38" s="4">
-        <v>1.1741200000000001E-3</v>
-      </c>
-      <c r="P38" s="3">
-        <v>1.6061999999999999E-4</v>
+      <c r="O38">
+        <v>1.1741E-3</v>
+      </c>
+      <c r="P38">
+        <v>1.8789999999999999E-4</v>
       </c>
       <c r="Q38">
         <v>21.02</v>
       </c>
       <c r="R38" s="2">
-        <v>0.1368</v>
+        <v>0.16</v>
       </c>
       <c r="S38">
-        <v>7.13</v>
+        <v>9.0602999999999998</v>
       </c>
       <c r="T38" s="2">
         <f t="shared" si="2"/>
@@ -3879,20 +3872,20 @@
       <c r="N39">
         <v>132.5</v>
       </c>
-      <c r="O39" s="4">
-        <v>1.4559900000000001E-3</v>
-      </c>
-      <c r="P39" s="3">
-        <v>1.9933E-4</v>
+      <c r="O39">
+        <v>1.456E-3</v>
+      </c>
+      <c r="P39">
+        <v>2.475E-4</v>
       </c>
       <c r="Q39">
         <v>23.97</v>
       </c>
       <c r="R39" s="2">
-        <v>0.13689999999999999</v>
+        <v>0.17</v>
       </c>
       <c r="S39">
-        <v>8.1300000000000008</v>
+        <v>10.243600000000001</v>
       </c>
       <c r="T39" s="2">
         <f t="shared" si="2"/>
@@ -3953,20 +3946,20 @@
       <c r="N40">
         <v>120.89</v>
       </c>
-      <c r="O40" s="4">
-        <v>1.12695E-3</v>
-      </c>
-      <c r="P40" s="3">
-        <v>1.4797000000000001E-4</v>
+      <c r="O40">
+        <v>1.127E-3</v>
+      </c>
+      <c r="P40">
+        <v>1.6899999999999999E-4</v>
       </c>
       <c r="Q40">
         <v>21.74</v>
       </c>
       <c r="R40" s="2">
-        <v>0.1313</v>
+        <v>0.15</v>
       </c>
       <c r="S40">
-        <v>7.39</v>
+        <v>9.4521999999999995</v>
       </c>
       <c r="T40" s="2">
         <f t="shared" si="2"/>
@@ -4027,27 +4020,27 @@
       <c r="N41">
         <v>130.15</v>
       </c>
-      <c r="O41" s="4">
-        <v>1.29262E-3</v>
-      </c>
-      <c r="P41" s="3">
-        <v>1.5447E-4</v>
+      <c r="O41">
+        <v>1.0097000000000001E-3</v>
+      </c>
+      <c r="P41">
+        <v>1.4139999999999999E-4</v>
       </c>
       <c r="Q41">
         <v>19.649999999999999</v>
       </c>
       <c r="R41" s="2">
-        <v>0.1195</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="S41">
-        <v>8.5299999999999994</v>
+        <v>8.6183999999999994</v>
       </c>
       <c r="T41" s="2">
         <f t="shared" si="2"/>
         <v>0.78539816339744828</v>
       </c>
       <c r="U41">
-        <v>25.4</v>
+        <v>19.84</v>
       </c>
       <c r="V41">
         <v>8.2899999999999991</v>
@@ -4101,27 +4094,27 @@
       <c r="N42">
         <v>116.69</v>
       </c>
-      <c r="O42" s="4">
-        <v>1.31098E-3</v>
-      </c>
-      <c r="P42" s="3">
-        <v>1.526E-4</v>
+      <c r="O42">
+        <v>9.812E-4</v>
+      </c>
+      <c r="P42">
+        <v>1.5699999999999999E-4</v>
       </c>
       <c r="Q42">
         <v>19.68</v>
       </c>
       <c r="R42" s="2">
-        <v>0.1164</v>
+        <v>0.16</v>
       </c>
       <c r="S42">
-        <v>8.57</v>
+        <v>8.4827999999999992</v>
       </c>
       <c r="T42" s="2">
         <f t="shared" si="2"/>
         <v>0.78539816339744828</v>
       </c>
       <c r="U42">
-        <v>25.8</v>
+        <v>19.309999999999999</v>
       </c>
       <c r="V42">
         <v>8.2899999999999991</v>
@@ -4175,27 +4168,27 @@
       <c r="N43">
         <v>114.11</v>
       </c>
-      <c r="O43" s="4">
-        <v>1.31098E-3</v>
-      </c>
-      <c r="P43" s="3">
-        <v>1.5666000000000001E-4</v>
+      <c r="O43">
+        <v>9.0450000000000003E-4</v>
+      </c>
+      <c r="P43">
+        <v>1.3569999999999999E-4</v>
       </c>
       <c r="Q43">
         <v>19.68</v>
       </c>
       <c r="R43" s="2">
-        <v>0.1195</v>
+        <v>0.15</v>
       </c>
       <c r="S43">
-        <v>8.5500000000000007</v>
+        <v>8.5564999999999998</v>
       </c>
       <c r="T43" s="2">
         <f t="shared" si="2"/>
         <v>0.78539816339744828</v>
       </c>
       <c r="U43">
-        <v>25.8</v>
+        <v>17.8</v>
       </c>
       <c r="V43">
         <v>8.2899999999999991</v>
@@ -4249,20 +4242,20 @@
       <c r="N44">
         <v>123.59</v>
       </c>
-      <c r="O44" s="4">
-        <v>1.7353799999999999E-3</v>
-      </c>
-      <c r="P44" s="3">
-        <v>2.1172000000000001E-4</v>
+      <c r="O44">
+        <v>1.7354E-3</v>
+      </c>
+      <c r="P44">
+        <v>2.6029999999999998E-4</v>
       </c>
       <c r="Q44">
         <v>21.2</v>
       </c>
       <c r="R44" s="2">
-        <v>0.122</v>
+        <v>0.15</v>
       </c>
       <c r="S44">
-        <v>10.09</v>
+        <v>9.2173999999999996</v>
       </c>
       <c r="T44" s="2">
         <f t="shared" si="2"/>
@@ -4323,20 +4316,20 @@
       <c r="N45">
         <v>131.56</v>
       </c>
-      <c r="O45" s="4">
-        <v>1.7497599999999999E-3</v>
-      </c>
-      <c r="P45" s="3">
-        <v>2.0875000000000001E-4</v>
+      <c r="O45">
+        <v>1.7497999999999999E-3</v>
+      </c>
+      <c r="P45">
+        <v>2.4499999999999999E-4</v>
       </c>
       <c r="Q45">
         <v>21.26</v>
       </c>
       <c r="R45" s="2">
-        <v>0.1193</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="S45">
-        <v>10.15</v>
+        <v>9.3246000000000002</v>
       </c>
       <c r="T45" s="2">
         <f t="shared" si="2"/>
@@ -4397,20 +4390,20 @@
       <c r="N46">
         <v>132.87</v>
       </c>
-      <c r="O46" s="4">
-        <v>1.84717E-3</v>
-      </c>
-      <c r="P46" s="3">
-        <v>2.4143E-4</v>
+      <c r="O46">
+        <v>1.8472E-3</v>
+      </c>
+      <c r="P46">
+        <v>2.9550000000000003E-4</v>
       </c>
       <c r="Q46">
         <v>19.760000000000002</v>
       </c>
       <c r="R46" s="2">
-        <v>0.13070000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="S46">
-        <v>9.32</v>
+        <v>8.5172000000000008</v>
       </c>
       <c r="T46" s="2">
         <f t="shared" si="2"/>
@@ -4471,20 +4464,20 @@
       <c r="N47">
         <v>136.30000000000001</v>
       </c>
-      <c r="O47" s="4">
-        <v>1.6368800000000001E-3</v>
-      </c>
-      <c r="P47" s="3">
-        <v>2.6615999999999999E-4</v>
+      <c r="O47">
+        <v>1.6368999999999999E-3</v>
+      </c>
+      <c r="P47">
+        <v>2.7829999999999999E-4</v>
       </c>
       <c r="Q47">
         <v>22.72</v>
       </c>
       <c r="R47" s="2">
-        <v>0.16259999999999999</v>
+        <v>0.17</v>
       </c>
       <c r="S47">
-        <v>10.14</v>
+        <v>9.7094000000000005</v>
       </c>
       <c r="T47" s="2">
         <f t="shared" si="2"/>
@@ -4545,20 +4538,20 @@
       <c r="N48">
         <v>114.54</v>
       </c>
-      <c r="O48" s="4">
-        <v>1.52268E-3</v>
-      </c>
-      <c r="P48" s="3">
-        <v>2.0038E-4</v>
+      <c r="O48">
+        <v>1.5227000000000001E-3</v>
+      </c>
+      <c r="P48">
+        <v>2.284E-4</v>
       </c>
       <c r="Q48">
         <v>26.67</v>
       </c>
       <c r="R48" s="2">
-        <v>0.13159999999999999</v>
+        <v>0.15</v>
       </c>
       <c r="S48">
-        <v>12.26</v>
+        <v>11.595700000000001</v>
       </c>
       <c r="T48" s="2">
         <f t="shared" si="2"/>
@@ -4611,28 +4604,28 @@
         <v>2.7749999999999999</v>
       </c>
       <c r="L49" s="2">
-        <v>4.8290677315390145</v>
+        <v>6.5915011999999997</v>
       </c>
       <c r="M49">
-        <v>2.74</v>
+        <v>3.74</v>
       </c>
       <c r="N49">
         <v>122.69</v>
       </c>
-      <c r="O49" s="4">
-        <v>1.6364800000000001E-3</v>
-      </c>
-      <c r="P49" s="3">
-        <v>2.3418000000000001E-4</v>
+      <c r="O49">
+        <v>1.6364999999999999E-3</v>
+      </c>
+      <c r="P49">
+        <v>2.6180000000000002E-4</v>
       </c>
       <c r="Q49">
         <v>23.85</v>
       </c>
       <c r="R49" s="2">
-        <v>0.1431</v>
+        <v>0.16</v>
       </c>
       <c r="S49">
-        <v>10.84</v>
+        <v>10.280200000000001</v>
       </c>
       <c r="T49" s="2">
         <f t="shared" si="2"/>
@@ -4693,20 +4686,20 @@
       <c r="N50">
         <v>122.26</v>
       </c>
-      <c r="O50" s="4">
-        <v>1.69093E-3</v>
-      </c>
-      <c r="P50" s="3">
-        <v>2.4366000000000001E-4</v>
+      <c r="O50">
+        <v>1.6909E-3</v>
+      </c>
+      <c r="P50">
+        <v>2.875E-4</v>
       </c>
       <c r="Q50">
         <v>24.59</v>
       </c>
       <c r="R50" s="2">
-        <v>0.14410000000000001</v>
+        <v>0.17</v>
       </c>
       <c r="S50">
-        <v>11.17</v>
+        <v>10.5085</v>
       </c>
       <c r="T50" s="2">
         <f t="shared" si="2"/>
@@ -4767,27 +4760,27 @@
       <c r="N51">
         <v>135.32</v>
       </c>
-      <c r="O51" s="4">
-        <v>1.5642900000000001E-3</v>
-      </c>
-      <c r="P51" s="3">
-        <v>2.4262E-4</v>
+      <c r="O51">
+        <v>1.6909E-3</v>
+      </c>
+      <c r="P51">
+        <v>3.213E-4</v>
       </c>
       <c r="Q51">
-        <v>27.61</v>
+        <v>28.5</v>
       </c>
       <c r="R51" s="2">
-        <v>0.15509999999999999</v>
+        <v>0.19</v>
       </c>
       <c r="S51">
-        <v>11.95</v>
+        <v>11.9748</v>
       </c>
       <c r="T51" s="2">
         <f t="shared" si="2"/>
         <v>1.5707963267948966</v>
       </c>
       <c r="U51">
-        <v>43.19</v>
+        <v>48.19</v>
       </c>
       <c r="V51">
         <v>12.52</v>
@@ -4841,27 +4834,27 @@
       <c r="N52">
         <v>120.89</v>
       </c>
-      <c r="O52" s="4">
-        <v>1.6464299999999999E-3</v>
-      </c>
-      <c r="P52" s="3">
-        <v>2.6753999999999998E-4</v>
+      <c r="O52">
+        <v>1.7828E-3</v>
+      </c>
+      <c r="P52">
+        <v>3.2089999999999999E-4</v>
       </c>
       <c r="Q52">
-        <v>26.36</v>
+        <v>28.5</v>
       </c>
       <c r="R52" s="2">
-        <v>0.16250000000000001</v>
+        <v>0.18</v>
       </c>
       <c r="S52">
-        <v>11.34</v>
+        <v>12.0763</v>
       </c>
       <c r="T52" s="2">
         <f t="shared" si="2"/>
         <v>1.5707963267948966</v>
       </c>
       <c r="U52">
-        <v>43.4</v>
+        <v>50.81</v>
       </c>
       <c r="V52">
         <v>12.52</v>
@@ -4915,27 +4908,27 @@
       <c r="N53">
         <v>123.14</v>
       </c>
-      <c r="O53" s="4">
-        <v>1.6092000000000001E-3</v>
-      </c>
-      <c r="P53" s="3">
-        <v>2.6150000000000001E-4</v>
+      <c r="O53">
+        <v>1.6982E-3</v>
+      </c>
+      <c r="P53">
+        <v>3.3960000000000001E-4</v>
       </c>
       <c r="Q53">
-        <v>26.97</v>
+        <v>28.5</v>
       </c>
       <c r="R53" s="2">
-        <v>0.16250000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="S53">
-        <v>11.6</v>
+        <v>11.875</v>
       </c>
       <c r="T53" s="2">
         <f t="shared" si="2"/>
         <v>1.5707963267948966</v>
       </c>
       <c r="U53">
-        <v>43.4</v>
+        <v>48.4</v>
       </c>
       <c r="V53">
         <v>12.52</v>
@@ -5054,682 +5047,21 @@
       <c r="P64"/>
       <c r="R64"/>
     </row>
-    <row r="65" spans="7:18" x14ac:dyDescent="0.2">
-      <c r="G65"/>
-      <c r="I65"/>
-      <c r="J65"/>
-      <c r="K65"/>
-      <c r="L65"/>
-      <c r="O65"/>
-      <c r="P65"/>
-      <c r="R65"/>
-    </row>
-    <row r="66" spans="7:18" x14ac:dyDescent="0.2">
-      <c r="G66"/>
-      <c r="I66"/>
-      <c r="J66"/>
-      <c r="K66"/>
-      <c r="L66"/>
-      <c r="O66"/>
-      <c r="P66"/>
-      <c r="R66"/>
-    </row>
-    <row r="67" spans="7:18" x14ac:dyDescent="0.2">
-      <c r="G67"/>
-      <c r="I67"/>
-      <c r="J67"/>
-      <c r="K67"/>
-      <c r="L67"/>
-      <c r="O67"/>
-      <c r="P67"/>
-      <c r="R67"/>
-    </row>
-    <row r="68" spans="7:18" x14ac:dyDescent="0.2">
-      <c r="G68"/>
-      <c r="I68"/>
-      <c r="J68"/>
-      <c r="K68"/>
-      <c r="L68"/>
-      <c r="O68"/>
-      <c r="P68"/>
-      <c r="R68"/>
-    </row>
-    <row r="69" spans="7:18" x14ac:dyDescent="0.2">
-      <c r="G69"/>
-      <c r="I69"/>
-      <c r="J69"/>
-      <c r="K69"/>
-      <c r="L69"/>
-      <c r="O69"/>
-      <c r="P69"/>
-      <c r="R69"/>
-    </row>
-    <row r="70" spans="7:18" x14ac:dyDescent="0.2">
-      <c r="G70"/>
-      <c r="I70"/>
-      <c r="J70"/>
-      <c r="K70"/>
-      <c r="L70"/>
-      <c r="O70"/>
-      <c r="P70"/>
-      <c r="R70"/>
-    </row>
-    <row r="71" spans="7:18" x14ac:dyDescent="0.2">
-      <c r="G71"/>
-      <c r="I71"/>
-      <c r="J71"/>
-      <c r="K71"/>
-      <c r="L71"/>
-      <c r="O71"/>
-      <c r="P71"/>
-      <c r="R71"/>
-    </row>
-    <row r="72" spans="7:18" x14ac:dyDescent="0.2">
-      <c r="G72"/>
-      <c r="I72"/>
-      <c r="J72"/>
-      <c r="K72"/>
-      <c r="L72"/>
-      <c r="O72"/>
-      <c r="P72"/>
-      <c r="R72"/>
-    </row>
-    <row r="73" spans="7:18" x14ac:dyDescent="0.2">
-      <c r="G73"/>
-      <c r="I73"/>
-      <c r="J73"/>
-      <c r="K73"/>
-      <c r="L73"/>
-      <c r="O73"/>
-      <c r="P73"/>
-      <c r="R73"/>
-    </row>
-    <row r="74" spans="7:18" x14ac:dyDescent="0.2">
-      <c r="G74"/>
-      <c r="I74"/>
-      <c r="J74"/>
-      <c r="K74"/>
-      <c r="L74"/>
-      <c r="O74"/>
-      <c r="P74"/>
-      <c r="R74"/>
-    </row>
-    <row r="75" spans="7:18" x14ac:dyDescent="0.2">
-      <c r="G75"/>
-      <c r="I75"/>
-      <c r="J75"/>
-      <c r="K75"/>
-      <c r="L75"/>
-      <c r="O75"/>
-      <c r="P75"/>
-      <c r="R75"/>
-    </row>
-    <row r="76" spans="7:18" x14ac:dyDescent="0.2">
-      <c r="G76"/>
-      <c r="I76"/>
-      <c r="J76"/>
-      <c r="K76"/>
-      <c r="L76"/>
-      <c r="O76"/>
-      <c r="P76"/>
-      <c r="R76"/>
-    </row>
-    <row r="77" spans="7:18" x14ac:dyDescent="0.2">
-      <c r="G77"/>
-      <c r="I77"/>
-      <c r="J77"/>
-      <c r="K77"/>
-      <c r="L77"/>
-      <c r="O77"/>
-      <c r="P77"/>
-      <c r="R77"/>
-    </row>
+    <row r="65" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="66" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="67" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="68" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="69" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="70" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="71" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="72" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="73" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="74" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="75" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="76" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="77" customFormat="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{174416E8-D472-1244-B2F8-F4BD841DC05A}">
-  <dimension ref="A1:G23"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="5" max="5" width="15" customWidth="1"/>
-    <col min="6" max="6" width="17.1640625" customWidth="1"/>
-    <col min="7" max="7" width="21.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2">
-        <v>31</v>
-      </c>
-      <c r="B2">
-        <v>0</v>
-      </c>
-      <c r="C2">
-        <v>31.09</v>
-      </c>
-      <c r="D2">
-        <v>2.7092000000000001E-4</v>
-      </c>
-      <c r="E2">
-        <v>1.29688E-3</v>
-      </c>
-      <c r="F2">
-        <v>0.2089</v>
-      </c>
-      <c r="G2">
-        <v>6.42</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3">
-        <v>32</v>
-      </c>
-      <c r="B3">
-        <v>0</v>
-      </c>
-      <c r="C3">
-        <v>33.29</v>
-      </c>
-      <c r="D3">
-        <v>2.4282000000000001E-4</v>
-      </c>
-      <c r="E3">
-        <v>1.21959E-3</v>
-      </c>
-      <c r="F3">
-        <v>0.1991</v>
-      </c>
-      <c r="G3">
-        <v>6.88</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A4">
-        <v>33</v>
-      </c>
-      <c r="B4">
-        <v>0</v>
-      </c>
-      <c r="C4">
-        <v>33.76</v>
-      </c>
-      <c r="D4">
-        <v>2.309E-4</v>
-      </c>
-      <c r="E4">
-        <v>1.20261E-3</v>
-      </c>
-      <c r="F4">
-        <v>0.192</v>
-      </c>
-      <c r="G4">
-        <v>6.98</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5">
-        <v>34</v>
-      </c>
-      <c r="B5">
-        <v>15</v>
-      </c>
-      <c r="C5">
-        <v>28.87</v>
-      </c>
-      <c r="D5">
-        <v>2.2723E-4</v>
-      </c>
-      <c r="E5">
-        <v>1.3397999999999999E-3</v>
-      </c>
-      <c r="F5">
-        <v>0.1696</v>
-      </c>
-      <c r="G5">
-        <v>7.08</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6">
-        <v>35</v>
-      </c>
-      <c r="B6">
-        <v>15</v>
-      </c>
-      <c r="C6">
-        <v>28.93</v>
-      </c>
-      <c r="D6">
-        <v>2.6267E-4</v>
-      </c>
-      <c r="E6">
-        <v>1.51746E-3</v>
-      </c>
-      <c r="F6">
-        <v>0.1731</v>
-      </c>
-      <c r="G6">
-        <v>7.09</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A7">
-        <v>36</v>
-      </c>
-      <c r="B7">
-        <v>15</v>
-      </c>
-      <c r="C7">
-        <v>27.28</v>
-      </c>
-      <c r="D7">
-        <v>2.4766000000000002E-4</v>
-      </c>
-      <c r="E7">
-        <v>1.4039600000000001E-3</v>
-      </c>
-      <c r="F7">
-        <v>0.1764</v>
-      </c>
-      <c r="G7">
-        <v>6.69</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A8">
-        <v>37</v>
-      </c>
-      <c r="B8">
-        <v>30</v>
-      </c>
-      <c r="C8">
-        <v>21.02</v>
-      </c>
-      <c r="D8">
-        <v>1.6061999999999999E-4</v>
-      </c>
-      <c r="E8">
-        <v>1.1741200000000001E-3</v>
-      </c>
-      <c r="F8">
-        <v>0.1368</v>
-      </c>
-      <c r="G8">
-        <v>7.13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A9">
-        <v>38</v>
-      </c>
-      <c r="B9">
-        <v>30</v>
-      </c>
-      <c r="C9">
-        <v>23.97</v>
-      </c>
-      <c r="D9">
-        <v>1.9933E-4</v>
-      </c>
-      <c r="E9">
-        <v>1.4559900000000001E-3</v>
-      </c>
-      <c r="F9">
-        <v>0.13689999999999999</v>
-      </c>
-      <c r="G9">
-        <v>8.1300000000000008</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A10">
-        <v>39</v>
-      </c>
-      <c r="B10">
-        <v>30</v>
-      </c>
-      <c r="C10">
-        <v>21.74</v>
-      </c>
-      <c r="D10">
-        <v>1.4797000000000001E-4</v>
-      </c>
-      <c r="E10">
-        <v>1.12695E-3</v>
-      </c>
-      <c r="F10">
-        <v>0.1313</v>
-      </c>
-      <c r="G10">
-        <v>7.39</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A11">
-        <v>40</v>
-      </c>
-      <c r="B11">
-        <v>45</v>
-      </c>
-      <c r="C11">
-        <v>19.649999999999999</v>
-      </c>
-      <c r="D11">
-        <v>1.5447E-4</v>
-      </c>
-      <c r="E11">
-        <v>1.29262E-3</v>
-      </c>
-      <c r="F11">
-        <v>0.1195</v>
-      </c>
-      <c r="G11">
-        <v>8.5299999999999994</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A12">
-        <v>41</v>
-      </c>
-      <c r="B12">
-        <v>45</v>
-      </c>
-      <c r="C12">
-        <v>19.68</v>
-      </c>
-      <c r="D12">
-        <v>1.526E-4</v>
-      </c>
-      <c r="E12">
-        <v>1.31098E-3</v>
-      </c>
-      <c r="F12">
-        <v>0.1164</v>
-      </c>
-      <c r="G12">
-        <v>8.57</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A13">
-        <v>42</v>
-      </c>
-      <c r="B13">
-        <v>45</v>
-      </c>
-      <c r="C13">
-        <v>19.68</v>
-      </c>
-      <c r="D13">
-        <v>1.5666000000000001E-4</v>
-      </c>
-      <c r="E13">
-        <v>1.31098E-3</v>
-      </c>
-      <c r="F13">
-        <v>0.1195</v>
-      </c>
-      <c r="G13">
-        <v>8.5500000000000007</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A14">
-        <v>43</v>
-      </c>
-      <c r="B14">
-        <v>60</v>
-      </c>
-      <c r="C14">
-        <v>21.2</v>
-      </c>
-      <c r="D14">
-        <v>2.1172000000000001E-4</v>
-      </c>
-      <c r="E14">
-        <v>1.7353799999999999E-3</v>
-      </c>
-      <c r="F14">
-        <v>0.122</v>
-      </c>
-      <c r="G14">
-        <v>10.09</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A15">
-        <v>44</v>
-      </c>
-      <c r="B15">
-        <v>60</v>
-      </c>
-      <c r="C15">
-        <v>21.26</v>
-      </c>
-      <c r="D15">
-        <v>2.0875000000000001E-4</v>
-      </c>
-      <c r="E15">
-        <v>1.7497599999999999E-3</v>
-      </c>
-      <c r="F15">
-        <v>0.1193</v>
-      </c>
-      <c r="G15">
-        <v>10.15</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A16">
-        <v>45</v>
-      </c>
-      <c r="B16">
-        <v>60</v>
-      </c>
-      <c r="C16">
-        <v>19.760000000000002</v>
-      </c>
-      <c r="D16">
-        <v>2.4143E-4</v>
-      </c>
-      <c r="E16">
-        <v>1.84717E-3</v>
-      </c>
-      <c r="F16">
-        <v>0.13070000000000001</v>
-      </c>
-      <c r="G16">
-        <v>9.32</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A17">
-        <v>46</v>
-      </c>
-      <c r="B17">
-        <v>75</v>
-      </c>
-      <c r="C17">
-        <v>22.72</v>
-      </c>
-      <c r="D17">
-        <v>2.6615999999999999E-4</v>
-      </c>
-      <c r="E17">
-        <v>1.6368800000000001E-3</v>
-      </c>
-      <c r="F17">
-        <v>0.16259999999999999</v>
-      </c>
-      <c r="G17">
-        <v>10.14</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A18">
-        <v>47</v>
-      </c>
-      <c r="B18">
-        <v>75</v>
-      </c>
-      <c r="C18">
-        <v>26.67</v>
-      </c>
-      <c r="D18">
-        <v>2.0038E-4</v>
-      </c>
-      <c r="E18">
-        <v>1.52268E-3</v>
-      </c>
-      <c r="F18">
-        <v>0.13159999999999999</v>
-      </c>
-      <c r="G18">
-        <v>12.26</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A19">
-        <v>48</v>
-      </c>
-      <c r="B19">
-        <v>75</v>
-      </c>
-      <c r="C19">
-        <v>23.85</v>
-      </c>
-      <c r="D19">
-        <v>2.3418000000000001E-4</v>
-      </c>
-      <c r="E19">
-        <v>1.6364800000000001E-3</v>
-      </c>
-      <c r="F19">
-        <v>0.1431</v>
-      </c>
-      <c r="G19">
-        <v>10.84</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A20">
-        <v>49</v>
-      </c>
-      <c r="B20">
-        <v>75</v>
-      </c>
-      <c r="C20">
-        <v>24.59</v>
-      </c>
-      <c r="D20">
-        <v>2.4366000000000001E-4</v>
-      </c>
-      <c r="E20">
-        <v>1.69093E-3</v>
-      </c>
-      <c r="F20">
-        <v>0.14410000000000001</v>
-      </c>
-      <c r="G20">
-        <v>11.17</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A21">
-        <v>50</v>
-      </c>
-      <c r="B21">
-        <v>90</v>
-      </c>
-      <c r="C21">
-        <v>27.61</v>
-      </c>
-      <c r="D21">
-        <v>2.4262E-4</v>
-      </c>
-      <c r="E21">
-        <v>1.5642900000000001E-3</v>
-      </c>
-      <c r="F21">
-        <v>0.15509999999999999</v>
-      </c>
-      <c r="G21">
-        <v>11.95</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A22">
-        <v>51</v>
-      </c>
-      <c r="B22">
-        <v>90</v>
-      </c>
-      <c r="C22">
-        <v>26.36</v>
-      </c>
-      <c r="D22">
-        <v>2.6753999999999998E-4</v>
-      </c>
-      <c r="E22">
-        <v>1.6464299999999999E-3</v>
-      </c>
-      <c r="F22">
-        <v>0.16250000000000001</v>
-      </c>
-      <c r="G22">
-        <v>11.34</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A23">
-        <v>52</v>
-      </c>
-      <c r="B23">
-        <v>90</v>
-      </c>
-      <c r="C23">
-        <v>26.97</v>
-      </c>
-      <c r="D23">
-        <v>2.6150000000000001E-4</v>
-      </c>
-      <c r="E23">
-        <v>1.6092000000000001E-3</v>
-      </c>
-      <c r="F23">
-        <v>0.16250000000000001</v>
-      </c>
-      <c r="G23">
-        <v>11.6</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>